--- a/03_GC500_Delivery_Control/review_25Oct2026_baseplan7/GC500_Baseplan7_vs_Site_25Oct2026.xlsx
+++ b/03_GC500_Delivery_Control/review_25Oct2026_baseplan7/GC500_Baseplan7_vs_Site_25Oct2026.xlsx
@@ -41534,7 +41534,7 @@
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>Fence, no scrim (m)</t>
+          <t>Fence, no scrim (m): line 3 at $16.16 + hoarding line 5 at $23.59</t>
         </is>
       </c>
       <c r="B2" s="6" t="n">
@@ -41558,7 +41558,7 @@
         <v>16.16</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>143630.08</v>
+        <v>144447.38</v>
       </c>
     </row>
     <row r="3">
@@ -41808,7 +41808,7 @@
       <c r="F11" s="6" t="n"/>
       <c r="G11" s="6" t="n"/>
       <c r="H11" s="6" t="n">
-        <v>308289.53</v>
+        <v>309106.83</v>
       </c>
     </row>
   </sheetData>

--- a/03_GC500_Delivery_Control/review_25Oct2026_baseplan7/GC500_Baseplan7_vs_Site_25Oct2026.xlsx
+++ b/03_GC500_Delivery_Control/review_25Oct2026_baseplan7/GC500_Baseplan7_vs_Site_25Oct2026.xlsx
@@ -14,11 +14,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Charge lines" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event labour" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fencing (9990776)" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Generators" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="On site, no line" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Branch tie-out" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start dates" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Since 22 Oct" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Arrivals vs dockets" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Generators" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="On site, no line" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Branch tie-out" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start dates" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Since 22 Oct" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2641,42 +2642,42 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="inlineStr">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>9961976</t>
         </is>
       </c>
-      <c r="B56" s="3" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>52</t>
         </is>
       </c>
-      <c r="C56" s="3" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
         <is>
           <t>Quantity</t>
         </is>
       </c>
-      <c r="D56" s="3" t="inlineStr">
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Labour Charge: 2 x $333.12</t>
         </is>
       </c>
-      <c r="E56" s="3" t="inlineStr">
-        <is>
-          <t>1 on site (GN23); GN20 never came</t>
-        </is>
-      </c>
-      <c r="F56" s="3" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>1 on site (GN23); the second is GN20, which Andrew said never came (docket 26102821 says 30 Sep)</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>Quantity 1</t>
         </is>
       </c>
-      <c r="G56" s="3" t="n">
+      <c r="G56" s="2" t="n">
         <v>-333.12</v>
       </c>
-      <c r="H56" s="3" t="inlineStr">
-        <is>
-          <t>Baseplan</t>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>Ask Andrew</t>
         </is>
       </c>
     </row>
@@ -3231,42 +3232,42 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="3" t="inlineStr">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>9961976</t>
         </is>
       </c>
-      <c r="B71" s="3" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="C71" s="3" t="inlineStr">
+      <c r="C71" s="2" t="inlineStr">
         <is>
           <t>Remove</t>
         </is>
       </c>
-      <c r="D71" s="3" t="inlineStr">
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>GN20-S01-Generator 365kVA Diesel (1276701) Delivered at $6,260.40</t>
         </is>
       </c>
-      <c r="E71" s="3" t="inlineStr">
-        <is>
-          <t>GN20's 365 kVA never came (Andrew, 22 Oct 2026: GN20 off the list; record_22Oct2026_gn20_never_came)</t>
-        </is>
-      </c>
-      <c r="F71" s="3" t="inlineStr">
-        <is>
-          <t>Close the line (no charge)</t>
-        </is>
-      </c>
-      <c r="G71" s="3" t="n">
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>GN20's 365 kVA: Andrew, 22 Oct 2026, "never came to site 1276701" (record_22Oct2026_gn20_never_came). But Coates' docket 26102821 has it out on 30 Sep, the line is Delivered on that docket, and our record holds a photo filed under GN20/1276701 at 14:14 that day: settle with Andrew before the branch closes the line</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>Close the line (no charge) if it never came; if it came, an In docket and standby to the day it left</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="n">
         <v>-6260.4</v>
       </c>
-      <c r="H71" s="3" t="inlineStr">
-        <is>
-          <t>Baseplan</t>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>Ask Andrew</t>
         </is>
       </c>
     </row>
@@ -3311,40 +3312,40 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="5" t="inlineStr">
+      <c r="A73" s="4" t="inlineStr">
         <is>
           <t>9968955</t>
         </is>
       </c>
-      <c r="B73" s="5" t="inlineStr">
+      <c r="B73" s="4" t="inlineStr">
         <is>
           <t>38</t>
         </is>
       </c>
-      <c r="C73" s="5" t="inlineStr">
+      <c r="C73" s="4" t="inlineStr">
         <is>
           <t>Asset number</t>
         </is>
       </c>
-      <c r="D73" s="5" t="inlineStr">
+      <c r="D73" s="4" t="inlineStr">
         <is>
           <t>WC07 asset 1317643</t>
         </is>
       </c>
-      <c r="E73" s="5" t="inlineStr">
-        <is>
-          <t>WC07 on site carries 1002538, 1002566, 1002651, 1002715, 1083300, 1181004, 1192643, 1200595, 1211959, 1212552, 1317626, 1317632, 1317640, 1317641, 1317647, 1317648, 1317649, 1317652, 1317658, 1317743</t>
-        </is>
-      </c>
-      <c r="F73" s="5" t="inlineStr">
-        <is>
-          <t>Correct the number on the line (the site number stands)</t>
-        </is>
-      </c>
-      <c r="G73" s="5" t="n"/>
-      <c r="H73" s="5" t="inlineStr">
-        <is>
-          <t>Baseplan</t>
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t>our record has 1317743; Coates docket 26081411 has 1317643, the same as this line</t>
+        </is>
+      </c>
+      <c r="F73" s="4" t="inlineStr">
+        <is>
+          <t>Check the unit: our 1317743 is probably a keying slip for 1317643 (correct our record, not the line)</t>
+        </is>
+      </c>
+      <c r="G73" s="4" t="n"/>
+      <c r="H73" s="4" t="inlineStr">
+        <is>
+          <t>Our record</t>
         </is>
       </c>
     </row>
@@ -3898,6 +3899,162 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Asset no</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Turned up</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>P&amp;L branch</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>Building 6m</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>142514</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E2" s="6" t="inlineStr">
+        <is>
+          <t>KINP</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>HRP</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>Building 6m</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>1189410</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>KINP</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>FR01</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Fridge</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>1129733</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>KINP</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>FR02</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Fridge</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>1157786</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>KINP</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3983,14 +4140,14 @@
         <v>85964.00999999999</v>
       </c>
       <c r="D3" s="6" t="n">
-        <v>-3175.12</v>
+        <v>3418.4</v>
       </c>
       <c r="E3" s="6" t="n">
-        <v>28071.82</v>
+        <v>21478.3</v>
       </c>
       <c r="F3" s="6" t="inlineStr">
         <is>
-          <t>Ask Andrew · Quantity: $-600.00; Baseplan · Hours: $15.01; Baseplan · Quantity: $-333.12; Baseplan · Rate: $3,403.39; Baseplan · Remove: $-6,260.40; Decision · Rate: $28,671.82</t>
+          <t>Ask Andrew · Quantity: $-933.12; Ask Andrew · Remove: $-6,260.40; Baseplan · Hours: $15.01; Baseplan · Rate: $3,403.39; Decision · Rate: $28,671.82</t>
         </is>
       </c>
     </row>
@@ -4051,10 +4208,10 @@
         <v>1022962.43</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>127387.19</v>
+        <v>133980.71</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>19473.42</v>
+        <v>12879.9</v>
       </c>
       <c r="F6" s="6" t="inlineStr"/>
     </row>
@@ -4063,7 +4220,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10247,7 +10404,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -28385,7 +28542,7 @@
       <c r="N241" s="2" t="n"/>
       <c r="O241" s="2" t="inlineStr">
         <is>
-          <t>GN20's 365 kVA never came (Andrew, 22 Oct 2026: GN20 off the list; record_22Oct2026_gn20_never_came)</t>
+          <t>GN20's 365 kVA: Andrew, 22 Oct 2026, "never came to site 1276701" (record_22Oct2026_gn20_never_came). But Coates' docket 26102821 has it out on 30 Sep, the line is Delivered on that docket, and our record holds a photo filed under GN20/1276701 at 14:14 that day: settle with Andrew before the branch closes the line</t>
         </is>
       </c>
     </row>
@@ -40870,7 +41027,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1 large set on site: GN23 (GN20 never came)</t>
+          <t>1 large set on site: GN23 (GN20: Andrew said never came; docket 26102821 says 30 Sep)</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -41822,6 +41979,2274 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:K47"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="70" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Check</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Our reference</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Coates docket</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Docket date</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>What</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Ours (turned up)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Days ours later</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Finding</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Who</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Changes a charge?</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>T0002</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="n">
+        <v>26056582</v>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>1264929</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>LT01 MOLENDINAR Lighting Tower LED Metro</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="n"/>
+      <c r="H2" s="5" t="n"/>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>name only: the towers sit on T0002 on our record (Molendinar council yard, 11 Sep)</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>nobody</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>T0002</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="n">
+        <v>26056582</v>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>1314284</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>LT02 MOLENDINAR Lighting Tower LED Metro</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="n"/>
+      <c r="H3" s="5" t="n"/>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>name only: as LT01</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>nobody</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>T0002</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>26056582</v>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>1264899</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>LT03 MOLENDINAR Lighting Tower LED 76500lm Hybrid</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="n"/>
+      <c r="H4" s="5" t="n"/>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>name only: as LT01</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>nobody</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>T0002</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>26056623</v>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>1188888</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>LT04 MOLENDINAR Lighting Tower LED Metro</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="n"/>
+      <c r="H5" s="5" t="n"/>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>name only: as LT01</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>nobody</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>GN20</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>26102821</v>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1276701</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>GN20-S01-Generator 365kVA Diesel</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="n"/>
+      <c r="H6" s="2" t="n"/>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>not on our record</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>Andrew</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>GN?</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>26121298</v>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>1316182</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>GN26 CONCERT Generator - 200kVA (Diesel)</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="n"/>
+      <c r="H7" s="5" t="n"/>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>name only: the concert sets sit under their own references on our record</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>nobody</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>GN?</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>26121310</v>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>1316183</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>GN27 CONCERT-Generator - 200kVA (Diesel)</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="n"/>
+      <c r="H8" s="5" t="n"/>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>name only: as GN26</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>nobody</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>LT06</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>26139060</v>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>1224791</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>LT05/06-Lighting Tower POD Metro</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="n"/>
+      <c r="H9" s="5" t="n"/>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>name only: the tower pod sits under another reference on our record</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>nobody</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>26064095</v>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1320150</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>P05 Microwave Oven</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="n"/>
+      <c r="H10" s="2" t="n"/>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>not on our record</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>Andrew</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>26064095</v>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>1127574</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>P05 Auto Boil</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="n"/>
+      <c r="H11" s="4" t="n"/>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>our record calls it Aircon; the docket says boiler</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>Our record</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>CP1</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>26064099</v>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1116687</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>CP1 Refrigerator - Large</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="n"/>
+      <c r="H12" s="2" t="n"/>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>not on our record</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>Andrew</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>CP1</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>26064099</v>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>119810</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>CP1 Urn</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="n"/>
+      <c r="H13" s="2" t="n"/>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>not on our record</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>Andrew</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>P33</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>26064103</v>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>1328952</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>P33 Refrigerator - Large</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="n"/>
+      <c r="H14" s="4" t="n"/>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>keying slip: our record has 1238952 on P33</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>Our record</t>
+        </is>
+      </c>
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>P09</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>26076665</v>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>1254390</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>P09 Auto Boil</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="n"/>
+      <c r="H15" s="2" t="n"/>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>not on our record</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>Andrew</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>HRP</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>26085104</v>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>1189410</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>P36 Portable Building Shell 6.0M x 3.0M - Cyclonic Rated</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="n"/>
+      <c r="H16" s="5" t="n"/>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>name only: our record has this shell as HRP (22 Oct review: line 93 is HRP, not P36)</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>nobody</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>P58</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>26088630</v>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>1273656</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>P44 Portable Building Shell 6.0M x 3.0M - Cyclonic Rated</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="n"/>
+      <c r="H17" s="5" t="n"/>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>name only: our record has this shell as P58 (22 Oct review: line 59 is P58, not P44)</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>nobody</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>P39</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>26094129</v>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>1272737</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>P38 Refrigerator - Large</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="n"/>
+      <c r="H18" s="2" t="n"/>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>on our record under another reference</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>Andrew</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>P38</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>26094136</v>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>1272755</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>P39 Refrigerator - Large</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="n"/>
+      <c r="H19" s="2" t="n"/>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>on our record under another reference</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>Andrew</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>P66</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>26126001</v>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>1311990</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>P66 Refrigerator - Large</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="n"/>
+      <c r="H20" s="4" t="n"/>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>keying slip: our record has 131190 on P66</t>
+        </is>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>Our record</t>
+        </is>
+      </c>
+      <c r="K20" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>P51</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>26126190</v>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>1328959</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>P46 Refrigerator - Large</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="n"/>
+      <c r="H21" s="2" t="n"/>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>on our record under another reference</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>Andrew</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>P46, P54</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>26126190</v>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>1328957</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>P51 Refrigerator - Large</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="n"/>
+      <c r="H22" s="2" t="n"/>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>on our record under another reference</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>Andrew</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>WC21</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>26064136</v>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>1083399</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>WC21 Toilet Portable - Fresh Water Flush</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="n"/>
+      <c r="H23" s="2" t="n"/>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>not on our record</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>Andrew</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>WC07</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="n">
+        <v>26081411</v>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>1317643</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>WC07 Toilet Portable - Fresh Water Flush</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="n"/>
+      <c r="H24" s="4" t="n"/>
+      <c r="I24" s="4" t="inlineStr">
+        <is>
+          <t>keying slip: our record has 1317743 on WC07</t>
+        </is>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>Our record</t>
+        </is>
+      </c>
+      <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>WC67</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>26107560</v>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>172824</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>WC01 Toilet Portable - Fresh Water Flush</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="n"/>
+      <c r="H25" s="5" t="n"/>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>placed at WC67 on our record; the docket names WC01 (where it was meant to go)</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>nobody</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr"/>
+      <c r="C26" s="2" t="n">
+        <v>26135873</v>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>1065384</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Laserplane</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="n"/>
+      <c r="H26" s="2" t="n"/>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>not on our record</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>Andrew</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Number on two references</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>P26, P46</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="n"/>
+      <c r="D27" s="4" t="n"/>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>1311992</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>Fridge / Fridge Lge / Furniture</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="n"/>
+      <c r="H27" s="4" t="n"/>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>one number, two references on our record: keep the one it is on</t>
+        </is>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>Our record</t>
+        </is>
+      </c>
+      <c r="K27" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Number on two references</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>P28, P46</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="n"/>
+      <c r="D28" s="4" t="n"/>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>1283996</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>Fridge / Fridge Lge / Furniture</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="n"/>
+      <c r="H28" s="4" t="n"/>
+      <c r="I28" s="4" t="inlineStr">
+        <is>
+          <t>one number, two references on our record: keep the one it is on</t>
+        </is>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>Our record</t>
+        </is>
+      </c>
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Number on two references</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>FL02, T0004</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="n"/>
+      <c r="D29" s="4" t="n"/>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>1197839</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>Access &amp; plant / Forklift 2.5T / Other</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="n"/>
+      <c r="H29" s="4" t="n"/>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>one number, two references on our record: keep the one it is on</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>Our record</t>
+        </is>
+      </c>
+      <c r="K29" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Number on two references</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>T0001, T0103</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="n"/>
+      <c r="D30" s="4" t="n"/>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>1211404</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>VMS / vms5</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="n"/>
+      <c r="H30" s="4" t="n"/>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>one number, two references on our record: keep the one it is on</t>
+        </is>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>Our record</t>
+        </is>
+      </c>
+      <c r="K30" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Number on two references</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>P41, P62</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="n"/>
+      <c r="D31" s="4" t="n"/>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>1189908</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>Air conditioner</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="n"/>
+      <c r="H31" s="4" t="n"/>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>one number, two references on our record: keep the one it is on</t>
+        </is>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>Our record</t>
+        </is>
+      </c>
+      <c r="K31" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Number on two references</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>P46, P54</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="n"/>
+      <c r="D32" s="4" t="n"/>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>1328957</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>Fridge</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="n"/>
+      <c r="H32" s="4" t="n"/>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t>one number, two references on our record: keep the one it is on</t>
+        </is>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>Our record</t>
+        </is>
+      </c>
+      <c r="K32" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>Arrival</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>T0002</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="n">
+        <v>26056582</v>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>1264899</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>Lighting towers</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="n"/>
+      <c r="H33" s="5" t="n"/>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>known: the towers went to the Molendinar council yard on 11 Sep, not to site (15 Oct review)</t>
+        </is>
+      </c>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>nobody</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="inlineStr">
+        <is>
+          <t>no (charged over the event)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Arrival</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>T0004</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="n">
+        <v>26056701</v>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>1197839</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Access &amp; plant</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="n"/>
+      <c r="H34" s="2" t="n"/>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>no arrival on our record</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>Andrew</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Arrival</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>T0243</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="n">
+        <v>26091446</v>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>1311144</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>Toilets &amp; amenities</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="n"/>
+      <c r="H35" s="2" t="n"/>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>no arrival on our record</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>Andrew</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>no (charged over the event)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Arrival</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>FL02</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="n">
+        <v>26056701</v>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>1197839</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>docket 14 day(s) before ours</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>Andrew</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Arrival</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>EQ0005</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="n">
+        <v>26122181</v>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>1262224</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>Access &amp; plant</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>docket 10 day(s) before ours</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>Andrew</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Arrival</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>WC06</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="n">
+        <v>26064136</v>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>1195658</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>Toilets &amp; amenities</t>
+        </is>
+      </c>
+      <c r="G38" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="I38" s="4" t="inlineStr">
+        <is>
+          <t>docket 8 day(s) before ours</t>
+        </is>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>Our record</t>
+        </is>
+      </c>
+      <c r="K38" s="4" t="inlineStr">
+        <is>
+          <t>no (charged over the event)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Arrival</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>EQ0001</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="n">
+        <v>26133817</v>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>1220903</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>Access &amp; plant</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>docket 3 day(s) before ours</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>Andrew</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>Arrival</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>T0024</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="n">
+        <v>26064235</v>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>1211968</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>Toilets &amp; amenities</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="H40" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I40" s="5" t="inlineStr">
+        <is>
+          <t>a team reference on its own hire schedule (held out of every charge)</t>
+        </is>
+      </c>
+      <c r="J40" s="5" t="inlineStr">
+        <is>
+          <t>nobody</t>
+        </is>
+      </c>
+      <c r="K40" s="5" t="inlineStr">
+        <is>
+          <t>no (charged over the event)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>Arrival</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>EQ0002</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="n">
+        <v>26141428</v>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>1300290</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>Access &amp; plant</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>docket 1 day(s) before ours</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>Andrew</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Arrival</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>EQ0003</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="n">
+        <v>26141448</v>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>1286482</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>Access &amp; plant</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>docket 1 day(s) before ours</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>Andrew</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Arrival</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>P44</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="n">
+        <v>26088639</v>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>198481</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>Portable buildings</t>
+        </is>
+      </c>
+      <c r="G43" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="H43" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I43" s="4" t="inlineStr">
+        <is>
+          <t>docket 1 day(s) before ours</t>
+        </is>
+      </c>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>Our record</t>
+        </is>
+      </c>
+      <c r="K43" s="4" t="inlineStr">
+        <is>
+          <t>no (charged over the event)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Arrival</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>WC67</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="n">
+        <v>26107560</v>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>172824</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>Toilets &amp; amenities</t>
+        </is>
+      </c>
+      <c r="G44" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="H44" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I44" s="4" t="inlineStr">
+        <is>
+          <t>docket 1 day(s) before ours</t>
+        </is>
+      </c>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>Our record</t>
+        </is>
+      </c>
+      <c r="K44" s="4" t="inlineStr">
+        <is>
+          <t>no (charged over the event)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>Barrier arrival</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>no barrier reference went in that day</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="n">
+        <v>26079322</v>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>ARMORZONMASHTL2</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>WB03 Barrier - Crash Rated Water filled - Armorzone MASH TL2</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="n"/>
+      <c r="H45" s="2" t="n"/>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>a barrier docket with no matching day on our record (WB03 went in 23 Sep on ours; Baseplan has 18 Sep)</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>Andrew</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>VMS arrival</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>VMS09</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="n"/>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>1211404</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>Variable message board</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>docket out 2026-09-07, 2026-10-12; in 2026-10-12</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>Andrew</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>VMS arrival</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>VMS13</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="n"/>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>1191957</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>Variable message board</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>docket out 2026-10-16</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>Andrew</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -42653,160 +45078,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Asset no</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Turned up</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>P&amp;L branch</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>AA</t>
-        </is>
-      </c>
-      <c r="B2" s="6" t="inlineStr">
-        <is>
-          <t>Building 6m</t>
-        </is>
-      </c>
-      <c r="C2" s="6" t="inlineStr">
-        <is>
-          <t>142514</t>
-        </is>
-      </c>
-      <c r="D2" s="6" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="E2" s="6" t="inlineStr">
-        <is>
-          <t>KINP</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>HRP</t>
-        </is>
-      </c>
-      <c r="B3" s="6" t="inlineStr">
-        <is>
-          <t>Building 6m</t>
-        </is>
-      </c>
-      <c r="C3" s="6" t="inlineStr">
-        <is>
-          <t>1189410</t>
-        </is>
-      </c>
-      <c r="D3" s="6" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="E3" s="6" t="inlineStr">
-        <is>
-          <t>KINP</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>FR01</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>Fridge</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>1129733</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>KINP</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>FR02</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>Fridge</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>1157786</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>KINP</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/03_GC500_Delivery_Control/review_25Oct2026_baseplan7/GC500_Baseplan7_vs_Site_25Oct2026.xlsx
+++ b/03_GC500_Delivery_Control/review_25Oct2026_baseplan7/GC500_Baseplan7_vs_Site_25Oct2026.xlsx
@@ -2642,42 +2642,42 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+      <c r="A56" s="3" t="inlineStr">
         <is>
           <t>9961976</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B56" s="3" t="inlineStr">
         <is>
           <t>52</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
+      <c r="C56" s="3" t="inlineStr">
         <is>
           <t>Quantity</t>
         </is>
       </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="D56" s="3" t="inlineStr">
         <is>
           <t>Labour Charge: 2 x $333.12</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>1 on site (GN23); the second is GN20, which Andrew said never came (docket 26102821 says 30 Sep)</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>1 on site (GN23); the second was GN20, which never came to site (Andrew, 22 and 25 Oct)</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
         <is>
           <t>Quantity 1</t>
         </is>
       </c>
-      <c r="G56" s="2" t="n">
+      <c r="G56" s="3" t="n">
         <v>-333.12</v>
       </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>Ask Andrew</t>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>Baseplan</t>
         </is>
       </c>
     </row>
@@ -3232,42 +3232,42 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+      <c r="A71" s="3" t="inlineStr">
         <is>
           <t>9961976</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
+      <c r="B71" s="3" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="C71" s="2" t="inlineStr">
+      <c r="C71" s="3" t="inlineStr">
         <is>
           <t>Remove</t>
         </is>
       </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="D71" s="3" t="inlineStr">
         <is>
           <t>GN20-S01-Generator 365kVA Diesel (1276701) Delivered at $6,260.40</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
-        <is>
-          <t>GN20's 365 kVA: Andrew, 22 Oct 2026, "never came to site 1276701" (record_22Oct2026_gn20_never_came). But Coates' docket 26102821 has it out on 30 Sep, the line is Delivered on that docket, and our record holds a photo filed under GN20/1276701 at 14:14 that day: settle with Andrew before the branch closes the line</t>
-        </is>
-      </c>
-      <c r="F71" s="2" t="inlineStr">
-        <is>
-          <t>Close the line (no charge) if it never came; if it came, an In docket and standby to the day it left</t>
-        </is>
-      </c>
-      <c r="G71" s="2" t="n">
+      <c r="E71" s="3" t="inlineStr">
+        <is>
+          <t>GN20's 365 kVA never came to site (Andrew, 22 Oct 2026, and again 25 Oct: "this never came to site 1276701 Generator 365kVA Diesel"). Coates' docket 26102821 (out 30 Sep) and the line's Delivered status are wrong: the branch reverses the docket</t>
+        </is>
+      </c>
+      <c r="F71" s="3" t="inlineStr">
+        <is>
+          <t>Reverse docket 26102821 and close the line (no charge)</t>
+        </is>
+      </c>
+      <c r="G71" s="3" t="n">
         <v>-6260.4</v>
       </c>
-      <c r="H71" s="2" t="inlineStr">
-        <is>
-          <t>Ask Andrew</t>
+      <c r="H71" s="3" t="inlineStr">
+        <is>
+          <t>Baseplan</t>
         </is>
       </c>
     </row>
@@ -4140,14 +4140,14 @@
         <v>85964.00999999999</v>
       </c>
       <c r="D3" s="6" t="n">
-        <v>3418.4</v>
+        <v>-3175.12</v>
       </c>
       <c r="E3" s="6" t="n">
-        <v>21478.3</v>
+        <v>28071.82</v>
       </c>
       <c r="F3" s="6" t="inlineStr">
         <is>
-          <t>Ask Andrew · Quantity: $-933.12; Ask Andrew · Remove: $-6,260.40; Baseplan · Hours: $15.01; Baseplan · Rate: $3,403.39; Decision · Rate: $28,671.82</t>
+          <t>Ask Andrew · Quantity: $-600.00; Baseplan · Hours: $15.01; Baseplan · Quantity: $-333.12; Baseplan · Rate: $3,403.39; Baseplan · Remove: $-6,260.40; Decision · Rate: $28,671.82</t>
         </is>
       </c>
     </row>
@@ -4208,10 +4208,10 @@
         <v>1022962.43</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>133980.71</v>
+        <v>127387.19</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>12879.9</v>
+        <v>19473.42</v>
       </c>
       <c r="F6" s="6" t="inlineStr"/>
     </row>
@@ -28542,7 +28542,7 @@
       <c r="N241" s="2" t="n"/>
       <c r="O241" s="2" t="inlineStr">
         <is>
-          <t>GN20's 365 kVA: Andrew, 22 Oct 2026, "never came to site 1276701" (record_22Oct2026_gn20_never_came). But Coates' docket 26102821 has it out on 30 Sep, the line is Delivered on that docket, and our record holds a photo filed under GN20/1276701 at 14:14 that day: settle with Andrew before the branch closes the line</t>
+          <t>GN20's 365 kVA never came to site (Andrew, 22 Oct 2026, and again 25 Oct: "this never came to site 1276701 Generator 365kVA Diesel"). Coates' docket 26102821 (out 30 Sep) and the line's Delivered status are wrong: the branch reverses the docket</t>
         </is>
       </c>
     </row>
@@ -41027,7 +41027,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1 large set on site: GN23 (GN20: Andrew said never came; docket 26102821 says 30 Sep)</t>
+          <t>1 large set on site: GN23 (GN20 never came to site; Andrew, 22 and 25 Oct)</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -42241,47 +42241,47 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>Number</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>GN20</t>
         </is>
       </c>
-      <c r="C6" s="2" t="n">
+      <c r="C6" s="4" t="n">
         <v>26102821</v>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>1276701</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>GN20-S01-Generator 365kVA Diesel</t>
         </is>
       </c>
-      <c r="G6" s="2" t="n"/>
-      <c r="H6" s="2" t="n"/>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>not on our record</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>Andrew</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="G6" s="4" t="n"/>
+      <c r="H6" s="4" t="n"/>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>never came to site (Andrew, 22 and 25 Oct): the docket is wrong; the branch reverses it and closes line 6</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>Baseplan</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
         <is>
           <t>no</t>
         </is>

--- a/03_GC500_Delivery_Control/review_25Oct2026_baseplan7/GC500_Baseplan7_vs_Site_25Oct2026.xlsx
+++ b/03_GC500_Delivery_Control/review_25Oct2026_baseplan7/GC500_Baseplan7_vs_Site_25Oct2026.xlsx
@@ -14,12 +14,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Charge lines" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event labour" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fencing (9990776)" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Arrivals vs dockets" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Generators" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="On site, no line" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Branch tie-out" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start dates" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Since 22 Oct" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Generators" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="On site, no line" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Branch tie-out" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start dates" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Since 22 Oct" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -466,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H87"/>
+  <dimension ref="A1:H86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2682,54 +2681,52 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>9961976</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>9968955</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>84, 140</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
         <is>
           <t>Quantity</t>
         </is>
       </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>Transport Charge: 10 x $300.00</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>8 on site (GN03, GN04, GN10, GN25)</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>Quantity 8</t>
-        </is>
-      </c>
-      <c r="G57" s="2" t="n">
-        <v>-600</v>
-      </c>
-      <c r="H57" s="2" t="inlineStr">
-        <is>
-          <t>Ask Andrew</t>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>WC67 FWF: 3 on hire</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>WC67 has 4 FWF on site (arrived Thu 01 Oct)</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>Add 1 FWF (hire line)</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="n"/>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>Baseplan</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>9968955</t>
+          <t>9972648/9990776</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>84, 140</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
@@ -2739,17 +2736,17 @@
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>WC67 FWF: 3 on hire</t>
+          <t>WB07: 0 barriers</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>WC67 has 4 FWF on site (arrived Thu 01 Oct)</t>
+          <t>WB07: 17 on site</t>
         </is>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>Add 1 FWF (hire line)</t>
+          <t>Match the quantity to the site count (barriers are charged from when they go in)</t>
         </is>
       </c>
       <c r="G58" s="3" t="n"/>
@@ -2767,7 +2764,7 @@
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
@@ -2777,12 +2774,12 @@
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>WB07: 0 barriers</t>
+          <t>WB05: 12 barriers</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>WB07: 17 on site</t>
+          <t>WB05: 13 on site</t>
         </is>
       </c>
       <c r="F59" s="3" t="inlineStr">
@@ -2805,7 +2802,7 @@
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
@@ -2815,12 +2812,12 @@
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>WB05: 12 barriers</t>
+          <t>WB04: 13 barriers</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>WB05: 13 on site</t>
+          <t>WB04: 14 on site</t>
         </is>
       </c>
       <c r="F60" s="3" t="inlineStr">
@@ -2838,12 +2835,12 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>9972648/9990776</t>
+          <t>9990776</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
@@ -2853,20 +2850,22 @@
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>WB04: 13 barriers</t>
+          <t>Ped Gates: 32</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>WB04: 14 on site</t>
+          <t>22 on the signed dockets (to 25 Oct)</t>
         </is>
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>Match the quantity to the site count (barriers are charged from when they go in)</t>
-        </is>
-      </c>
-      <c r="G61" s="3" t="n"/>
+          <t>Quantity 22</t>
+        </is>
+      </c>
+      <c r="G61" s="3" t="n">
+        <v>-361.8</v>
+      </c>
       <c r="H61" s="3" t="inlineStr">
         <is>
           <t>Baseplan</t>
@@ -2881,7 +2880,7 @@
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3, 5</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
@@ -2891,21 +2890,21 @@
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>Ped Gates: 32</t>
+          <t>1.8 m security fence 8778 m + with hoarding 110 m</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>22 on the signed dockets (to 25 Oct)</t>
+          <t>13270 m of fence with no scrim on the signed dockets</t>
         </is>
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>Quantity 22</t>
+          <t>Quantity 13160 m on line 3 (keep the 110 m with hoarding on line 5 if it is in the dockets' clean metres)</t>
         </is>
       </c>
       <c r="G62" s="3" t="n">
-        <v>-361.8</v>
+        <v>70813.12</v>
       </c>
       <c r="H62" s="3" t="inlineStr">
         <is>
@@ -2921,7 +2920,7 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>3, 5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
@@ -2931,21 +2930,21 @@
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>1.8 m security fence 8778 m + with hoarding 110 m</t>
+          <t>Fence Relocation: 1520</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>13270 m of fence with no scrim on the signed dockets</t>
+          <t>137.5 on the signed dockets (to 25 Oct); demob relocation still to come</t>
         </is>
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>Quantity 13160 m on line 3 (keep the 110 m with hoarding on line 5 if it is in the dockets' clean metres)</t>
+          <t>Quantity 137.5 to date</t>
         </is>
       </c>
       <c r="G63" s="3" t="n">
-        <v>70813.12</v>
+        <v>-11958.62</v>
       </c>
       <c r="H63" s="3" t="inlineStr">
         <is>
@@ -2961,7 +2960,7 @@
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
@@ -2971,21 +2970,21 @@
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>Fence Relocation: 1520</t>
+          <t>1.8m Fence w/Scrim: 2775</t>
         </is>
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>137.5 on the signed dockets (to 25 Oct); demob relocation still to come</t>
+          <t>3977.5 m of fence with scrim on the signed dockets (to 25 Oct)</t>
         </is>
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>Quantity 137.5 to date</t>
+          <t>Quantity 3977.5</t>
         </is>
       </c>
       <c r="G64" s="3" t="n">
-        <v>-11958.62</v>
+        <v>19432.4</v>
       </c>
       <c r="H64" s="3" t="inlineStr">
         <is>
@@ -3001,7 +3000,7 @@
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
@@ -3011,21 +3010,21 @@
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>1.8m Fence w/Scrim: 2775</t>
+          <t>Barrier - Crowd Control: 2350</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>3977.5 m of fence with scrim on the signed dockets (to 25 Oct)</t>
+          <t>2195 on the signed dockets (to 25 Oct)</t>
         </is>
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>Quantity 3977.5</t>
+          <t>Quantity 2195</t>
         </is>
       </c>
       <c r="G65" s="3" t="n">
-        <v>19432.4</v>
+        <v>-1164.05</v>
       </c>
       <c r="H65" s="3" t="inlineStr">
         <is>
@@ -3041,7 +3040,7 @@
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
@@ -3051,21 +3050,21 @@
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>Barrier - Crowd Control: 2350</t>
+          <t>Barrier - Crowd Control Flat Feet: 220</t>
         </is>
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>2195 on the signed dockets (to 25 Oct)</t>
+          <t>270 on the signed dockets (to 25 Oct)</t>
         </is>
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>Quantity 2195</t>
+          <t>Quantity 270</t>
         </is>
       </c>
       <c r="G66" s="3" t="n">
-        <v>-1164.05</v>
+        <v>375.5</v>
       </c>
       <c r="H66" s="3" t="inlineStr">
         <is>
@@ -3081,7 +3080,7 @@
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
@@ -3091,21 +3090,21 @@
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>Barrier - Crowd Control Flat Feet: 220</t>
+          <t>Demarcation CCB: 4603</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>270 on the signed dockets (to 25 Oct)</t>
+          <t>5062.5 on the signed dockets (to 25 Oct)</t>
         </is>
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>Quantity 270</t>
+          <t>Quantity 5062.5</t>
         </is>
       </c>
       <c r="G67" s="3" t="n">
-        <v>375.5</v>
+        <v>6010.26</v>
       </c>
       <c r="H67" s="3" t="inlineStr">
         <is>
@@ -3121,7 +3120,7 @@
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
@@ -3131,21 +3130,21 @@
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>Demarcation CCB: 4603</t>
+          <t>Shade Cloth: 2775</t>
         </is>
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>5062.5 on the signed dockets (to 25 Oct)</t>
+          <t>3977.5 m of fence with scrim on the signed dockets (to 25 Oct)</t>
         </is>
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>Quantity 5062.5</t>
+          <t>Quantity 3977.5</t>
         </is>
       </c>
       <c r="G68" s="3" t="n">
-        <v>6010.26</v>
+        <v>11267.43</v>
       </c>
       <c r="H68" s="3" t="inlineStr">
         <is>
@@ -3154,92 +3153,92 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="3" t="inlineStr">
-        <is>
-          <t>9990776</t>
-        </is>
-      </c>
-      <c r="B69" s="3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C69" s="3" t="inlineStr">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>our P&amp;L</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>servicing</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
         <is>
           <t>Quantity</t>
         </is>
       </c>
-      <c r="D69" s="3" t="inlineStr">
-        <is>
-          <t>Shade Cloth: 2775</t>
-        </is>
-      </c>
-      <c r="E69" s="3" t="inlineStr">
-        <is>
-          <t>3977.5 m of fence with scrim on the signed dockets (to 25 Oct)</t>
-        </is>
-      </c>
-      <c r="F69" s="3" t="inlineStr">
-        <is>
-          <t>Quantity 3977.5</t>
-        </is>
-      </c>
-      <c r="G69" s="3" t="n">
-        <v>11267.43</v>
-      </c>
-      <c r="H69" s="3" t="inlineStr">
+      <c r="D69" s="4" t="inlineStr">
+        <is>
+          <t>the P&amp;L charges WC31's two 16-pan blocks as sewer-connect cleans (2 x 3 x $260.25 = $1,561.50)</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>they are pumped out every night (servicing tracker), as Baseplan line 142 charges them (2 x 3 x $624.60 = $3,747.60)</t>
+        </is>
+      </c>
+      <c r="F69" s="4" t="inlineStr">
+        <is>
+          <t>Count the 16-pans with the tank pump-outs on Costs (P&amp;L +$2,186.10)</t>
+        </is>
+      </c>
+      <c r="G69" s="4" t="n"/>
+      <c r="H69" s="4" t="inlineStr">
+        <is>
+          <t>Our record</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>9961976</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>Remove</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>GN20-S01-Generator 365kVA Diesel (1276701) Delivered at $6,260.40</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="inlineStr">
+        <is>
+          <t>GN20's 365 kVA never came to site (Andrew, 22 Oct 2026, and again 25 Oct: "this never came to site 1276701 Generator 365kVA Diesel"). Coates' docket 26102821 (out 30 Sep) and the line's Delivered status are wrong: the branch reverses the docket</t>
+        </is>
+      </c>
+      <c r="F70" s="3" t="inlineStr">
+        <is>
+          <t>Reverse docket 26102821 and close the line (no charge)</t>
+        </is>
+      </c>
+      <c r="G70" s="3" t="n">
+        <v>-6260.4</v>
+      </c>
+      <c r="H70" s="3" t="inlineStr">
         <is>
           <t>Baseplan</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="4" t="inlineStr">
-        <is>
-          <t>our P&amp;L</t>
-        </is>
-      </c>
-      <c r="B70" s="4" t="inlineStr">
-        <is>
-          <t>servicing</t>
-        </is>
-      </c>
-      <c r="C70" s="4" t="inlineStr">
-        <is>
-          <t>Quantity</t>
-        </is>
-      </c>
-      <c r="D70" s="4" t="inlineStr">
-        <is>
-          <t>the P&amp;L charges WC31's two 16-pan blocks as sewer-connect cleans (2 x 3 x $260.25 = $1,561.50)</t>
-        </is>
-      </c>
-      <c r="E70" s="4" t="inlineStr">
-        <is>
-          <t>they are pumped out every night (servicing tracker), as Baseplan line 142 charges them (2 x 3 x $624.60 = $3,747.60)</t>
-        </is>
-      </c>
-      <c r="F70" s="4" t="inlineStr">
-        <is>
-          <t>Count the 16-pans with the tank pump-outs on Costs (P&amp;L +$2,186.10)</t>
-        </is>
-      </c>
-      <c r="G70" s="4" t="n"/>
-      <c r="H70" s="4" t="inlineStr">
-        <is>
-          <t>Our record</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>9961976</t>
+          <t>9968955</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>154</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
@@ -3249,21 +3248,21 @@
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>GN20-S01-Generator 365kVA Diesel (1276701) Delivered at $6,260.40</t>
+          <t>PG29 Toilet FWF at $90.07</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>GN20's 365 kVA never came to site (Andrew, 22 Oct 2026, and again 25 Oct: "this never came to site 1276701 Generator 365kVA Diesel"). Coates' docket 26102821 (out 30 Sep) and the line's Delivered status are wrong: the branch reverses the docket</t>
+          <t>PG29 is on its own hire schedule (held out of every charge, Andrew 23 Oct)</t>
         </is>
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>Reverse docket 26102821 and close the line (no charge)</t>
+          <t>Take the line off this contract</t>
         </is>
       </c>
       <c r="G71" s="3" t="n">
-        <v>-6260.4</v>
+        <v>-90.06999999999999</v>
       </c>
       <c r="H71" s="3" t="inlineStr">
         <is>
@@ -3272,80 +3271,80 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="3" t="inlineStr">
+      <c r="A72" s="5" t="inlineStr">
         <is>
           <t>9968955</t>
         </is>
       </c>
-      <c r="B72" s="3" t="inlineStr">
-        <is>
-          <t>154</t>
-        </is>
-      </c>
-      <c r="C72" s="3" t="inlineStr">
-        <is>
-          <t>Remove</t>
-        </is>
-      </c>
-      <c r="D72" s="3" t="inlineStr">
-        <is>
-          <t>PG29 Toilet FWF at $90.07</t>
-        </is>
-      </c>
-      <c r="E72" s="3" t="inlineStr">
-        <is>
-          <t>PG29 is on its own hire schedule (held out of every charge, Andrew 23 Oct)</t>
-        </is>
-      </c>
-      <c r="F72" s="3" t="inlineStr">
-        <is>
-          <t>Take the line off this contract</t>
-        </is>
-      </c>
-      <c r="G72" s="3" t="n">
-        <v>-90.06999999999999</v>
-      </c>
-      <c r="H72" s="3" t="inlineStr">
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="C72" s="5" t="inlineStr">
+        <is>
+          <t>Asset number</t>
+        </is>
+      </c>
+      <c r="D72" s="5" t="inlineStr">
+        <is>
+          <t>WC07 asset 1317643</t>
+        </is>
+      </c>
+      <c r="E72" s="5" t="inlineStr">
+        <is>
+          <t>WC07 on site carries 1002538, 1002566, 1002651, 1002715, 1083300, 1181004, 1192643, 1200595, 1211959, 1212552, 1317626, 1317632, 1317640, 1317641, 1317647, 1317648, 1317649, 1317652, 1317658, 1317743</t>
+        </is>
+      </c>
+      <c r="F72" s="5" t="inlineStr">
+        <is>
+          <t>Correct the number on the line (the site number stands)</t>
+        </is>
+      </c>
+      <c r="G72" s="5" t="n"/>
+      <c r="H72" s="5" t="inlineStr">
         <is>
           <t>Baseplan</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="4" t="inlineStr">
-        <is>
-          <t>9968955</t>
-        </is>
-      </c>
-      <c r="B73" s="4" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="C73" s="4" t="inlineStr">
-        <is>
-          <t>Asset number</t>
-        </is>
-      </c>
-      <c r="D73" s="4" t="inlineStr">
-        <is>
-          <t>WC07 asset 1317643</t>
-        </is>
-      </c>
-      <c r="E73" s="4" t="inlineStr">
-        <is>
-          <t>our record has 1317743; Coates docket 26081411 has 1317643, the same as this line</t>
-        </is>
-      </c>
-      <c r="F73" s="4" t="inlineStr">
-        <is>
-          <t>Check the unit: our 1317743 is probably a keying slip for 1317643 (correct our record, not the line)</t>
-        </is>
-      </c>
-      <c r="G73" s="4" t="n"/>
-      <c r="H73" s="4" t="inlineStr">
-        <is>
-          <t>Our record</t>
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>9961265</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="C73" s="5" t="inlineStr">
+        <is>
+          <t>Start date</t>
+        </is>
+      </c>
+      <c r="D73" s="5" t="inlineStr">
+        <is>
+          <t>VMS22 445T Variable Message Board Senior Premiair: start Wed 21 Oct</t>
+        </is>
+      </c>
+      <c r="E73" s="5" t="inlineStr">
+        <is>
+          <t>on site Thu 22 Oct (Andrew's word (22 Oct) / pin on site)</t>
+        </is>
+      </c>
+      <c r="F73" s="5" t="inlineStr">
+        <is>
+          <t>Start Thu 22 Oct (VMS is charged from when it goes in)</t>
+        </is>
+      </c>
+      <c r="G73" s="5" t="n">
+        <v>53.61</v>
+      </c>
+      <c r="H73" s="5" t="inlineStr">
+        <is>
+          <t>Baseplan</t>
         </is>
       </c>
     </row>
@@ -3357,7 +3356,7 @@
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
@@ -3367,7 +3366,7 @@
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>VMS22 445T Variable Message Board Senior Premiair: start Wed 21 Oct</t>
+          <t>VMS24 450T Variable Message Board Senior: start Mon 19 Oct</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
@@ -3381,7 +3380,7 @@
         </is>
       </c>
       <c r="G74" s="5" t="n">
-        <v>53.61</v>
+        <v>160.83</v>
       </c>
       <c r="H74" s="5" t="inlineStr">
         <is>
@@ -3397,7 +3396,7 @@
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
@@ -3407,21 +3406,21 @@
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>VMS24 450T Variable Message Board Senior: start Mon 19 Oct</t>
+          <t>VMS14 Variable Message Board Junior: start Mon 19 Oct</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
         <is>
-          <t>on site Thu 22 Oct (Andrew's word (22 Oct) / pin on site)</t>
+          <t>on site Fri 16 Oct (recorded on site (load T0158))</t>
         </is>
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>Start Thu 22 Oct (VMS is charged from when it goes in)</t>
+          <t>Start Fri 16 Oct (VMS is charged from when it goes in)</t>
         </is>
       </c>
       <c r="G75" s="5" t="n">
-        <v>160.83</v>
+        <v>-160.83</v>
       </c>
       <c r="H75" s="5" t="inlineStr">
         <is>
@@ -3437,7 +3436,7 @@
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
@@ -3447,7 +3446,7 @@
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>VMS14 Variable Message Board Junior: start Mon 19 Oct</t>
+          <t>VMS15 Variable Message Board Senior: start Mon 19 Oct</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
@@ -3477,7 +3476,7 @@
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
@@ -3487,7 +3486,7 @@
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>VMS15 Variable Message Board Senior: start Mon 19 Oct</t>
+          <t>VMS16 Variable Message Board Senior: start Mon 19 Oct</t>
         </is>
       </c>
       <c r="E77" s="5" t="inlineStr">
@@ -3517,7 +3516,7 @@
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>39</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
@@ -3527,7 +3526,7 @@
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>VMS16 Variable Message Board Senior: start Mon 19 Oct</t>
+          <t>VMS17 Variable Message Board Senior: start Mon 19 Oct</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
@@ -3552,12 +3551,12 @@
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>9961265</t>
+          <t>9961976</t>
         </is>
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>48</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
@@ -3567,22 +3566,20 @@
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>VMS17 Variable Message Board Senior: start Mon 19 Oct</t>
+          <t>GN06 Generator - 60kVA (Diesel): start Mon 19 Oct</t>
         </is>
       </c>
       <c r="E79" s="5" t="inlineStr">
         <is>
-          <t>on site Fri 16 Oct (recorded on site (load T0158))</t>
+          <t>GN06 first on site Thu 15 Oct</t>
         </is>
       </c>
       <c r="F79" s="5" t="inlineStr">
         <is>
-          <t>Start Fri 16 Oct (VMS is charged from when it goes in)</t>
-        </is>
-      </c>
-      <c r="G79" s="5" t="n">
-        <v>-160.83</v>
-      </c>
+          <t>Start Thu 15 Oct (charged from when it goes in)</t>
+        </is>
+      </c>
+      <c r="G79" s="5" t="n"/>
       <c r="H79" s="5" t="inlineStr">
         <is>
           <t>Baseplan</t>
@@ -3592,12 +3589,12 @@
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t>9961976</t>
+          <t>9972648</t>
         </is>
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
@@ -3607,17 +3604,17 @@
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>GN06 Generator - 60kVA (Diesel): start Mon 19 Oct</t>
+          <t>WB03 Barrier - Crash Rated Water filled - Armorzon: start Fri 18 Sep</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
         <is>
-          <t>GN06 first on site Thu 15 Oct</t>
+          <t>WB03 first on site Wed 23 Sep</t>
         </is>
       </c>
       <c r="F80" s="5" t="inlineStr">
         <is>
-          <t>Start Thu 15 Oct (charged from when it goes in)</t>
+          <t>Start Wed 23 Sep (charged from when it goes in)</t>
         </is>
       </c>
       <c r="G80" s="5" t="n"/>
@@ -3628,40 +3625,40 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="5" t="inlineStr">
-        <is>
-          <t>9972648</t>
-        </is>
-      </c>
-      <c r="B81" s="5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C81" s="5" t="inlineStr">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>9987005</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
         <is>
           <t>Start date</t>
         </is>
       </c>
-      <c r="D81" s="5" t="inlineStr">
-        <is>
-          <t>WB03 Barrier - Crash Rated Water filled - Armorzon: start Fri 18 Sep</t>
-        </is>
-      </c>
-      <c r="E81" s="5" t="inlineStr">
-        <is>
-          <t>WB03 first on site Wed 23 Sep</t>
-        </is>
-      </c>
-      <c r="F81" s="5" t="inlineStr">
-        <is>
-          <t>Start Wed 23 Sep (charged from when it goes in)</t>
-        </is>
-      </c>
-      <c r="G81" s="5" t="n"/>
-      <c r="H81" s="5" t="inlineStr">
-        <is>
-          <t>Baseplan</t>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>Supply Forklift 5.0t Diesel: start Mon 05 Oct</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>T0085 first on site Mon 28 Sep (machines changed on some plant references: confirm this unit's day)</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>Start Mon 28 Sep (charged from when it goes in)</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="n"/>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>Ask Andrew</t>
         </is>
       </c>
     </row>
@@ -3673,7 +3670,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -3683,17 +3680,17 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Supply Forklift 5.0t Diesel: start Mon 05 Oct</t>
+          <t>Supply Telehandler Fork Extension 1800mm: start Mon 05 Oct</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>T0085 first on site Mon 28 Sep (machines changed on some plant references: confirm this unit's day)</t>
+          <t>EQ0005 first on site Fri 23 Oct (machines changed on some plant references: confirm this unit's day)</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>Start Mon 28 Sep (charged from when it goes in)</t>
+          <t>Start Fri 23 Oct (charged from when it goes in)</t>
         </is>
       </c>
       <c r="G82" s="2" t="n"/>
@@ -3711,7 +3708,7 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -3721,17 +3718,17 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Supply Telehandler Fork Extension 1800mm: start Mon 05 Oct</t>
+          <t>Forklift Rough Terrain 2.5t 4WD Diesel: start Tue 13 Oct</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>EQ0005 first on site Fri 23 Oct (machines changed on some plant references: confirm this unit's day)</t>
+          <t>T0109 first on site Mon 28 Sep (machines changed on some plant references: confirm this unit's day)</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>Start Fri 23 Oct (charged from when it goes in)</t>
+          <t>Start Mon 28 Sep (charged from when it goes in)</t>
         </is>
       </c>
       <c r="G83" s="2" t="n"/>
@@ -3744,12 +3741,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>9987005</t>
+          <t>9992300</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -3759,17 +3756,17 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Forklift Rough Terrain 2.5t 4WD Diesel: start Tue 13 Oct</t>
+          <t>Scissor Lift With Operator Protection 43ft (13.0M): start Mon 19 Oct</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>T0109 first on site Mon 28 Sep (machines changed on some plant references: confirm this unit's day)</t>
+          <t>EQ0001 first on site Thu 22 Oct (machines changed on some plant references: confirm this unit's day)</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>Start Mon 28 Sep (charged from when it goes in)</t>
+          <t>Start Thu 22 Oct (charged from when it goes in)</t>
         </is>
       </c>
       <c r="G84" s="2" t="n"/>
@@ -3780,40 +3777,40 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="inlineStr">
-        <is>
-          <t>9992300</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
+      <c r="A85" s="5" t="inlineStr">
+        <is>
+          <t>9994954</t>
+        </is>
+      </c>
+      <c r="B85" s="5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C85" s="5" t="inlineStr">
         <is>
           <t>Start date</t>
         </is>
       </c>
-      <c r="D85" s="2" t="inlineStr">
-        <is>
-          <t>Scissor Lift With Operator Protection 43ft (13.0M): start Mon 19 Oct</t>
-        </is>
-      </c>
-      <c r="E85" s="2" t="inlineStr">
-        <is>
-          <t>EQ0001 first on site Thu 22 Oct (machines changed on some plant references: confirm this unit's day)</t>
-        </is>
-      </c>
-      <c r="F85" s="2" t="inlineStr">
-        <is>
-          <t>Start Thu 22 Oct (charged from when it goes in)</t>
-        </is>
-      </c>
-      <c r="G85" s="2" t="n"/>
-      <c r="H85" s="2" t="inlineStr">
-        <is>
-          <t>Ask Andrew</t>
+      <c r="D85" s="5" t="inlineStr">
+        <is>
+          <t>GN26 Generator - 200kVA (Diesel): start Fri 23 Oct</t>
+        </is>
+      </c>
+      <c r="E85" s="5" t="inlineStr">
+        <is>
+          <t>GN? first on site Mon 12 Oct</t>
+        </is>
+      </c>
+      <c r="F85" s="5" t="inlineStr">
+        <is>
+          <t>Start Mon 12 Oct (charged from when it goes in)</t>
+        </is>
+      </c>
+      <c r="G85" s="5" t="n"/>
+      <c r="H85" s="5" t="inlineStr">
+        <is>
+          <t>Baseplan</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3822,7 @@
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
@@ -3835,7 +3832,7 @@
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>GN26 Generator - 200kVA (Diesel): start Fri 23 Oct</t>
+          <t>GN27 Generator - 200kVA (Diesel): start Fri 23 Oct</t>
         </is>
       </c>
       <c r="E86" s="5" t="inlineStr">
@@ -3850,44 +3847,6 @@
       </c>
       <c r="G86" s="5" t="n"/>
       <c r="H86" s="5" t="inlineStr">
-        <is>
-          <t>Baseplan</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="5" t="inlineStr">
-        <is>
-          <t>9994954</t>
-        </is>
-      </c>
-      <c r="B87" s="5" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="C87" s="5" t="inlineStr">
-        <is>
-          <t>Start date</t>
-        </is>
-      </c>
-      <c r="D87" s="5" t="inlineStr">
-        <is>
-          <t>GN27 Generator - 200kVA (Diesel): start Fri 23 Oct</t>
-        </is>
-      </c>
-      <c r="E87" s="5" t="inlineStr">
-        <is>
-          <t>GN? first on site Mon 12 Oct</t>
-        </is>
-      </c>
-      <c r="F87" s="5" t="inlineStr">
-        <is>
-          <t>Start Mon 12 Oct (charged from when it goes in)</t>
-        </is>
-      </c>
-      <c r="G87" s="5" t="n"/>
-      <c r="H87" s="5" t="inlineStr">
         <is>
           <t>Baseplan</t>
         </is>
@@ -3899,162 +3858,6 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Asset no</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Turned up</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>P&amp;L branch</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>AA</t>
-        </is>
-      </c>
-      <c r="B2" s="6" t="inlineStr">
-        <is>
-          <t>Building 6m</t>
-        </is>
-      </c>
-      <c r="C2" s="6" t="inlineStr">
-        <is>
-          <t>142514</t>
-        </is>
-      </c>
-      <c r="D2" s="6" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="E2" s="6" t="inlineStr">
-        <is>
-          <t>KINP</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>HRP</t>
-        </is>
-      </c>
-      <c r="B3" s="6" t="inlineStr">
-        <is>
-          <t>Building 6m</t>
-        </is>
-      </c>
-      <c r="C3" s="6" t="inlineStr">
-        <is>
-          <t>1189410</t>
-        </is>
-      </c>
-      <c r="D3" s="6" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="E3" s="6" t="inlineStr">
-        <is>
-          <t>KINP</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>FR01</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>Fridge</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>1129733</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>KINP</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>FR02</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>Fridge</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>1157786</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>KINP</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4143,11 +3946,11 @@
         <v>-3175.12</v>
       </c>
       <c r="E3" s="6" t="n">
-        <v>28071.82</v>
+        <v>28671.82</v>
       </c>
       <c r="F3" s="6" t="inlineStr">
         <is>
-          <t>Ask Andrew · Quantity: $-600.00; Baseplan · Hours: $15.01; Baseplan · Quantity: $-333.12; Baseplan · Rate: $3,403.39; Baseplan · Remove: $-6,260.40; Decision · Rate: $28,671.82</t>
+          <t>Baseplan · Hours: $15.01; Baseplan · Quantity: $-333.12; Baseplan · Rate: $3,403.39; Baseplan · Remove: $-6,260.40; Decision · Rate: $28,671.82</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4014,7 @@
         <v>127387.19</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>19473.42</v>
+        <v>20073.42</v>
       </c>
       <c r="F6" s="6" t="inlineStr"/>
     </row>
@@ -4220,7 +4023,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10404,7 +10207,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -14221,7 +14024,7 @@
       <c r="N6" s="2" t="n"/>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>nothing on the record carries this line</t>
+          <t>EQ0006 on our record since 25 Oct (Andrew: on site; record_25Oct2026_accessories_laserplane)</t>
         </is>
       </c>
     </row>
@@ -41047,52 +40850,52 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>9961976</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr">
         <is>
           <t>Transport Charge</t>
         </is>
       </c>
-      <c r="D27" s="2" t="n">
+      <c r="D27" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="E27" s="2" t="n">
+      <c r="E27" s="5" t="n">
         <v>300</v>
       </c>
-      <c r="F27" s="2" t="n">
+      <c r="F27" s="5" t="n">
         <v>3000</v>
       </c>
-      <c r="G27" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="H27" s="2" t="n">
-        <v>2400</v>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>4 sets up to 30 kVA (GN03, GN04, GN10, GN25) x 2 legs</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>Baseplan 10, ours 8</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
+      <c r="G27" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="H27" s="5" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>4 sets up to 30 kVA (GN03, GN04, GN10, GN25) x 2 legs + 2 for each swap on our record (GN10)</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>agrees</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="inlineStr">
         <is>
           <t>NVAC-FRI</t>
         </is>
       </c>
-      <c r="L27" s="2" t="inlineStr">
+      <c r="L27" s="5" t="inlineStr">
         <is>
           <t>NVAC</t>
         </is>
@@ -41979,2274 +41782,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K47"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="9" customWidth="1" min="8" max="8"/>
-    <col width="70" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Check</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Our reference</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Coates docket</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Docket date</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Number</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>What</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Ours (turned up)</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Days ours later</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Finding</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Who</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Changes a charge?</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>Number</t>
-        </is>
-      </c>
-      <c r="B2" s="5" t="inlineStr">
-        <is>
-          <t>T0002</t>
-        </is>
-      </c>
-      <c r="C2" s="5" t="n">
-        <v>26056582</v>
-      </c>
-      <c r="D2" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="E2" s="5" t="inlineStr">
-        <is>
-          <t>1264929</t>
-        </is>
-      </c>
-      <c r="F2" s="5" t="inlineStr">
-        <is>
-          <t>LT01 MOLENDINAR Lighting Tower LED Metro</t>
-        </is>
-      </c>
-      <c r="G2" s="5" t="n"/>
-      <c r="H2" s="5" t="n"/>
-      <c r="I2" s="5" t="inlineStr">
-        <is>
-          <t>name only: the towers sit on T0002 on our record (Molendinar council yard, 11 Sep)</t>
-        </is>
-      </c>
-      <c r="J2" s="5" t="inlineStr">
-        <is>
-          <t>nobody</t>
-        </is>
-      </c>
-      <c r="K2" s="5" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>Number</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>T0002</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="n">
-        <v>26056582</v>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>1314284</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>LT02 MOLENDINAR Lighting Tower LED Metro</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="n"/>
-      <c r="H3" s="5" t="n"/>
-      <c r="I3" s="5" t="inlineStr">
-        <is>
-          <t>name only: as LT01</t>
-        </is>
-      </c>
-      <c r="J3" s="5" t="inlineStr">
-        <is>
-          <t>nobody</t>
-        </is>
-      </c>
-      <c r="K3" s="5" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>Number</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>T0002</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="n">
-        <v>26056582</v>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>1264899</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>LT03 MOLENDINAR Lighting Tower LED 76500lm Hybrid</t>
-        </is>
-      </c>
-      <c r="G4" s="5" t="n"/>
-      <c r="H4" s="5" t="n"/>
-      <c r="I4" s="5" t="inlineStr">
-        <is>
-          <t>name only: as LT01</t>
-        </is>
-      </c>
-      <c r="J4" s="5" t="inlineStr">
-        <is>
-          <t>nobody</t>
-        </is>
-      </c>
-      <c r="K4" s="5" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>Number</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>T0002</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="n">
-        <v>26056623</v>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>1188888</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>LT04 MOLENDINAR Lighting Tower LED Metro</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="n"/>
-      <c r="H5" s="5" t="n"/>
-      <c r="I5" s="5" t="inlineStr">
-        <is>
-          <t>name only: as LT01</t>
-        </is>
-      </c>
-      <c r="J5" s="5" t="inlineStr">
-        <is>
-          <t>nobody</t>
-        </is>
-      </c>
-      <c r="K5" s="5" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>Number</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>GN20</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>26102821</v>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>1276701</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>GN20-S01-Generator 365kVA Diesel</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="n"/>
-      <c r="H6" s="4" t="n"/>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>never came to site (Andrew, 22 and 25 Oct): the docket is wrong; the branch reverses it and closes line 6</t>
-        </is>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>Baseplan</t>
-        </is>
-      </c>
-      <c r="K6" s="4" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>Number</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>GN?</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="n">
-        <v>26121298</v>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>1316182</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>GN26 CONCERT Generator - 200kVA (Diesel)</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="n"/>
-      <c r="H7" s="5" t="n"/>
-      <c r="I7" s="5" t="inlineStr">
-        <is>
-          <t>name only: the concert sets sit under their own references on our record</t>
-        </is>
-      </c>
-      <c r="J7" s="5" t="inlineStr">
-        <is>
-          <t>nobody</t>
-        </is>
-      </c>
-      <c r="K7" s="5" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>Number</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>GN?</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="n">
-        <v>26121310</v>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>1316183</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>GN27 CONCERT-Generator - 200kVA (Diesel)</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="n"/>
-      <c r="H8" s="5" t="n"/>
-      <c r="I8" s="5" t="inlineStr">
-        <is>
-          <t>name only: as GN26</t>
-        </is>
-      </c>
-      <c r="J8" s="5" t="inlineStr">
-        <is>
-          <t>nobody</t>
-        </is>
-      </c>
-      <c r="K8" s="5" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>Number</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>LT06</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="n">
-        <v>26139060</v>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>1224791</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>LT05/06-Lighting Tower POD Metro</t>
-        </is>
-      </c>
-      <c r="G9" s="5" t="n"/>
-      <c r="H9" s="5" t="n"/>
-      <c r="I9" s="5" t="inlineStr">
-        <is>
-          <t>name only: the tower pod sits under another reference on our record</t>
-        </is>
-      </c>
-      <c r="J9" s="5" t="inlineStr">
-        <is>
-          <t>nobody</t>
-        </is>
-      </c>
-      <c r="K9" s="5" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Number</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>P05</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="n">
-        <v>26064095</v>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1320150</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>P05 Microwave Oven</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="n"/>
-      <c r="H10" s="2" t="n"/>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>not on our record</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>Andrew</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>Number</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>P05</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>26064095</v>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>1127574</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>P05 Auto Boil</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="n"/>
-      <c r="H11" s="4" t="n"/>
-      <c r="I11" s="4" t="inlineStr">
-        <is>
-          <t>our record calls it Aircon; the docket says boiler</t>
-        </is>
-      </c>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t>Our record</t>
-        </is>
-      </c>
-      <c r="K11" s="4" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>Number</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>CP1</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="n">
-        <v>26064099</v>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>1116687</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>CP1 Refrigerator - Large</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="n"/>
-      <c r="H12" s="2" t="n"/>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>not on our record</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>Andrew</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>Number</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>CP1</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="n">
-        <v>26064099</v>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>119810</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>CP1 Urn</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="n"/>
-      <c r="H13" s="2" t="n"/>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>not on our record</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>Andrew</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>Number</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>P33</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="n">
-        <v>26064103</v>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>1328952</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>P33 Refrigerator - Large</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="n"/>
-      <c r="H14" s="4" t="n"/>
-      <c r="I14" s="4" t="inlineStr">
-        <is>
-          <t>keying slip: our record has 1238952 on P33</t>
-        </is>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>Our record</t>
-        </is>
-      </c>
-      <c r="K14" s="4" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>Number</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>P09</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="n">
-        <v>26076665</v>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>1254390</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>P09 Auto Boil</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="n"/>
-      <c r="H15" s="2" t="n"/>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>not on our record</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>Andrew</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>Number</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>HRP</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="n">
-        <v>26085104</v>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>1189410</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="inlineStr">
-        <is>
-          <t>P36 Portable Building Shell 6.0M x 3.0M - Cyclonic Rated</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="n"/>
-      <c r="H16" s="5" t="n"/>
-      <c r="I16" s="5" t="inlineStr">
-        <is>
-          <t>name only: our record has this shell as HRP (22 Oct review: line 93 is HRP, not P36)</t>
-        </is>
-      </c>
-      <c r="J16" s="5" t="inlineStr">
-        <is>
-          <t>nobody</t>
-        </is>
-      </c>
-      <c r="K16" s="5" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>Number</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>P58</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="n">
-        <v>26088630</v>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>1273656</t>
-        </is>
-      </c>
-      <c r="F17" s="5" t="inlineStr">
-        <is>
-          <t>P44 Portable Building Shell 6.0M x 3.0M - Cyclonic Rated</t>
-        </is>
-      </c>
-      <c r="G17" s="5" t="n"/>
-      <c r="H17" s="5" t="n"/>
-      <c r="I17" s="5" t="inlineStr">
-        <is>
-          <t>name only: our record has this shell as P58 (22 Oct review: line 59 is P58, not P44)</t>
-        </is>
-      </c>
-      <c r="J17" s="5" t="inlineStr">
-        <is>
-          <t>nobody</t>
-        </is>
-      </c>
-      <c r="K17" s="5" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>Number</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>P39</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="n">
-        <v>26094129</v>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>1272737</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>P38 Refrigerator - Large</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="n"/>
-      <c r="H18" s="2" t="n"/>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>on our record under another reference</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>Andrew</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>Number</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>P38</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="n">
-        <v>26094136</v>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>1272755</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>P39 Refrigerator - Large</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="n"/>
-      <c r="H19" s="2" t="n"/>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>on our record under another reference</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>Andrew</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>Number</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>P66</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="n">
-        <v>26126001</v>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>1311990</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>P66 Refrigerator - Large</t>
-        </is>
-      </c>
-      <c r="G20" s="4" t="n"/>
-      <c r="H20" s="4" t="n"/>
-      <c r="I20" s="4" t="inlineStr">
-        <is>
-          <t>keying slip: our record has 131190 on P66</t>
-        </is>
-      </c>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>Our record</t>
-        </is>
-      </c>
-      <c r="K20" s="4" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>Number</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>P51</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="n">
-        <v>26126190</v>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>1328959</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>P46 Refrigerator - Large</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="n"/>
-      <c r="H21" s="2" t="n"/>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>on our record under another reference</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>Andrew</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>Number</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>P46, P54</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="n">
-        <v>26126190</v>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>1328957</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>P51 Refrigerator - Large</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="n"/>
-      <c r="H22" s="2" t="n"/>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>on our record under another reference</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>Andrew</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>Number</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>WC21</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="n">
-        <v>26064136</v>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>1083399</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>WC21 Toilet Portable - Fresh Water Flush</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="n"/>
-      <c r="H23" s="2" t="n"/>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>not on our record</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>Andrew</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>Number</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>WC07</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="n">
-        <v>26081411</v>
-      </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>1317643</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
-          <t>WC07 Toilet Portable - Fresh Water Flush</t>
-        </is>
-      </c>
-      <c r="G24" s="4" t="n"/>
-      <c r="H24" s="4" t="n"/>
-      <c r="I24" s="4" t="inlineStr">
-        <is>
-          <t>keying slip: our record has 1317743 on WC07</t>
-        </is>
-      </c>
-      <c r="J24" s="4" t="inlineStr">
-        <is>
-          <t>Our record</t>
-        </is>
-      </c>
-      <c r="K24" s="4" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>Number</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>WC67</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="n">
-        <v>26107560</v>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>172824</t>
-        </is>
-      </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>WC01 Toilet Portable - Fresh Water Flush</t>
-        </is>
-      </c>
-      <c r="G25" s="5" t="n"/>
-      <c r="H25" s="5" t="n"/>
-      <c r="I25" s="5" t="inlineStr">
-        <is>
-          <t>placed at WC67 on our record; the docket names WC01 (where it was meant to go)</t>
-        </is>
-      </c>
-      <c r="J25" s="5" t="inlineStr">
-        <is>
-          <t>nobody</t>
-        </is>
-      </c>
-      <c r="K25" s="5" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>Number</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr"/>
-      <c r="C26" s="2" t="n">
-        <v>26135873</v>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>1065384</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>Laserplane</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="n"/>
-      <c r="H26" s="2" t="n"/>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>not on our record</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>Andrew</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>Number on two references</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>P26, P46</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="n"/>
-      <c r="D27" s="4" t="n"/>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>1311992</t>
-        </is>
-      </c>
-      <c r="F27" s="4" t="inlineStr">
-        <is>
-          <t>Fridge / Fridge Lge / Furniture</t>
-        </is>
-      </c>
-      <c r="G27" s="4" t="n"/>
-      <c r="H27" s="4" t="n"/>
-      <c r="I27" s="4" t="inlineStr">
-        <is>
-          <t>one number, two references on our record: keep the one it is on</t>
-        </is>
-      </c>
-      <c r="J27" s="4" t="inlineStr">
-        <is>
-          <t>Our record</t>
-        </is>
-      </c>
-      <c r="K27" s="4" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>Number on two references</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>P28, P46</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="n"/>
-      <c r="D28" s="4" t="n"/>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>1283996</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="inlineStr">
-        <is>
-          <t>Fridge / Fridge Lge / Furniture</t>
-        </is>
-      </c>
-      <c r="G28" s="4" t="n"/>
-      <c r="H28" s="4" t="n"/>
-      <c r="I28" s="4" t="inlineStr">
-        <is>
-          <t>one number, two references on our record: keep the one it is on</t>
-        </is>
-      </c>
-      <c r="J28" s="4" t="inlineStr">
-        <is>
-          <t>Our record</t>
-        </is>
-      </c>
-      <c r="K28" s="4" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>Number on two references</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>FL02, T0004</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="n"/>
-      <c r="D29" s="4" t="n"/>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>1197839</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>Access &amp; plant / Forklift 2.5T / Other</t>
-        </is>
-      </c>
-      <c r="G29" s="4" t="n"/>
-      <c r="H29" s="4" t="n"/>
-      <c r="I29" s="4" t="inlineStr">
-        <is>
-          <t>one number, two references on our record: keep the one it is on</t>
-        </is>
-      </c>
-      <c r="J29" s="4" t="inlineStr">
-        <is>
-          <t>Our record</t>
-        </is>
-      </c>
-      <c r="K29" s="4" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>Number on two references</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>T0001, T0103</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="n"/>
-      <c r="D30" s="4" t="n"/>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>1211404</t>
-        </is>
-      </c>
-      <c r="F30" s="4" t="inlineStr">
-        <is>
-          <t>VMS / vms5</t>
-        </is>
-      </c>
-      <c r="G30" s="4" t="n"/>
-      <c r="H30" s="4" t="n"/>
-      <c r="I30" s="4" t="inlineStr">
-        <is>
-          <t>one number, two references on our record: keep the one it is on</t>
-        </is>
-      </c>
-      <c r="J30" s="4" t="inlineStr">
-        <is>
-          <t>Our record</t>
-        </is>
-      </c>
-      <c r="K30" s="4" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>Number on two references</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>P41, P62</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="n"/>
-      <c r="D31" s="4" t="n"/>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t>1189908</t>
-        </is>
-      </c>
-      <c r="F31" s="4" t="inlineStr">
-        <is>
-          <t>Air conditioner</t>
-        </is>
-      </c>
-      <c r="G31" s="4" t="n"/>
-      <c r="H31" s="4" t="n"/>
-      <c r="I31" s="4" t="inlineStr">
-        <is>
-          <t>one number, two references on our record: keep the one it is on</t>
-        </is>
-      </c>
-      <c r="J31" s="4" t="inlineStr">
-        <is>
-          <t>Our record</t>
-        </is>
-      </c>
-      <c r="K31" s="4" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>Number on two references</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>P46, P54</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="n"/>
-      <c r="D32" s="4" t="n"/>
-      <c r="E32" s="4" t="inlineStr">
-        <is>
-          <t>1328957</t>
-        </is>
-      </c>
-      <c r="F32" s="4" t="inlineStr">
-        <is>
-          <t>Fridge</t>
-        </is>
-      </c>
-      <c r="G32" s="4" t="n"/>
-      <c r="H32" s="4" t="n"/>
-      <c r="I32" s="4" t="inlineStr">
-        <is>
-          <t>one number, two references on our record: keep the one it is on</t>
-        </is>
-      </c>
-      <c r="J32" s="4" t="inlineStr">
-        <is>
-          <t>Our record</t>
-        </is>
-      </c>
-      <c r="K32" s="4" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>Arrival</t>
-        </is>
-      </c>
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>T0002</t>
-        </is>
-      </c>
-      <c r="C33" s="5" t="n">
-        <v>26056582</v>
-      </c>
-      <c r="D33" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="E33" s="5" t="inlineStr">
-        <is>
-          <t>1264899</t>
-        </is>
-      </c>
-      <c r="F33" s="5" t="inlineStr">
-        <is>
-          <t>Lighting towers</t>
-        </is>
-      </c>
-      <c r="G33" s="5" t="n"/>
-      <c r="H33" s="5" t="n"/>
-      <c r="I33" s="5" t="inlineStr">
-        <is>
-          <t>known: the towers went to the Molendinar council yard on 11 Sep, not to site (15 Oct review)</t>
-        </is>
-      </c>
-      <c r="J33" s="5" t="inlineStr">
-        <is>
-          <t>nobody</t>
-        </is>
-      </c>
-      <c r="K33" s="5" t="inlineStr">
-        <is>
-          <t>no (charged over the event)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>Arrival</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>T0004</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="n">
-        <v>26056701</v>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>1197839</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>Access &amp; plant</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="n"/>
-      <c r="H34" s="2" t="n"/>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>no arrival on our record</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>Andrew</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>Arrival</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>T0243</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="n">
-        <v>26091446</v>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>1311144</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>Toilets &amp; amenities</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="n"/>
-      <c r="H35" s="2" t="n"/>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>no arrival on our record</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>Andrew</t>
-        </is>
-      </c>
-      <c r="K35" s="2" t="inlineStr">
-        <is>
-          <t>no (charged over the event)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>Arrival</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>FL02</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="n">
-        <v>26056701</v>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>1197839</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>docket 14 day(s) before ours</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>Andrew</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>Arrival</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>EQ0005</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="n">
-        <v>26122181</v>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>1262224</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>Access &amp; plant</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>docket 10 day(s) before ours</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>Andrew</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="4" t="inlineStr">
-        <is>
-          <t>Arrival</t>
-        </is>
-      </c>
-      <c r="B38" s="4" t="inlineStr">
-        <is>
-          <t>WC06</t>
-        </is>
-      </c>
-      <c r="C38" s="4" t="n">
-        <v>26064136</v>
-      </c>
-      <c r="D38" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="E38" s="4" t="inlineStr">
-        <is>
-          <t>1195658</t>
-        </is>
-      </c>
-      <c r="F38" s="4" t="inlineStr">
-        <is>
-          <t>Toilets &amp; amenities</t>
-        </is>
-      </c>
-      <c r="G38" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="H38" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="I38" s="4" t="inlineStr">
-        <is>
-          <t>docket 8 day(s) before ours</t>
-        </is>
-      </c>
-      <c r="J38" s="4" t="inlineStr">
-        <is>
-          <t>Our record</t>
-        </is>
-      </c>
-      <c r="K38" s="4" t="inlineStr">
-        <is>
-          <t>no (charged over the event)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>Arrival</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>EQ0001</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="n">
-        <v>26133817</v>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>1220903</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>Access &amp; plant</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>docket 3 day(s) before ours</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>Andrew</t>
-        </is>
-      </c>
-      <c r="K39" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>Arrival</t>
-        </is>
-      </c>
-      <c r="B40" s="5" t="inlineStr">
-        <is>
-          <t>T0024</t>
-        </is>
-      </c>
-      <c r="C40" s="5" t="n">
-        <v>26064235</v>
-      </c>
-      <c r="D40" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="E40" s="5" t="inlineStr">
-        <is>
-          <t>1211968</t>
-        </is>
-      </c>
-      <c r="F40" s="5" t="inlineStr">
-        <is>
-          <t>Toilets &amp; amenities</t>
-        </is>
-      </c>
-      <c r="G40" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-26</t>
-        </is>
-      </c>
-      <c r="H40" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="I40" s="5" t="inlineStr">
-        <is>
-          <t>a team reference on its own hire schedule (held out of every charge)</t>
-        </is>
-      </c>
-      <c r="J40" s="5" t="inlineStr">
-        <is>
-          <t>nobody</t>
-        </is>
-      </c>
-      <c r="K40" s="5" t="inlineStr">
-        <is>
-          <t>no (charged over the event)</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>Arrival</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>EQ0002</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="n">
-        <v>26141428</v>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>1300290</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>Access &amp; plant</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>docket 1 day(s) before ours</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>Andrew</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>Arrival</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>EQ0003</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="n">
-        <v>26141448</v>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>1286482</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>Access &amp; plant</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>docket 1 day(s) before ours</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>Andrew</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="4" t="inlineStr">
-        <is>
-          <t>Arrival</t>
-        </is>
-      </c>
-      <c r="B43" s="4" t="inlineStr">
-        <is>
-          <t>P44</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="n">
-        <v>26088639</v>
-      </c>
-      <c r="D43" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="E43" s="4" t="inlineStr">
-        <is>
-          <t>198481</t>
-        </is>
-      </c>
-      <c r="F43" s="4" t="inlineStr">
-        <is>
-          <t>Portable buildings</t>
-        </is>
-      </c>
-      <c r="G43" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="H43" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I43" s="4" t="inlineStr">
-        <is>
-          <t>docket 1 day(s) before ours</t>
-        </is>
-      </c>
-      <c r="J43" s="4" t="inlineStr">
-        <is>
-          <t>Our record</t>
-        </is>
-      </c>
-      <c r="K43" s="4" t="inlineStr">
-        <is>
-          <t>no (charged over the event)</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="4" t="inlineStr">
-        <is>
-          <t>Arrival</t>
-        </is>
-      </c>
-      <c r="B44" s="4" t="inlineStr">
-        <is>
-          <t>WC67</t>
-        </is>
-      </c>
-      <c r="C44" s="4" t="n">
-        <v>26107560</v>
-      </c>
-      <c r="D44" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="E44" s="4" t="inlineStr">
-        <is>
-          <t>172824</t>
-        </is>
-      </c>
-      <c r="F44" s="4" t="inlineStr">
-        <is>
-          <t>Toilets &amp; amenities</t>
-        </is>
-      </c>
-      <c r="G44" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="H44" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I44" s="4" t="inlineStr">
-        <is>
-          <t>docket 1 day(s) before ours</t>
-        </is>
-      </c>
-      <c r="J44" s="4" t="inlineStr">
-        <is>
-          <t>Our record</t>
-        </is>
-      </c>
-      <c r="K44" s="4" t="inlineStr">
-        <is>
-          <t>no (charged over the event)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>Barrier arrival</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>no barrier reference went in that day</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="n">
-        <v>26079322</v>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>ARMORZONMASHTL2</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>WB03 Barrier - Crash Rated Water filled - Armorzone MASH TL2</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="n"/>
-      <c r="H45" s="2" t="n"/>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>a barrier docket with no matching day on our record (WB03 went in 23 Sep on ours; Baseplan has 18 Sep)</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>Andrew</t>
-        </is>
-      </c>
-      <c r="K45" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>VMS arrival</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>VMS09</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="n"/>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>1211404</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>Variable message board</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>docket out 2026-09-07, 2026-10-12; in 2026-10-12</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>Andrew</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>VMS arrival</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>VMS13</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="n"/>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>1191957</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>Variable message board</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>docket out 2026-10-16</t>
-        </is>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>Andrew</t>
-        </is>
-      </c>
-      <c r="K47" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -45078,4 +42613,160 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Asset no</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Turned up</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>P&amp;L branch</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>Building 6m</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>142514</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E2" s="6" t="inlineStr">
+        <is>
+          <t>KINP</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>HRP</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>Building 6m</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>1189410</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>KINP</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>FR01</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Fridge</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>1129733</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>KINP</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>FR02</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Fridge</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>1157786</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>KINP</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/03_GC500_Delivery_Control/review_25Oct2026_baseplan7/GC500_Baseplan7_vs_Site_25Oct2026.xlsx
+++ b/03_GC500_Delivery_Control/review_25Oct2026_baseplan7/GC500_Baseplan7_vs_Site_25Oct2026.xlsx
@@ -2648,7 +2648,7 @@
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>55</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
@@ -2658,21 +2658,21 @@
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>Labour Charge: 2 x $333.12</t>
+          <t>Transport Charge: 2 x $600.00</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>1 on site (GN23); the second was GN20, which never came to site (Andrew, 22 and 25 Oct)</t>
+          <t>4 on site (GN20, GN23 x 2 legs)</t>
         </is>
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>Quantity 1</t>
+          <t>Quantity 4</t>
         </is>
       </c>
       <c r="G56" s="3" t="n">
-        <v>-333.12</v>
+        <v>1200</v>
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
@@ -3193,12 +3193,12 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>9961976</t>
+          <t>9968955</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>154</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
@@ -3208,21 +3208,21 @@
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>GN20-S01-Generator 365kVA Diesel (1276701) Delivered at $6,260.40</t>
+          <t>PG29 Toilet FWF at $90.07</t>
         </is>
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>GN20's 365 kVA never came to site (Andrew, 22 Oct 2026, and again 25 Oct: "this never came to site 1276701 Generator 365kVA Diesel"). Coates' docket 26102821 (out 30 Sep) and the line's Delivered status are wrong: the branch reverses the docket</t>
+          <t>PG29 is on its own hire schedule (held out of every charge, Andrew 23 Oct)</t>
         </is>
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>Reverse docket 26102821 and close the line (no charge)</t>
+          <t>Take the line off this contract</t>
         </is>
       </c>
       <c r="G70" s="3" t="n">
-        <v>-6260.4</v>
+        <v>-90.06999999999999</v>
       </c>
       <c r="H70" s="3" t="inlineStr">
         <is>
@@ -3231,80 +3231,78 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="3" t="inlineStr">
+      <c r="A71" s="5" t="inlineStr">
         <is>
           <t>9968955</t>
         </is>
       </c>
-      <c r="B71" s="3" t="inlineStr">
-        <is>
-          <t>154</t>
-        </is>
-      </c>
-      <c r="C71" s="3" t="inlineStr">
-        <is>
-          <t>Remove</t>
-        </is>
-      </c>
-      <c r="D71" s="3" t="inlineStr">
-        <is>
-          <t>PG29 Toilet FWF at $90.07</t>
-        </is>
-      </c>
-      <c r="E71" s="3" t="inlineStr">
-        <is>
-          <t>PG29 is on its own hire schedule (held out of every charge, Andrew 23 Oct)</t>
-        </is>
-      </c>
-      <c r="F71" s="3" t="inlineStr">
-        <is>
-          <t>Take the line off this contract</t>
-        </is>
-      </c>
-      <c r="G71" s="3" t="n">
-        <v>-90.06999999999999</v>
-      </c>
-      <c r="H71" s="3" t="inlineStr">
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>Asset number</t>
+        </is>
+      </c>
+      <c r="D71" s="5" t="inlineStr">
+        <is>
+          <t>WC07 asset 1317643</t>
+        </is>
+      </c>
+      <c r="E71" s="5" t="inlineStr">
+        <is>
+          <t>WC07 on site carries 1002538, 1002566, 1002651, 1002715, 1083300, 1181004, 1192643, 1200595, 1211959, 1212552, 1317626, 1317632, 1317640, 1317641, 1317647, 1317648, 1317649, 1317652, 1317658, 1317743</t>
+        </is>
+      </c>
+      <c r="F71" s="5" t="inlineStr">
+        <is>
+          <t>Correct the number on the line (the site number stands)</t>
+        </is>
+      </c>
+      <c r="G71" s="5" t="n"/>
+      <c r="H71" s="5" t="inlineStr">
         <is>
           <t>Baseplan</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="5" t="inlineStr">
-        <is>
-          <t>9968955</t>
-        </is>
-      </c>
-      <c r="B72" s="5" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="C72" s="5" t="inlineStr">
-        <is>
-          <t>Asset number</t>
-        </is>
-      </c>
-      <c r="D72" s="5" t="inlineStr">
-        <is>
-          <t>WC07 asset 1317643</t>
-        </is>
-      </c>
-      <c r="E72" s="5" t="inlineStr">
-        <is>
-          <t>WC07 on site carries 1002538, 1002566, 1002651, 1002715, 1083300, 1181004, 1192643, 1200595, 1211959, 1212552, 1317626, 1317632, 1317640, 1317641, 1317647, 1317648, 1317649, 1317652, 1317658, 1317743</t>
-        </is>
-      </c>
-      <c r="F72" s="5" t="inlineStr">
-        <is>
-          <t>Correct the number on the line (the site number stands)</t>
-        </is>
-      </c>
-      <c r="G72" s="5" t="n"/>
-      <c r="H72" s="5" t="inlineStr">
-        <is>
-          <t>Baseplan</t>
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>our record</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>GN20</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>Not on site</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr">
+        <is>
+          <t>GN20 365 kVA (1276701) is Delivered from Wed 30 Sep on Baseplan, as it should be</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t>our record deleted GN20 on 20 Oct and the P&amp;L stopped charging it on 22 Oct (v11.18)</t>
+        </is>
+      </c>
+      <c r="F72" s="4" t="inlineStr">
+        <is>
+          <t>Put it back on our record and the P&amp;L (the page will not re-use a deleted reference)</t>
+        </is>
+      </c>
+      <c r="G72" s="4" t="n"/>
+      <c r="H72" s="4" t="inlineStr">
+        <is>
+          <t>Our record</t>
         </is>
       </c>
     </row>
@@ -3943,14 +3941,14 @@
         <v>85964.00999999999</v>
       </c>
       <c r="D3" s="6" t="n">
-        <v>-3175.12</v>
+        <v>4618.4</v>
       </c>
       <c r="E3" s="6" t="n">
         <v>28671.82</v>
       </c>
       <c r="F3" s="6" t="inlineStr">
         <is>
-          <t>Baseplan · Hours: $15.01; Baseplan · Quantity: $-333.12; Baseplan · Rate: $3,403.39; Baseplan · Remove: $-6,260.40; Decision · Rate: $28,671.82</t>
+          <t>Baseplan · Hours: $15.01; Baseplan · Quantity: $1,200.00; Baseplan · Rate: $3,403.39; Decision · Rate: $28,671.82</t>
         </is>
       </c>
     </row>
@@ -4011,7 +4009,7 @@
         <v>1022962.43</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>127387.19</v>
+        <v>135180.71</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>20073.42</v>
@@ -28341,11 +28339,19 @@
         </is>
       </c>
       <c r="L241" s="2" t="n"/>
-      <c r="M241" s="2" t="n"/>
-      <c r="N241" s="2" t="n"/>
+      <c r="M241" s="2" t="inlineStr">
+        <is>
+          <t>GN20</t>
+        </is>
+      </c>
+      <c r="N241" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
       <c r="O241" s="2" t="inlineStr">
         <is>
-          <t>GN20's 365 kVA never came to site (Andrew, 22 Oct 2026, and again 25 Oct: "this never came to site 1276701 Generator 365kVA Diesel"). Coates' docket 26102821 (out 30 Sep) and the line's Delivered status are wrong: the branch reverses the docket</t>
+          <t>GN20 on site from Wed 30 Sep (Andrew, 25 Oct: "the gn20 is here"); the line stands. Our record deleted the reference on 20 Oct and the P&amp;L dropped it on 22 Oct: both to be put back</t>
         </is>
       </c>
     </row>
@@ -40798,52 +40804,52 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>9961976</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>52</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="C26" s="5" t="inlineStr">
         <is>
           <t>Labour Charge</t>
         </is>
       </c>
-      <c r="D26" s="2" t="n">
+      <c r="D26" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="E26" s="2" t="n">
+      <c r="E26" s="5" t="n">
         <v>333.12</v>
       </c>
-      <c r="F26" s="2" t="n">
+      <c r="F26" s="5" t="n">
         <v>666.24</v>
       </c>
-      <c r="G26" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H26" s="2" t="n">
-        <v>333.12</v>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>1 large set on site: GN23 (GN20 never came to site; Andrew, 22 and 25 Oct)</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>Baseplan 2, ours 1</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
+      <c r="G26" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H26" s="5" t="n">
+        <v>666.24</v>
+      </c>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>2 large sets on site: GN20, GN23</t>
+        </is>
+      </c>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>agrees</t>
+        </is>
+      </c>
+      <c r="K26" s="5" t="inlineStr">
         <is>
           <t>NVAC-INS</t>
         </is>
       </c>
-      <c r="L26" s="2" t="inlineStr">
+      <c r="L26" s="5" t="inlineStr">
         <is>
           <t>NVAC</t>
         </is>
@@ -40954,52 +40960,52 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="inlineStr">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>9961976</t>
         </is>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>Transport Charge</t>
         </is>
       </c>
-      <c r="D29" s="5" t="n">
+      <c r="D29" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E29" s="5" t="n">
+      <c r="E29" s="2" t="n">
         <v>600</v>
       </c>
-      <c r="F29" s="5" t="n">
+      <c r="F29" s="2" t="n">
         <v>1200</v>
       </c>
-      <c r="G29" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="H29" s="5" t="n">
-        <v>1200</v>
-      </c>
-      <c r="I29" s="5" t="inlineStr">
-        <is>
-          <t>1 large set x 2 legs</t>
-        </is>
-      </c>
-      <c r="J29" s="5" t="inlineStr">
-        <is>
-          <t>agrees</t>
-        </is>
-      </c>
-      <c r="K29" s="5" t="inlineStr">
+      <c r="G29" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="H29" s="2" t="n">
+        <v>2400</v>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>2 large sets (GN20, GN23) x 2 legs</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>Baseplan 2, ours 4</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>NVAC-FRI</t>
         </is>
       </c>
-      <c r="L29" s="5" t="inlineStr">
+      <c r="L29" s="2" t="inlineStr">
         <is>
           <t>NVAC</t>
         </is>
@@ -41874,10 +41880,14 @@
           <t>1276701</t>
         </is>
       </c>
-      <c r="E2" s="6" t="n"/>
+      <c r="E2" s="6" t="inlineStr">
+        <is>
+          <t>GN20</t>
+        </is>
+      </c>
       <c r="F2" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G2" s="6" t="inlineStr">
@@ -41889,7 +41899,11 @@
         <v>6260.4</v>
       </c>
       <c r="I2" s="6" t="n"/>
-      <c r="J2" s="6" t="n"/>
+      <c r="J2" s="6" t="inlineStr">
+        <is>
+          <t>off the P&amp;L since 22 Oct: to be put back</t>
+        </is>
+      </c>
       <c r="K2" s="6" t="inlineStr">
         <is>
           <t>NVAC-HIR</t>

--- a/03_GC500_Delivery_Control/review_25Oct2026_baseplan7/GC500_Baseplan7_vs_Site_25Oct2026.xlsx
+++ b/03_GC500_Delivery_Control/review_25Oct2026_baseplan7/GC500_Baseplan7_vs_Site_25Oct2026.xlsx
@@ -1888,7 +1888,7 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
@@ -1898,21 +1898,21 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>GN19-Generator - Diesel - 80kVA DEL AS 6: $1,254.50</t>
+          <t>GN20-S01-Generator 365kVA Diesel: $6,260.40</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>the P&amp;L charges $965.01 (Street Rate Card 2026 · Generator 60 kVA · published Standby Rate before 23 Oct, from the day it turned up Mon 19 Oct)</t>
+          <t>the P&amp;L charges $6,840.83 (Street Rate Card 2026 · Generator 315 kVA · next size down from 350 kVA · published Standby Rate before 23 Oct, from the day it turned up Wed 30 Sep)</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>Rate $965.01</t>
+          <t>Rate $6,840.83</t>
         </is>
       </c>
       <c r="G37" s="3" t="n">
-        <v>-289.49</v>
+        <v>580.4299999999999</v>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -1938,21 +1938,21 @@
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>GN23-Generator - Sync - Hardwire Only 15: $2,412.54</t>
+          <t>GN19-Generator - Diesel - 80kVA DEL AS 6: $1,254.50</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>the P&amp;L charges $3,886.83 (Street Rate Card 2026 · Generator 150 kVA · published Standby Rate before 23 Oct, from the day it turned up Wed 30 Sep)</t>
+          <t>the P&amp;L charges $965.01 (Street Rate Card 2026 · Generator 60 kVA · published Standby Rate before 23 Oct, from the day it turned up Mon 19 Oct)</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>Rate $3,886.83</t>
+          <t>Rate $965.01</t>
         </is>
       </c>
       <c r="G38" s="3" t="n">
-        <v>1474.29</v>
+        <v>-289.49</v>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -1978,21 +1978,21 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>GN03-Generator - 30kVA (Diesel): $1,132.28</t>
+          <t>GN23-Generator - Sync - Hardwire Only 15: $2,412.54</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>the P&amp;L charges $1,981.47 (Street Rate Card 2026 · Generator 30 kVA · published Standby Rate before 23 Oct, from the day it turned up Thu 01 Oct)</t>
+          <t>the P&amp;L charges $3,886.83 (Street Rate Card 2026 · Generator 150 kVA · published Standby Rate before 23 Oct, from the day it turned up Wed 30 Sep)</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>Rate $1,981.47</t>
+          <t>Rate $3,886.83</t>
         </is>
       </c>
       <c r="G39" s="3" t="n">
-        <v>849.1900000000001</v>
+        <v>1474.29</v>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -2018,21 +2018,21 @@
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>GN18-Generator - 60kVA (Diesel): $2,187.36</t>
+          <t>GN03-Generator - 30kVA (Diesel): $1,132.28</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>the P&amp;L charges $2,005.07 (Street Rate Card 2026 · Generator 50 kVA · published Standby Rate before 23 Oct, from the day it turned up Wed 07 Oct)</t>
+          <t>the P&amp;L charges $1,981.47 (Street Rate Card 2026 · Generator 30 kVA · published Standby Rate before 23 Oct, from the day it turned up Thu 01 Oct)</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>Rate $2,005.07</t>
+          <t>Rate $1,981.47</t>
         </is>
       </c>
       <c r="G40" s="3" t="n">
-        <v>-182.29</v>
+        <v>849.1900000000001</v>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
@@ -2048,7 +2048,7 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
@@ -2058,21 +2058,21 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>GN04-Generator - 30kVA (Diesel): $919.97</t>
+          <t>GN18-Generator - 60kVA (Diesel): $2,187.36</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>the P&amp;L charges $707.67 (Street Rate Card 2026 · Generator 30 kVA · published Standby Rate before 23 Oct, from the day it turned up Mon 19 Oct)</t>
+          <t>the P&amp;L charges $2,005.07 (Street Rate Card 2026 · Generator 50 kVA · published Standby Rate before 23 Oct, from the day it turned up Wed 07 Oct)</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>Rate $707.67</t>
+          <t>Rate $2,005.07</t>
         </is>
       </c>
       <c r="G41" s="3" t="n">
-        <v>-212.3</v>
+        <v>-182.29</v>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -2098,21 +2098,21 @@
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>G10- Generator - 60kVA (Diesel): $1,142.96</t>
+          <t>GN04-Generator - 30kVA (Diesel): $919.97</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>the P&amp;L charges $611.16 (Street Rate Card 2026 · Generator 20 kVA · published Standby Rate before 23 Oct, from the day it turned up Mon 19 Oct)</t>
+          <t>the P&amp;L charges $707.67 (Street Rate Card 2026 · Generator 30 kVA · published Standby Rate before 23 Oct, from the day it turned up Mon 19 Oct)</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>Rate $611.16</t>
+          <t>Rate $707.67</t>
         </is>
       </c>
       <c r="G42" s="3" t="n">
-        <v>-531.8</v>
+        <v>-212.3</v>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
@@ -2138,21 +2138,21 @@
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>GN01-Generator - 60kVA (Diesel): $1,544.00</t>
+          <t>G10- Generator - 60kVA (Diesel): $1,142.96</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>the P&amp;L charges $2,991.52 (Street Rate Card 2026 · Generator 60 kVA · published Standby Rate before 23 Oct, from the day it turned up Mon 28 Sep)</t>
+          <t>the P&amp;L charges $611.16 (Street Rate Card 2026 · Generator 20 kVA · published Standby Rate before 23 Oct, from the day it turned up Mon 19 Oct)</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>Rate $2,991.52</t>
+          <t>Rate $611.16</t>
         </is>
       </c>
       <c r="G43" s="3" t="n">
-        <v>1447.52</v>
+        <v>-531.8</v>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
@@ -2168,7 +2168,7 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -2178,21 +2178,21 @@
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>GN25-Generator - 20kVA (Diesel): $855.63</t>
+          <t>GN01-Generator - 60kVA (Diesel): $1,544.00</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>the P&amp;L charges $611.16 (Street Rate Card 2026 · Generator 20 kVA · published Standby Rate before 23 Oct, from the day it turned up Mon 19 Oct)</t>
+          <t>the P&amp;L charges $2,991.52 (Street Rate Card 2026 · Generator 60 kVA · published Standby Rate before 23 Oct, from the day it turned up Mon 28 Sep)</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>Rate $611.16</t>
+          <t>Rate $2,991.52</t>
         </is>
       </c>
       <c r="G44" s="3" t="n">
-        <v>-244.47</v>
+        <v>1447.52</v>
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
@@ -2218,21 +2218,21 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>LT05/06-Lighting Tower POD Metro: $385.98</t>
+          <t>GN25-Generator - 20kVA (Diesel): $855.63</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>a light tower is charged for the three event days at the card ($64.33 a day = $192.99), never its days on site (branch rule)</t>
+          <t>the P&amp;L charges $611.16 (Street Rate Card 2026 · Generator 20 kVA · published Standby Rate before 23 Oct, from the day it turned up Mon 19 Oct)</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>Rate $192.99</t>
+          <t>Rate $611.16</t>
         </is>
       </c>
       <c r="G45" s="3" t="n">
-        <v>-192.99</v>
+        <v>-244.47</v>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
@@ -2248,7 +2248,7 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -2281,82 +2281,82 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+      <c r="A47" s="3" t="inlineStr">
         <is>
           <t>9961976</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>Rate</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>LT05/06-Lighting Tower POD Metro: $385.98</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>a light tower is charged for the three event days at the card ($64.33 a day = $192.99), never its days on site (branch rule)</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>Rate $192.99</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="n">
+        <v>-192.99</v>
+      </c>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>Baseplan</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>9961976</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>21, 25, 26, 27, 31, 34, 35</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
         <is>
           <t>Rate</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Coates forklifts at $0 (COATES Forklift 3.0t Contain, COATES Forklift Rough Terrai, COATES Forklift Rough Terrai, ...)</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>the P&amp;L charges them from the card: $28,671.82 of NVAC revenue</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>Andrew to say: Coates own (no charge, the P&amp;L comes down) or charged to the V8s (rates on the lines)</t>
         </is>
       </c>
-      <c r="G47" s="2" t="n">
+      <c r="G48" s="2" t="n">
         <v>28671.82</v>
       </c>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>Decision</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="3" t="inlineStr">
-        <is>
-          <t>9961976</t>
-        </is>
-      </c>
-      <c r="B48" s="3" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="C48" s="3" t="inlineStr">
-        <is>
-          <t>Rate</t>
-        </is>
-      </c>
-      <c r="D48" s="3" t="inlineStr">
-        <is>
-          <t>GN21-Generator - 60kVA (Diesel): $868.50</t>
-        </is>
-      </c>
-      <c r="E48" s="3" t="inlineStr">
-        <is>
-          <t>the P&amp;L charges $2,798.52 (Street Rate Card 2026 · Generator 60 kVA · published Standby Rate before 23 Oct, from the day it turned up Wed 30 Sep)</t>
-        </is>
-      </c>
-      <c r="F48" s="3" t="inlineStr">
-        <is>
-          <t>Rate $2,798.52</t>
-        </is>
-      </c>
-      <c r="G48" s="3" t="n">
-        <v>1930.02</v>
-      </c>
-      <c r="H48" s="3" t="inlineStr">
-        <is>
-          <t>Baseplan</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>38</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
@@ -2378,21 +2378,21 @@
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>GN13 Generator - 60kVA (Diesel) DEL AS 4: $1,406.72</t>
+          <t>GN21-Generator - 60kVA (Diesel): $868.50</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>the P&amp;L charges $1,494.68 (Street Rate Card 2026 · Generator 45 kVA · published Standby Rate before 23 Oct, from the day it turned up Mon 12 Oct)</t>
+          <t>the P&amp;L charges $2,798.52 (Street Rate Card 2026 · Generator 60 kVA · published Standby Rate before 23 Oct, from the day it turned up Wed 30 Sep)</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>Rate $1,494.68</t>
+          <t>Rate $2,798.52</t>
         </is>
       </c>
       <c r="G49" s="3" t="n">
-        <v>87.95999999999999</v>
+        <v>1930.02</v>
       </c>
       <c r="H49" s="3" t="inlineStr">
         <is>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>44</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -2418,21 +2418,21 @@
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>GN06 Generator - 60kVA (Diesel): $1,184.82</t>
+          <t>GN13 Generator - 60kVA (Diesel) DEL AS 4: $1,406.72</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>the P&amp;L charges $1,275.95 (Street Rate Card 2026 · Generator 50 kVA · published Standby Rate before 23 Oct, from the day it turned up Thu 15 Oct)</t>
+          <t>the P&amp;L charges $1,494.68 (Street Rate Card 2026 · Generator 45 kVA · published Standby Rate before 23 Oct, from the day it turned up Mon 12 Oct)</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>Rate $1,275.95</t>
+          <t>Rate $1,494.68</t>
         </is>
       </c>
       <c r="G50" s="3" t="n">
-        <v>91.13</v>
+        <v>87.95999999999999</v>
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
@@ -2448,7 +2448,7 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>48</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
@@ -2458,21 +2458,21 @@
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>GN24-Generator - 60kVA (Diesel) - Traile: $984.33</t>
+          <t>GN06 Generator - 60kVA (Diesel): $1,184.82</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>the P&amp;L charges $965.01 (Street Rate Card 2026 · Generator 60 kVA · published Standby Rate before 23 Oct, from the day it turned up Mon 19 Oct)</t>
+          <t>the P&amp;L charges $1,275.95 (Street Rate Card 2026 · Generator 50 kVA · published Standby Rate before 23 Oct, from the day it turned up Thu 15 Oct)</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>Rate $965.01</t>
+          <t>Rate $1,275.95</t>
         </is>
       </c>
       <c r="G51" s="3" t="n">
-        <v>-19.32</v>
+        <v>91.13</v>
       </c>
       <c r="H51" s="3" t="inlineStr">
         <is>
@@ -2483,12 +2483,12 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>9990776</t>
+          <t>9961976</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>49</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
@@ -2498,21 +2498,21 @@
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>Barrier - Crowd Control Flat Feet: $7.51</t>
+          <t>GN24-Generator - 60kVA (Diesel) - Traile: $984.33</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>the card rate the P&amp;L charges is $9.65</t>
+          <t>the P&amp;L charges $965.01 (Street Rate Card 2026 · Generator 60 kVA · published Standby Rate before 23 Oct, from the day it turned up Mon 19 Oct)</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>Rate $9.65</t>
+          <t>Rate $965.01</t>
         </is>
       </c>
       <c r="G52" s="3" t="n">
-        <v>578.1</v>
+        <v>-19.32</v>
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
@@ -2523,12 +2523,12 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>9994954</t>
+          <t>9990776</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
@@ -2538,21 +2538,21 @@
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>GN26 Generator - 200kVA (Diesel): $2,005.08</t>
+          <t>Barrier - Crowd Control Flat Feet: $7.51</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>the P&amp;L charges $3,098.74 (Street Rate Card 2026 · Generator 200 kVA · published Standby Rate before 23 Oct, from the day it turned up Mon 12 Oct)</t>
+          <t>the card rate the P&amp;L charges is $9.65</t>
         </is>
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>Rate $3,098.74</t>
+          <t>Rate $9.65</t>
         </is>
       </c>
       <c r="G53" s="3" t="n">
-        <v>1093.66</v>
+        <v>578.1</v>
       </c>
       <c r="H53" s="3" t="inlineStr">
         <is>
@@ -2568,127 +2568,127 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>Rate</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>GN26 Generator - 200kVA (Diesel): $2,005.08</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>the P&amp;L charges $3,098.74 (Street Rate Card 2026 · Generator 200 kVA · published Standby Rate before 23 Oct, from the day it turned up Mon 12 Oct)</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>Rate $3,098.74</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="n">
+        <v>1093.66</v>
+      </c>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>Baseplan</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>9994954</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="C54" s="3" t="inlineStr">
+      <c r="C55" s="3" t="inlineStr">
         <is>
           <t>Rate</t>
         </is>
       </c>
-      <c r="D54" s="3" t="inlineStr">
+      <c r="D55" s="3" t="inlineStr">
         <is>
           <t>GN27 Generator - 200kVA (Diesel): $2,551.92</t>
         </is>
       </c>
-      <c r="E54" s="3" t="inlineStr">
+      <c r="E55" s="3" t="inlineStr">
         <is>
           <t>the P&amp;L charges $3,098.74 (Street Rate Card 2026 · Generator 200 kVA · published Standby Rate before 23 Oct, from the day it turned up Mon 12 Oct)</t>
         </is>
       </c>
-      <c r="F54" s="3" t="inlineStr">
+      <c r="F55" s="3" t="inlineStr">
         <is>
           <t>Rate $3,098.74</t>
         </is>
       </c>
-      <c r="G54" s="3" t="n">
+      <c r="G55" s="3" t="n">
         <v>546.8200000000001</v>
       </c>
-      <c r="H54" s="3" t="inlineStr">
+      <c r="H55" s="3" t="inlineStr">
         <is>
           <t>Baseplan</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>9968862 / 9968955</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>140 / 163</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>ACCOM / MEALS 50% x 2 = $27,700.00</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>the C004 scope (row 68) charges $19,101.60 for accommodation and travel, half each on buildings and toilets</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>Andrew to say which figure stands</t>
         </is>
       </c>
-      <c r="G55" s="2" t="n">
+      <c r="G56" s="2" t="n">
         <v>-8598.4</v>
       </c>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>Decision</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="3" t="inlineStr">
-        <is>
-          <t>9961976</t>
-        </is>
-      </c>
-      <c r="B56" s="3" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="C56" s="3" t="inlineStr">
-        <is>
-          <t>Quantity</t>
-        </is>
-      </c>
-      <c r="D56" s="3" t="inlineStr">
-        <is>
-          <t>Transport Charge: 2 x $600.00</t>
-        </is>
-      </c>
-      <c r="E56" s="3" t="inlineStr">
-        <is>
-          <t>4 on site (GN20, GN23 x 2 legs)</t>
-        </is>
-      </c>
-      <c r="F56" s="3" t="inlineStr">
-        <is>
-          <t>Quantity 4</t>
-        </is>
-      </c>
-      <c r="G56" s="3" t="n">
-        <v>1200</v>
-      </c>
-      <c r="H56" s="3" t="inlineStr">
-        <is>
-          <t>Baseplan</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>9968955</t>
+          <t>9961976</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>84, 140</t>
+          <t>55</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
@@ -2698,20 +2698,22 @@
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>WC67 FWF: 3 on hire</t>
+          <t>Transport Charge: 2 x $600.00</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>WC67 has 4 FWF on site (arrived Thu 01 Oct)</t>
+          <t>4 on site (GN20-A, GN23 x 2 legs)</t>
         </is>
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>Add 1 FWF (hire line)</t>
-        </is>
-      </c>
-      <c r="G57" s="3" t="n"/>
+          <t>Quantity 4</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="n">
+        <v>1200</v>
+      </c>
       <c r="H57" s="3" t="inlineStr">
         <is>
           <t>Baseplan</t>
@@ -2721,12 +2723,12 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>9972648/9990776</t>
+          <t>9968955</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>84, 140</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
@@ -2736,17 +2738,17 @@
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>WB07: 0 barriers</t>
+          <t>WC67 FWF: 3 on hire</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>WB07: 17 on site</t>
+          <t>WC67 has 4 FWF on site (arrived Thu 01 Oct)</t>
         </is>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>Match the quantity to the site count (barriers are charged from when they go in)</t>
+          <t>Add 1 FWF (hire line)</t>
         </is>
       </c>
       <c r="G58" s="3" t="n"/>
@@ -2764,7 +2766,7 @@
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
@@ -2774,12 +2776,12 @@
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>WB05: 12 barriers</t>
+          <t>WB07: 0 barriers</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>WB05: 13 on site</t>
+          <t>WB07: 17 on site</t>
         </is>
       </c>
       <c r="F59" s="3" t="inlineStr">
@@ -2802,7 +2804,7 @@
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
@@ -2812,12 +2814,12 @@
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>WB04: 13 barriers</t>
+          <t>WB05: 12 barriers</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>WB04: 14 on site</t>
+          <t>WB05: 13 on site</t>
         </is>
       </c>
       <c r="F60" s="3" t="inlineStr">
@@ -2835,12 +2837,12 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>9990776</t>
+          <t>9972648/9990776</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
@@ -2850,22 +2852,20 @@
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>Ped Gates: 32</t>
+          <t>WB04: 13 barriers</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>22 on the signed dockets (to 25 Oct)</t>
+          <t>WB04: 14 on site</t>
         </is>
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>Quantity 22</t>
-        </is>
-      </c>
-      <c r="G61" s="3" t="n">
-        <v>-361.8</v>
-      </c>
+          <t>Match the quantity to the site count (barriers are charged from when they go in)</t>
+        </is>
+      </c>
+      <c r="G61" s="3" t="n"/>
       <c r="H61" s="3" t="inlineStr">
         <is>
           <t>Baseplan</t>
@@ -2880,7 +2880,7 @@
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>3, 5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
@@ -2890,21 +2890,21 @@
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>1.8 m security fence 8778 m + with hoarding 110 m</t>
+          <t>Ped Gates: 32</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>13270 m of fence with no scrim on the signed dockets</t>
+          <t>22 on the signed dockets (to 25 Oct)</t>
         </is>
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>Quantity 13160 m on line 3 (keep the 110 m with hoarding on line 5 if it is in the dockets' clean metres)</t>
+          <t>Quantity 22</t>
         </is>
       </c>
       <c r="G62" s="3" t="n">
-        <v>70813.12</v>
+        <v>-361.8</v>
       </c>
       <c r="H62" s="3" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3, 5</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
@@ -2930,21 +2930,21 @@
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>Fence Relocation: 1520</t>
+          <t>1.8 m security fence 8778 m + with hoarding 110 m</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>137.5 on the signed dockets (to 25 Oct); demob relocation still to come</t>
+          <t>9292.5 m of fence with no scrim on the signed dockets (their 13270 m of clean less the 3977.5 m under the scrim, charged once)</t>
         </is>
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>Quantity 137.5 to date</t>
+          <t>Quantity 9182.5 m on line 3 (keep the 110 m with hoarding on line 5 if it is in the dockets' clean metres)</t>
         </is>
       </c>
       <c r="G63" s="3" t="n">
-        <v>-11958.62</v>
+        <v>6536.72</v>
       </c>
       <c r="H63" s="3" t="inlineStr">
         <is>
@@ -2960,7 +2960,7 @@
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
@@ -2970,21 +2970,21 @@
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>1.8m Fence w/Scrim: 2775</t>
+          <t>Fence Relocation: 1520</t>
         </is>
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>3977.5 m of fence with scrim on the signed dockets (to 25 Oct)</t>
+          <t>137.5 on the signed dockets (to 25 Oct); demob relocation still to come</t>
         </is>
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>Quantity 3977.5</t>
+          <t>Quantity 137.5 to date</t>
         </is>
       </c>
       <c r="G64" s="3" t="n">
-        <v>19432.4</v>
+        <v>-11958.62</v>
       </c>
       <c r="H64" s="3" t="inlineStr">
         <is>
@@ -3000,7 +3000,7 @@
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
@@ -3010,21 +3010,21 @@
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>Barrier - Crowd Control: 2350</t>
+          <t>1.8m Fence w/Scrim: 2775</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>2195 on the signed dockets (to 25 Oct)</t>
+          <t>3977.5 m of fence with scrim on the signed dockets (to 25 Oct)</t>
         </is>
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>Quantity 2195</t>
+          <t>Quantity 3977.5</t>
         </is>
       </c>
       <c r="G65" s="3" t="n">
-        <v>-1164.05</v>
+        <v>19432.4</v>
       </c>
       <c r="H65" s="3" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
@@ -3050,21 +3050,21 @@
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>Barrier - Crowd Control Flat Feet: 220</t>
+          <t>Barrier - Crowd Control: 2350</t>
         </is>
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>270 on the signed dockets (to 25 Oct)</t>
+          <t>2195 on the signed dockets (to 25 Oct)</t>
         </is>
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>Quantity 270</t>
+          <t>Quantity 2195</t>
         </is>
       </c>
       <c r="G66" s="3" t="n">
-        <v>375.5</v>
+        <v>-1164.05</v>
       </c>
       <c r="H66" s="3" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
@@ -3090,21 +3090,21 @@
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>Demarcation CCB: 4603</t>
+          <t>Barrier - Crowd Control Flat Feet: 220</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>5062.5 on the signed dockets (to 25 Oct)</t>
+          <t>270 on the signed dockets (to 25 Oct)</t>
         </is>
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>Quantity 5062.5</t>
+          <t>Quantity 270</t>
         </is>
       </c>
       <c r="G67" s="3" t="n">
-        <v>6010.26</v>
+        <v>375.5</v>
       </c>
       <c r="H67" s="3" t="inlineStr">
         <is>
@@ -3120,189 +3120,191 @@
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>Demarcation CCB: 4603</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="inlineStr">
+        <is>
+          <t>5062.5 on the signed dockets (to 25 Oct)</t>
+        </is>
+      </c>
+      <c r="F68" s="3" t="inlineStr">
+        <is>
+          <t>Quantity 5062.5</t>
+        </is>
+      </c>
+      <c r="G68" s="3" t="n">
+        <v>6010.26</v>
+      </c>
+      <c r="H68" s="3" t="inlineStr">
+        <is>
+          <t>Baseplan</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>9990776</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="C68" s="3" t="inlineStr">
+      <c r="C69" s="3" t="inlineStr">
         <is>
           <t>Quantity</t>
         </is>
       </c>
-      <c r="D68" s="3" t="inlineStr">
+      <c r="D69" s="3" t="inlineStr">
         <is>
           <t>Shade Cloth: 2775</t>
         </is>
       </c>
-      <c r="E68" s="3" t="inlineStr">
+      <c r="E69" s="3" t="inlineStr">
         <is>
           <t>3977.5 m of fence with scrim on the signed dockets (to 25 Oct)</t>
         </is>
       </c>
-      <c r="F68" s="3" t="inlineStr">
+      <c r="F69" s="3" t="inlineStr">
         <is>
           <t>Quantity 3977.5</t>
         </is>
       </c>
-      <c r="G68" s="3" t="n">
+      <c r="G69" s="3" t="n">
         <v>11267.43</v>
       </c>
-      <c r="H68" s="3" t="inlineStr">
+      <c r="H69" s="3" t="inlineStr">
         <is>
           <t>Baseplan</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="4" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="4" t="inlineStr">
         <is>
           <t>our P&amp;L</t>
         </is>
       </c>
-      <c r="B69" s="4" t="inlineStr">
+      <c r="B70" s="4" t="inlineStr">
         <is>
           <t>servicing</t>
         </is>
       </c>
-      <c r="C69" s="4" t="inlineStr">
+      <c r="C70" s="4" t="inlineStr">
         <is>
           <t>Quantity</t>
         </is>
       </c>
-      <c r="D69" s="4" t="inlineStr">
+      <c r="D70" s="4" t="inlineStr">
         <is>
           <t>the P&amp;L charges WC31's two 16-pan blocks as sewer-connect cleans (2 x 3 x $260.25 = $1,561.50)</t>
         </is>
       </c>
-      <c r="E69" s="4" t="inlineStr">
+      <c r="E70" s="4" t="inlineStr">
         <is>
           <t>they are pumped out every night (servicing tracker), as Baseplan line 142 charges them (2 x 3 x $624.60 = $3,747.60)</t>
         </is>
       </c>
-      <c r="F69" s="4" t="inlineStr">
+      <c r="F70" s="4" t="inlineStr">
         <is>
           <t>Count the 16-pans with the tank pump-outs on Costs (P&amp;L +$2,186.10)</t>
         </is>
       </c>
-      <c r="G69" s="4" t="n"/>
-      <c r="H69" s="4" t="inlineStr">
+      <c r="G70" s="4" t="n"/>
+      <c r="H70" s="4" t="inlineStr">
         <is>
           <t>Our record</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="3" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
         <is>
           <t>9968955</t>
         </is>
       </c>
-      <c r="B70" s="3" t="inlineStr">
+      <c r="B71" s="3" t="inlineStr">
         <is>
           <t>154</t>
         </is>
       </c>
-      <c r="C70" s="3" t="inlineStr">
+      <c r="C71" s="3" t="inlineStr">
         <is>
           <t>Remove</t>
         </is>
       </c>
-      <c r="D70" s="3" t="inlineStr">
+      <c r="D71" s="3" t="inlineStr">
         <is>
           <t>PG29 Toilet FWF at $90.07</t>
         </is>
       </c>
-      <c r="E70" s="3" t="inlineStr">
+      <c r="E71" s="3" t="inlineStr">
         <is>
           <t>PG29 is on its own hire schedule (held out of every charge, Andrew 23 Oct)</t>
         </is>
       </c>
-      <c r="F70" s="3" t="inlineStr">
+      <c r="F71" s="3" t="inlineStr">
         <is>
           <t>Take the line off this contract</t>
         </is>
       </c>
-      <c r="G70" s="3" t="n">
+      <c r="G71" s="3" t="n">
         <v>-90.06999999999999</v>
       </c>
-      <c r="H70" s="3" t="inlineStr">
+      <c r="H71" s="3" t="inlineStr">
         <is>
           <t>Baseplan</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="5" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="5" t="inlineStr">
         <is>
           <t>9968955</t>
         </is>
       </c>
-      <c r="B71" s="5" t="inlineStr">
+      <c r="B72" s="5" t="inlineStr">
         <is>
           <t>38</t>
         </is>
       </c>
-      <c r="C71" s="5" t="inlineStr">
+      <c r="C72" s="5" t="inlineStr">
         <is>
           <t>Asset number</t>
         </is>
       </c>
-      <c r="D71" s="5" t="inlineStr">
+      <c r="D72" s="5" t="inlineStr">
         <is>
           <t>WC07 asset 1317643</t>
         </is>
       </c>
-      <c r="E71" s="5" t="inlineStr">
+      <c r="E72" s="5" t="inlineStr">
         <is>
           <t>WC07 on site carries 1002538, 1002566, 1002651, 1002715, 1083300, 1181004, 1192643, 1200595, 1211959, 1212552, 1317626, 1317632, 1317640, 1317641, 1317647, 1317648, 1317649, 1317652, 1317658, 1317743</t>
         </is>
       </c>
-      <c r="F71" s="5" t="inlineStr">
+      <c r="F72" s="5" t="inlineStr">
         <is>
           <t>Correct the number on the line (the site number stands)</t>
         </is>
       </c>
-      <c r="G71" s="5" t="n"/>
-      <c r="H71" s="5" t="inlineStr">
+      <c r="G72" s="5" t="n"/>
+      <c r="H72" s="5" t="inlineStr">
         <is>
           <t>Baseplan</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="4" t="inlineStr">
-        <is>
-          <t>our record</t>
-        </is>
-      </c>
-      <c r="B72" s="4" t="inlineStr">
-        <is>
-          <t>GN20</t>
-        </is>
-      </c>
-      <c r="C72" s="4" t="inlineStr">
-        <is>
-          <t>Not on site</t>
-        </is>
-      </c>
-      <c r="D72" s="4" t="inlineStr">
-        <is>
-          <t>GN20 365 kVA (1276701) is Delivered from Wed 30 Sep on Baseplan, as it should be</t>
-        </is>
-      </c>
-      <c r="E72" s="4" t="inlineStr">
-        <is>
-          <t>our record deleted GN20 on 20 Oct and the P&amp;L stopped charging it on 22 Oct (v11.18)</t>
-        </is>
-      </c>
-      <c r="F72" s="4" t="inlineStr">
-        <is>
-          <t>Put it back on our record and the P&amp;L (the page will not re-use a deleted reference)</t>
-        </is>
-      </c>
-      <c r="G72" s="4" t="n"/>
-      <c r="H72" s="4" t="inlineStr">
-        <is>
-          <t>Our record</t>
         </is>
       </c>
     </row>
@@ -3935,20 +3937,20 @@
         </is>
       </c>
       <c r="B3" s="6" t="n">
-        <v>83261.99000000001</v>
+        <v>90102.82000000001</v>
       </c>
       <c r="C3" s="6" t="n">
-        <v>85964.00999999999</v>
+        <v>92804.84</v>
       </c>
       <c r="D3" s="6" t="n">
-        <v>4618.4</v>
+        <v>5198.83</v>
       </c>
       <c r="E3" s="6" t="n">
         <v>28671.82</v>
       </c>
       <c r="F3" s="6" t="inlineStr">
         <is>
-          <t>Baseplan · Hours: $15.01; Baseplan · Quantity: $1,200.00; Baseplan · Rate: $3,403.39; Decision · Rate: $28,671.82</t>
+          <t>Baseplan · Hours: $15.01; Baseplan · Quantity: $1,200.00; Baseplan · Rate: $3,983.82; Decision · Rate: $28,671.82</t>
         </is>
       </c>
     </row>
@@ -3959,20 +3961,20 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>477058.5</v>
+        <v>412779.27</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>503580.9</v>
+        <v>439301.67</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>115865.98</v>
+        <v>51589.58</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Baseplan · Hours: $30.38; Baseplan · Missing line: $21,272.14; Baseplan · Quantity: $94,414.24; Baseplan · Rate: $578.10; Baseplan · Start date: $-428.88</t>
+          <t>Baseplan · Hours: $30.38; Baseplan · Missing line: $21,272.14; Baseplan · Quantity: $30,137.84; Baseplan · Rate: $578.10; Baseplan · Start date: $-428.88</t>
         </is>
       </c>
     </row>
@@ -4003,13 +4005,13 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>993557.87</v>
+        <v>936119.47</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>1022962.43</v>
+        <v>965524.03</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>135180.71</v>
+        <v>71484.74000000001</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>20073.42</v>
@@ -4027,7 +4029,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H162"/>
+  <dimension ref="A1:H163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -4199,25 +4201,25 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>9968955</t>
+          <t>9987005</t>
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>WC06 Toilet Portable - Fresh Water Flush</t>
+          <t>Laserplane</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>Mon 14 Sep</t>
+          <t>Fri 16 Oct</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>Wed 23 Sep</t>
+          <t>Sun 25 Oct</t>
         </is>
       </c>
       <c r="F5" s="6" t="n">
@@ -4230,7 +4232,7 @@
       </c>
       <c r="H5" s="6" t="inlineStr">
         <is>
-          <t>WC06 on site on the record</t>
+          <t>EQ0006 on site on the record</t>
         </is>
       </c>
     </row>
@@ -4241,11 +4243,11 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>WC50 Toilet Portable - Fresh Water Flush</t>
+          <t>WC06 Toilet Portable - Fresh Water Flush</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -4268,7 +4270,7 @@
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>WC50 on site on the record</t>
+          <t>WC06 on site on the record</t>
         </is>
       </c>
     </row>
@@ -4279,11 +4281,11 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>WC07 Toilet Portable - Fresh Water Flush</t>
+          <t>WC50 Toilet Portable - Fresh Water Flush</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
@@ -4293,11 +4295,11 @@
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>Tue 22 Sep</t>
+          <t>Wed 23 Sep</t>
         </is>
       </c>
       <c r="F7" s="6" t="n">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
@@ -4306,7 +4308,7 @@
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>WC07 on site on the record</t>
+          <t>WC50 on site on the record</t>
         </is>
       </c>
     </row>
@@ -4317,7 +4319,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
@@ -4355,7 +4357,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
@@ -4393,7 +4395,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
@@ -4431,7 +4433,7 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
@@ -4469,7 +4471,7 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
@@ -4507,7 +4509,7 @@
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
@@ -4545,7 +4547,7 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
@@ -4583,7 +4585,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
@@ -4621,7 +4623,7 @@
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
@@ -4659,7 +4661,7 @@
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
@@ -4697,7 +4699,7 @@
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
@@ -4735,7 +4737,7 @@
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
@@ -4773,7 +4775,7 @@
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
@@ -4811,7 +4813,7 @@
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
@@ -4849,7 +4851,7 @@
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
@@ -4887,7 +4889,7 @@
         </is>
       </c>
       <c r="B23" s="6" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
@@ -4925,7 +4927,7 @@
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
@@ -4963,7 +4965,7 @@
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
@@ -5001,7 +5003,7 @@
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
@@ -5039,11 +5041,11 @@
         </is>
       </c>
       <c r="B27" s="6" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>WC04 Toilet Portable - Fresh Water Flush</t>
+          <t>WC07 Toilet Portable - Fresh Water Flush</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
@@ -5066,7 +5068,7 @@
       </c>
       <c r="H27" s="6" t="inlineStr">
         <is>
-          <t>WC04 on site on the record</t>
+          <t>WC07 on site on the record</t>
         </is>
       </c>
     </row>
@@ -5077,11 +5079,11 @@
         </is>
       </c>
       <c r="B28" s="6" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>WC02 Toilet Portable - Fresh Water Flush</t>
+          <t>WC04 Toilet Portable - Fresh Water Flush</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
@@ -5104,7 +5106,7 @@
       </c>
       <c r="H28" s="6" t="inlineStr">
         <is>
-          <t>WC02 on site on the record</t>
+          <t>WC04 on site on the record</t>
         </is>
       </c>
     </row>
@@ -5115,11 +5117,11 @@
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>WC01 Toilet Portable - Fresh Water Flush</t>
+          <t>WC02 Toilet Portable - Fresh Water Flush</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
@@ -5129,11 +5131,11 @@
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>Mon 28 Sep</t>
+          <t>Tue 22 Sep</t>
         </is>
       </c>
       <c r="F29" s="6" t="n">
-        <v>-14</v>
+        <v>-8</v>
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
@@ -5142,7 +5144,7 @@
       </c>
       <c r="H29" s="6" t="inlineStr">
         <is>
-          <t>WC01 on site on the record</t>
+          <t>WC02 on site on the record</t>
         </is>
       </c>
     </row>
@@ -5153,11 +5155,11 @@
         </is>
       </c>
       <c r="B30" s="6" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>WC20 Toilet Block Male Female Cyclone Rated 6m x 3</t>
+          <t>WC01 Toilet Portable - Fresh Water Flush</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
@@ -5167,11 +5169,11 @@
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>Wed 07 Oct</t>
+          <t>Mon 28 Sep</t>
         </is>
       </c>
       <c r="F30" s="6" t="n">
-        <v>-23</v>
+        <v>-14</v>
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
@@ -5180,7 +5182,7 @@
       </c>
       <c r="H30" s="6" t="inlineStr">
         <is>
-          <t>WC20 on site on the record</t>
+          <t>WC01 on site on the record</t>
         </is>
       </c>
     </row>
@@ -5191,7 +5193,7 @@
         </is>
       </c>
       <c r="B31" s="6" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
@@ -5229,11 +5231,11 @@
         </is>
       </c>
       <c r="B32" s="6" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>WC20 Sewage Holding Tank 6.0M x 2.4M</t>
+          <t>WC20 Toilet Block Male Female Cyclone Rated 6m x 3</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
@@ -5267,7 +5269,7 @@
         </is>
       </c>
       <c r="B33" s="6" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
@@ -5305,11 +5307,11 @@
         </is>
       </c>
       <c r="B34" s="6" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>Wc86 Toilet - Disabled Access</t>
+          <t>WC20 Sewage Holding Tank 6.0M x 2.4M</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
@@ -5332,7 +5334,7 @@
       </c>
       <c r="H34" s="6" t="inlineStr">
         <is>
-          <t>WC86 on site on the record</t>
+          <t>WC20 on site on the record</t>
         </is>
       </c>
     </row>
@@ -5343,11 +5345,11 @@
         </is>
       </c>
       <c r="B35" s="6" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>WC27 Toilet Block 6.0M x 3.0M</t>
+          <t>Wc86 Toilet - Disabled Access</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
@@ -5357,11 +5359,11 @@
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>Fri 25 Sep</t>
+          <t>Wed 07 Oct</t>
         </is>
       </c>
       <c r="F35" s="6" t="n">
-        <v>-11</v>
+        <v>-23</v>
       </c>
       <c r="G35" s="6" t="inlineStr">
         <is>
@@ -5370,7 +5372,7 @@
       </c>
       <c r="H35" s="6" t="inlineStr">
         <is>
-          <t>WC27 on site on the record</t>
+          <t>WC86 on site on the record</t>
         </is>
       </c>
     </row>
@@ -5381,11 +5383,11 @@
         </is>
       </c>
       <c r="B36" s="6" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>WC27 Sewage Holding Tank 6.0M x 2.4M</t>
+          <t>WC27 Toilet Block 6.0M x 3.0M</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
@@ -5419,11 +5421,11 @@
         </is>
       </c>
       <c r="B37" s="6" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>WC15 Toilet Block Male Female Cyclone Rated 6m x 3</t>
+          <t>WC27 Sewage Holding Tank 6.0M x 2.4M</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
@@ -5446,7 +5448,7 @@
       </c>
       <c r="H37" s="6" t="inlineStr">
         <is>
-          <t>WC15 on site on the record</t>
+          <t>WC27 on site on the record</t>
         </is>
       </c>
     </row>
@@ -5457,7 +5459,7 @@
         </is>
       </c>
       <c r="B38" s="6" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
@@ -5495,11 +5497,11 @@
         </is>
       </c>
       <c r="B39" s="6" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>WC01 Toilet - Accessible</t>
+          <t>WC15 Toilet Block Male Female Cyclone Rated 6m x 3</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
@@ -5509,11 +5511,11 @@
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>Mon 28 Sep</t>
+          <t>Fri 25 Sep</t>
         </is>
       </c>
       <c r="F39" s="6" t="n">
-        <v>-14</v>
+        <v>-11</v>
       </c>
       <c r="G39" s="6" t="inlineStr">
         <is>
@@ -5522,7 +5524,7 @@
       </c>
       <c r="H39" s="6" t="inlineStr">
         <is>
-          <t>WC01 on site on the record</t>
+          <t>WC15 on site on the record</t>
         </is>
       </c>
     </row>
@@ -5533,11 +5535,11 @@
         </is>
       </c>
       <c r="B40" s="6" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>WC06 Toilet Portable - Fresh Water Flush</t>
+          <t>WC01 Toilet - Accessible</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
@@ -5547,11 +5549,11 @@
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>Wed 23 Sep</t>
+          <t>Mon 28 Sep</t>
         </is>
       </c>
       <c r="F40" s="6" t="n">
-        <v>-9</v>
+        <v>-14</v>
       </c>
       <c r="G40" s="6" t="inlineStr">
         <is>
@@ -5560,7 +5562,7 @@
       </c>
       <c r="H40" s="6" t="inlineStr">
         <is>
-          <t>WC06 on site on the record</t>
+          <t>WC01 on site on the record</t>
         </is>
       </c>
     </row>
@@ -5571,11 +5573,11 @@
         </is>
       </c>
       <c r="B41" s="6" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>WC41 Toilet Portable - Fresh Water Flush</t>
+          <t>WC06 Toilet Portable - Fresh Water Flush</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
@@ -5585,11 +5587,11 @@
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>Mon 28 Sep</t>
+          <t>Wed 23 Sep</t>
         </is>
       </c>
       <c r="F41" s="6" t="n">
-        <v>-14</v>
+        <v>-9</v>
       </c>
       <c r="G41" s="6" t="inlineStr">
         <is>
@@ -5598,7 +5600,7 @@
       </c>
       <c r="H41" s="6" t="inlineStr">
         <is>
-          <t>WC41 on site on the record</t>
+          <t>WC06 on site on the record</t>
         </is>
       </c>
     </row>
@@ -5609,11 +5611,11 @@
         </is>
       </c>
       <c r="B42" s="6" t="n">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>WC01 Toilet Portable - Fresh Water Flush</t>
+          <t>WC41 Toilet Portable - Fresh Water Flush</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
@@ -5636,7 +5638,7 @@
       </c>
       <c r="H42" s="6" t="inlineStr">
         <is>
-          <t>WC01 on site on the record</t>
+          <t>WC41 on site on the record</t>
         </is>
       </c>
     </row>
@@ -5647,11 +5649,11 @@
         </is>
       </c>
       <c r="B43" s="6" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>WC43 Toilet Portable - Fresh Water Flush</t>
+          <t>WC01 Toilet Portable - Fresh Water Flush</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
@@ -5674,7 +5676,7 @@
       </c>
       <c r="H43" s="6" t="inlineStr">
         <is>
-          <t>WC43 on site on the record</t>
+          <t>WC01 on site on the record</t>
         </is>
       </c>
     </row>
@@ -5685,11 +5687,11 @@
         </is>
       </c>
       <c r="B44" s="6" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>WC44 Toilet Portable - Fresh Water Flush</t>
+          <t>WC43 Toilet Portable - Fresh Water Flush</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
@@ -5699,11 +5701,11 @@
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>Thu 01 Oct</t>
+          <t>Mon 28 Sep</t>
         </is>
       </c>
       <c r="F44" s="6" t="n">
-        <v>-17</v>
+        <v>-14</v>
       </c>
       <c r="G44" s="6" t="inlineStr">
         <is>
@@ -5712,7 +5714,7 @@
       </c>
       <c r="H44" s="6" t="inlineStr">
         <is>
-          <t>WC44 on site on the record</t>
+          <t>WC43 on site on the record</t>
         </is>
       </c>
     </row>
@@ -5723,7 +5725,7 @@
         </is>
       </c>
       <c r="B45" s="6" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
@@ -5761,11 +5763,11 @@
         </is>
       </c>
       <c r="B46" s="6" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>WC67 Toilet Portable - Fresh Water Flush</t>
+          <t>WC44 Toilet Portable - Fresh Water Flush</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
@@ -5788,7 +5790,7 @@
       </c>
       <c r="H46" s="6" t="inlineStr">
         <is>
-          <t>WC67 on site on the record</t>
+          <t>WC44 on site on the record</t>
         </is>
       </c>
     </row>
@@ -5799,11 +5801,11 @@
         </is>
       </c>
       <c r="B47" s="6" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>WC70 Toilet Portable - Fresh Water Flush</t>
+          <t>WC67 Toilet Portable - Fresh Water Flush</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
@@ -5813,11 +5815,11 @@
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>Tue 13 Oct</t>
+          <t>Thu 01 Oct</t>
         </is>
       </c>
       <c r="F47" s="6" t="n">
-        <v>-29</v>
+        <v>-17</v>
       </c>
       <c r="G47" s="6" t="inlineStr">
         <is>
@@ -5826,7 +5828,7 @@
       </c>
       <c r="H47" s="6" t="inlineStr">
         <is>
-          <t>WC70 on site on the record</t>
+          <t>WC67 on site on the record</t>
         </is>
       </c>
     </row>
@@ -5837,11 +5839,11 @@
         </is>
       </c>
       <c r="B48" s="6" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>WC71 Toilet Portable - Fresh Water Flush</t>
+          <t>WC70 Toilet Portable - Fresh Water Flush</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
@@ -5851,11 +5853,11 @@
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>Thu 01 Oct</t>
+          <t>Tue 13 Oct</t>
         </is>
       </c>
       <c r="F48" s="6" t="n">
-        <v>-17</v>
+        <v>-29</v>
       </c>
       <c r="G48" s="6" t="inlineStr">
         <is>
@@ -5864,7 +5866,7 @@
       </c>
       <c r="H48" s="6" t="inlineStr">
         <is>
-          <t>WC71 on site on the record</t>
+          <t>WC70 on site on the record</t>
         </is>
       </c>
     </row>
@@ -5875,11 +5877,11 @@
         </is>
       </c>
       <c r="B49" s="6" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>WC69 Toilet Portable - Fresh Water Flush</t>
+          <t>WC71 Toilet Portable - Fresh Water Flush</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
@@ -5889,11 +5891,11 @@
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>Mon 12 Oct</t>
+          <t>Thu 01 Oct</t>
         </is>
       </c>
       <c r="F49" s="6" t="n">
-        <v>-28</v>
+        <v>-17</v>
       </c>
       <c r="G49" s="6" t="inlineStr">
         <is>
@@ -5902,7 +5904,7 @@
       </c>
       <c r="H49" s="6" t="inlineStr">
         <is>
-          <t>WC69 on site on the record</t>
+          <t>WC71 on site on the record</t>
         </is>
       </c>
     </row>
@@ -5913,11 +5915,11 @@
         </is>
       </c>
       <c r="B50" s="6" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>WC38 Toilet Portable - Fresh Water Flush</t>
+          <t>WC69 Toilet Portable - Fresh Water Flush</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
@@ -5927,11 +5929,11 @@
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>Tue 13 Oct</t>
+          <t>Mon 12 Oct</t>
         </is>
       </c>
       <c r="F50" s="6" t="n">
-        <v>-29</v>
+        <v>-28</v>
       </c>
       <c r="G50" s="6" t="inlineStr">
         <is>
@@ -5940,7 +5942,7 @@
       </c>
       <c r="H50" s="6" t="inlineStr">
         <is>
-          <t>WC38 on site on the record</t>
+          <t>WC69 on site on the record</t>
         </is>
       </c>
     </row>
@@ -5951,11 +5953,11 @@
         </is>
       </c>
       <c r="B51" s="6" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>WC39 Toilet Portable - Fresh Water Flush</t>
+          <t>WC38 Toilet Portable - Fresh Water Flush</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
@@ -5978,7 +5980,7 @@
       </c>
       <c r="H51" s="6" t="inlineStr">
         <is>
-          <t>WC39 on site on the record</t>
+          <t>WC38 on site on the record</t>
         </is>
       </c>
     </row>
@@ -5989,11 +5991,11 @@
         </is>
       </c>
       <c r="B52" s="6" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>WC40 Toilet Portable - Fresh Water Flush</t>
+          <t>WC39 Toilet Portable - Fresh Water Flush</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
@@ -6016,7 +6018,7 @@
       </c>
       <c r="H52" s="6" t="inlineStr">
         <is>
-          <t>WC40 on site on the record</t>
+          <t>WC39 on site on the record</t>
         </is>
       </c>
     </row>
@@ -6027,11 +6029,11 @@
         </is>
       </c>
       <c r="B53" s="6" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>WC60 Toilet Block 6.0M x 3.0M</t>
+          <t>WC40 Toilet Portable - Fresh Water Flush</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
@@ -6041,11 +6043,11 @@
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>Thu 01 Oct</t>
+          <t>Tue 13 Oct</t>
         </is>
       </c>
       <c r="F53" s="6" t="n">
-        <v>-17</v>
+        <v>-29</v>
       </c>
       <c r="G53" s="6" t="inlineStr">
         <is>
@@ -6054,7 +6056,7 @@
       </c>
       <c r="H53" s="6" t="inlineStr">
         <is>
-          <t>WC60 on site on the record</t>
+          <t>WC40 on site on the record</t>
         </is>
       </c>
     </row>
@@ -6065,7 +6067,7 @@
         </is>
       </c>
       <c r="B54" s="6" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
@@ -6103,11 +6105,11 @@
         </is>
       </c>
       <c r="B55" s="6" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>WC60 Sewage Holding Tank 6.0M x 2.4M</t>
+          <t>WC60 Toilet Block 6.0M x 3.0M</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
@@ -6141,7 +6143,7 @@
         </is>
       </c>
       <c r="B56" s="6" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
@@ -6179,11 +6181,11 @@
         </is>
       </c>
       <c r="B57" s="6" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>WC61 Toilet Portable - Fresh Water Flush</t>
+          <t>WC60 Sewage Holding Tank 6.0M x 2.4M</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
@@ -6193,11 +6195,11 @@
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>Mon 12 Oct</t>
+          <t>Thu 01 Oct</t>
         </is>
       </c>
       <c r="F57" s="6" t="n">
-        <v>-28</v>
+        <v>-17</v>
       </c>
       <c r="G57" s="6" t="inlineStr">
         <is>
@@ -6206,7 +6208,7 @@
       </c>
       <c r="H57" s="6" t="inlineStr">
         <is>
-          <t>WC61 on site on the record</t>
+          <t>WC60 on site on the record</t>
         </is>
       </c>
     </row>
@@ -6217,11 +6219,11 @@
         </is>
       </c>
       <c r="B58" s="6" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>WC31 Toilet - Accessible</t>
+          <t>WC61 Toilet Portable - Fresh Water Flush</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
@@ -6231,11 +6233,11 @@
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>Fri 25 Sep</t>
+          <t>Mon 12 Oct</t>
         </is>
       </c>
       <c r="F58" s="6" t="n">
-        <v>-11</v>
+        <v>-28</v>
       </c>
       <c r="G58" s="6" t="inlineStr">
         <is>
@@ -6244,7 +6246,7 @@
       </c>
       <c r="H58" s="6" t="inlineStr">
         <is>
-          <t>WC31 on site on the record</t>
+          <t>WC61 on site on the record</t>
         </is>
       </c>
     </row>
@@ -6255,11 +6257,11 @@
         </is>
       </c>
       <c r="B59" s="6" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>WC31 16 Pan Block</t>
+          <t>WC31 Toilet - Accessible</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
@@ -6293,11 +6295,11 @@
         </is>
       </c>
       <c r="B60" s="6" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>WC34 Toilet Portable - Fresh Water Flush</t>
+          <t>WC31 16 Pan Block</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
@@ -6307,11 +6309,11 @@
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>Tue 13 Oct</t>
+          <t>Fri 25 Sep</t>
         </is>
       </c>
       <c r="F60" s="6" t="n">
-        <v>-29</v>
+        <v>-11</v>
       </c>
       <c r="G60" s="6" t="inlineStr">
         <is>
@@ -6320,7 +6322,7 @@
       </c>
       <c r="H60" s="6" t="inlineStr">
         <is>
-          <t>WC34 on site on the record</t>
+          <t>WC31 on site on the record</t>
         </is>
       </c>
     </row>
@@ -6331,11 +6333,11 @@
         </is>
       </c>
       <c r="B61" s="6" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>WC33 Toilet Portable - Fresh Water Flush</t>
+          <t>WC34 Toilet Portable - Fresh Water Flush</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
@@ -6345,11 +6347,11 @@
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>Thu 01 Oct</t>
+          <t>Tue 13 Oct</t>
         </is>
       </c>
       <c r="F61" s="6" t="n">
-        <v>-17</v>
+        <v>-29</v>
       </c>
       <c r="G61" s="6" t="inlineStr">
         <is>
@@ -6358,7 +6360,7 @@
       </c>
       <c r="H61" s="6" t="inlineStr">
         <is>
-          <t>WC33 on site on the record</t>
+          <t>WC34 on site on the record</t>
         </is>
       </c>
     </row>
@@ -6369,11 +6371,11 @@
         </is>
       </c>
       <c r="B62" s="6" t="n">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>WC59 FWF Toilet</t>
+          <t>WC33 Toilet Portable - Fresh Water Flush</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
@@ -6396,7 +6398,7 @@
       </c>
       <c r="H62" s="6" t="inlineStr">
         <is>
-          <t>WC59 on site on the record</t>
+          <t>WC33 on site on the record</t>
         </is>
       </c>
     </row>
@@ -6407,11 +6409,11 @@
         </is>
       </c>
       <c r="B63" s="6" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>WC57 FWF Toilet</t>
+          <t>WC59 FWF Toilet</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
@@ -6421,11 +6423,11 @@
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>Wed 14 Oct</t>
+          <t>Thu 01 Oct</t>
         </is>
       </c>
       <c r="F63" s="6" t="n">
-        <v>-30</v>
+        <v>-17</v>
       </c>
       <c r="G63" s="6" t="inlineStr">
         <is>
@@ -6434,7 +6436,7 @@
       </c>
       <c r="H63" s="6" t="inlineStr">
         <is>
-          <t>WC57 on site on the record</t>
+          <t>WC59 on site on the record</t>
         </is>
       </c>
     </row>
@@ -6445,11 +6447,11 @@
         </is>
       </c>
       <c r="B64" s="6" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>WC49 FWF Toilet</t>
+          <t>WC57 FWF Toilet</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
@@ -6472,7 +6474,7 @@
       </c>
       <c r="H64" s="6" t="inlineStr">
         <is>
-          <t>WC49 on site on the record</t>
+          <t>WC57 on site on the record</t>
         </is>
       </c>
     </row>
@@ -6483,11 +6485,11 @@
         </is>
       </c>
       <c r="B65" s="6" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>WC48 FWF Toilet</t>
+          <t>WC49 FWF Toilet</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
@@ -6510,7 +6512,7 @@
       </c>
       <c r="H65" s="6" t="inlineStr">
         <is>
-          <t>WC48 on site on the record</t>
+          <t>WC49 on site on the record</t>
         </is>
       </c>
     </row>
@@ -6521,11 +6523,11 @@
         </is>
       </c>
       <c r="B66" s="6" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>WC51 FWF Toilet</t>
+          <t>WC48 FWF Toilet</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
@@ -6535,11 +6537,11 @@
       </c>
       <c r="E66" s="6" t="inlineStr">
         <is>
-          <t>Thu 15 Oct</t>
+          <t>Wed 14 Oct</t>
         </is>
       </c>
       <c r="F66" s="6" t="n">
-        <v>-31</v>
+        <v>-30</v>
       </c>
       <c r="G66" s="6" t="inlineStr">
         <is>
@@ -6548,7 +6550,7 @@
       </c>
       <c r="H66" s="6" t="inlineStr">
         <is>
-          <t>WC51 on site on the record</t>
+          <t>WC48 on site on the record</t>
         </is>
       </c>
     </row>
@@ -6559,11 +6561,11 @@
         </is>
       </c>
       <c r="B67" s="6" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>WC51 Toilet - Accessible</t>
+          <t>WC51 FWF Toilet</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
@@ -6597,11 +6599,11 @@
         </is>
       </c>
       <c r="B68" s="6" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>WC54 FWF Toilet</t>
+          <t>WC51 Toilet - Accessible</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
@@ -6611,11 +6613,11 @@
       </c>
       <c r="E68" s="6" t="inlineStr">
         <is>
-          <t>Wed 14 Oct</t>
+          <t>Thu 15 Oct</t>
         </is>
       </c>
       <c r="F68" s="6" t="n">
-        <v>-30</v>
+        <v>-31</v>
       </c>
       <c r="G68" s="6" t="inlineStr">
         <is>
@@ -6624,7 +6626,7 @@
       </c>
       <c r="H68" s="6" t="inlineStr">
         <is>
-          <t>WC54 on site on the record</t>
+          <t>WC51 on site on the record</t>
         </is>
       </c>
     </row>
@@ -6635,11 +6637,11 @@
         </is>
       </c>
       <c r="B69" s="6" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>WC56 FWF Toilet</t>
+          <t>WC54 FWF Toilet</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
@@ -6649,11 +6651,11 @@
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t>Thu 01 Oct</t>
+          <t>Wed 14 Oct</t>
         </is>
       </c>
       <c r="F69" s="6" t="n">
-        <v>-17</v>
+        <v>-30</v>
       </c>
       <c r="G69" s="6" t="inlineStr">
         <is>
@@ -6662,7 +6664,7 @@
       </c>
       <c r="H69" s="6" t="inlineStr">
         <is>
-          <t>WC56 on site on the record</t>
+          <t>WC54 on site on the record</t>
         </is>
       </c>
     </row>
@@ -6673,11 +6675,11 @@
         </is>
       </c>
       <c r="B70" s="6" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>WC45 Toilet Portable - Fresh Water Flush</t>
+          <t>WC56 FWF Toilet</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr">
@@ -6687,11 +6689,11 @@
       </c>
       <c r="E70" s="6" t="inlineStr">
         <is>
-          <t>Fri 16 Oct</t>
+          <t>Thu 01 Oct</t>
         </is>
       </c>
       <c r="F70" s="6" t="n">
-        <v>-32</v>
+        <v>-17</v>
       </c>
       <c r="G70" s="6" t="inlineStr">
         <is>
@@ -6700,7 +6702,7 @@
       </c>
       <c r="H70" s="6" t="inlineStr">
         <is>
-          <t>WC45 on site on the record</t>
+          <t>WC56 on site on the record</t>
         </is>
       </c>
     </row>
@@ -6711,11 +6713,11 @@
         </is>
       </c>
       <c r="B71" s="6" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>WC47 Toilet Portable - Fresh Water Flush</t>
+          <t>WC45 Toilet Portable - Fresh Water Flush</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
@@ -6725,11 +6727,11 @@
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>Thu 15 Oct</t>
+          <t>Fri 16 Oct</t>
         </is>
       </c>
       <c r="F71" s="6" t="n">
-        <v>-31</v>
+        <v>-32</v>
       </c>
       <c r="G71" s="6" t="inlineStr">
         <is>
@@ -6738,7 +6740,7 @@
       </c>
       <c r="H71" s="6" t="inlineStr">
         <is>
-          <t>WC47 on site on the record</t>
+          <t>WC45 on site on the record</t>
         </is>
       </c>
     </row>
@@ -6749,11 +6751,11 @@
         </is>
       </c>
       <c r="B72" s="6" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>WC19 Toilet Portable - Fresh Water Flush</t>
+          <t>WC47 Toilet Portable - Fresh Water Flush</t>
         </is>
       </c>
       <c r="D72" s="6" t="inlineStr">
@@ -6763,11 +6765,11 @@
       </c>
       <c r="E72" s="6" t="inlineStr">
         <is>
-          <t>Fri 16 Oct</t>
+          <t>Thu 15 Oct</t>
         </is>
       </c>
       <c r="F72" s="6" t="n">
-        <v>-32</v>
+        <v>-31</v>
       </c>
       <c r="G72" s="6" t="inlineStr">
         <is>
@@ -6776,7 +6778,7 @@
       </c>
       <c r="H72" s="6" t="inlineStr">
         <is>
-          <t>WC19 on site on the record</t>
+          <t>WC47 on site on the record</t>
         </is>
       </c>
     </row>
@@ -6787,11 +6789,11 @@
         </is>
       </c>
       <c r="B73" s="6" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>WC25 Toilet Portable - Fresh Water Flush</t>
+          <t>WC19 Toilet Portable - Fresh Water Flush</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
@@ -6801,11 +6803,11 @@
       </c>
       <c r="E73" s="6" t="inlineStr">
         <is>
-          <t>Thu 15 Oct</t>
+          <t>Fri 16 Oct</t>
         </is>
       </c>
       <c r="F73" s="6" t="n">
-        <v>-31</v>
+        <v>-32</v>
       </c>
       <c r="G73" s="6" t="inlineStr">
         <is>
@@ -6814,7 +6816,7 @@
       </c>
       <c r="H73" s="6" t="inlineStr">
         <is>
-          <t>WC25 on site on the record</t>
+          <t>WC19 on site on the record</t>
         </is>
       </c>
     </row>
@@ -6825,11 +6827,11 @@
         </is>
       </c>
       <c r="B74" s="6" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>WC23 Toilet Portable - Fresh Water Flush</t>
+          <t>WC25 Toilet Portable - Fresh Water Flush</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr">
@@ -6852,7 +6854,7 @@
       </c>
       <c r="H74" s="6" t="inlineStr">
         <is>
-          <t>WC23 on site on the record</t>
+          <t>WC25 on site on the record</t>
         </is>
       </c>
     </row>
@@ -6863,11 +6865,11 @@
         </is>
       </c>
       <c r="B75" s="6" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>WC26 Toilet Portable - Fresh Water Flush</t>
+          <t>WC23 Toilet Portable - Fresh Water Flush</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr">
@@ -6890,7 +6892,7 @@
       </c>
       <c r="H75" s="6" t="inlineStr">
         <is>
-          <t>WC26 on site on the record</t>
+          <t>WC23 on site on the record</t>
         </is>
       </c>
     </row>
@@ -6901,11 +6903,11 @@
         </is>
       </c>
       <c r="B76" s="6" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>WC24 Toilet Portable - Fresh Water Flush</t>
+          <t>WC26 Toilet Portable - Fresh Water Flush</t>
         </is>
       </c>
       <c r="D76" s="6" t="inlineStr">
@@ -6928,7 +6930,7 @@
       </c>
       <c r="H76" s="6" t="inlineStr">
         <is>
-          <t>WC24 on site on the record</t>
+          <t>WC26 on site on the record</t>
         </is>
       </c>
     </row>
@@ -6939,11 +6941,11 @@
         </is>
       </c>
       <c r="B77" s="6" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>WC13 Toilet Portable - Fresh Water Flush</t>
+          <t>WC24 Toilet Portable - Fresh Water Flush</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr">
@@ -6966,7 +6968,7 @@
       </c>
       <c r="H77" s="6" t="inlineStr">
         <is>
-          <t>WC13 on site on the record</t>
+          <t>WC24 on site on the record</t>
         </is>
       </c>
     </row>
@@ -6977,11 +6979,11 @@
         </is>
       </c>
       <c r="B78" s="6" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>WC28 Toilet Portable - Fresh Water Flush</t>
+          <t>WC13 Toilet Portable - Fresh Water Flush</t>
         </is>
       </c>
       <c r="D78" s="6" t="inlineStr">
@@ -7004,7 +7006,7 @@
       </c>
       <c r="H78" s="6" t="inlineStr">
         <is>
-          <t>WC28 on site on the record</t>
+          <t>WC13 on site on the record</t>
         </is>
       </c>
     </row>
@@ -7015,11 +7017,11 @@
         </is>
       </c>
       <c r="B79" s="6" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>WC29 Toilet Portable - Fresh Water Flush</t>
+          <t>WC28 Toilet Portable - Fresh Water Flush</t>
         </is>
       </c>
       <c r="D79" s="6" t="inlineStr">
@@ -7042,7 +7044,7 @@
       </c>
       <c r="H79" s="6" t="inlineStr">
         <is>
-          <t>WC29 on site on the record</t>
+          <t>WC28 on site on the record</t>
         </is>
       </c>
     </row>
@@ -7053,11 +7055,11 @@
         </is>
       </c>
       <c r="B80" s="6" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>WC30 Toilet Portable - Fresh Water Flush</t>
+          <t>WC29 Toilet Portable - Fresh Water Flush</t>
         </is>
       </c>
       <c r="D80" s="6" t="inlineStr">
@@ -7067,11 +7069,11 @@
       </c>
       <c r="E80" s="6" t="inlineStr">
         <is>
-          <t>Fri 16 Oct</t>
+          <t>Thu 15 Oct</t>
         </is>
       </c>
       <c r="F80" s="6" t="n">
-        <v>-32</v>
+        <v>-31</v>
       </c>
       <c r="G80" s="6" t="inlineStr">
         <is>
@@ -7080,7 +7082,7 @@
       </c>
       <c r="H80" s="6" t="inlineStr">
         <is>
-          <t>WC30 on site on the record</t>
+          <t>WC29 on site on the record</t>
         </is>
       </c>
     </row>
@@ -7091,11 +7093,11 @@
         </is>
       </c>
       <c r="B81" s="6" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>WC35 Toilet Portable - Fresh Water Flush</t>
+          <t>WC30 Toilet Portable - Fresh Water Flush</t>
         </is>
       </c>
       <c r="D81" s="6" t="inlineStr">
@@ -7118,7 +7120,7 @@
       </c>
       <c r="H81" s="6" t="inlineStr">
         <is>
-          <t>WC35 on site on the record</t>
+          <t>WC30 on site on the record</t>
         </is>
       </c>
     </row>
@@ -7129,11 +7131,11 @@
         </is>
       </c>
       <c r="B82" s="6" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
-          <t>WC46 Toilet Portable - Fresh Water Flush</t>
+          <t>WC35 Toilet Portable - Fresh Water Flush</t>
         </is>
       </c>
       <c r="D82" s="6" t="inlineStr">
@@ -7156,7 +7158,7 @@
       </c>
       <c r="H82" s="6" t="inlineStr">
         <is>
-          <t>WC46 on site on the record</t>
+          <t>WC35 on site on the record</t>
         </is>
       </c>
     </row>
@@ -7167,11 +7169,11 @@
         </is>
       </c>
       <c r="B83" s="6" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>WC55 Toilet Portable - Fresh Water Flush</t>
+          <t>WC46 Toilet Portable - Fresh Water Flush</t>
         </is>
       </c>
       <c r="D83" s="6" t="inlineStr">
@@ -7181,11 +7183,11 @@
       </c>
       <c r="E83" s="6" t="inlineStr">
         <is>
-          <t>Thu 15 Oct</t>
+          <t>Fri 16 Oct</t>
         </is>
       </c>
       <c r="F83" s="6" t="n">
-        <v>-31</v>
+        <v>-32</v>
       </c>
       <c r="G83" s="6" t="inlineStr">
         <is>
@@ -7194,7 +7196,7 @@
       </c>
       <c r="H83" s="6" t="inlineStr">
         <is>
-          <t>WC55 on site on the record</t>
+          <t>WC46 on site on the record</t>
         </is>
       </c>
     </row>
@@ -7205,11 +7207,11 @@
         </is>
       </c>
       <c r="B84" s="6" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
-          <t>WC62 Toilet Portable - Fresh Water Flush</t>
+          <t>WC55 Toilet Portable - Fresh Water Flush</t>
         </is>
       </c>
       <c r="D84" s="6" t="inlineStr">
@@ -7219,11 +7221,11 @@
       </c>
       <c r="E84" s="6" t="inlineStr">
         <is>
-          <t>Fri 16 Oct</t>
+          <t>Thu 15 Oct</t>
         </is>
       </c>
       <c r="F84" s="6" t="n">
-        <v>-32</v>
+        <v>-31</v>
       </c>
       <c r="G84" s="6" t="inlineStr">
         <is>
@@ -7232,7 +7234,7 @@
       </c>
       <c r="H84" s="6" t="inlineStr">
         <is>
-          <t>WC62 on site on the record</t>
+          <t>WC55 on site on the record</t>
         </is>
       </c>
     </row>
@@ -7243,11 +7245,11 @@
         </is>
       </c>
       <c r="B85" s="6" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>WC65 Toilet Portable - Fresh Water Flush</t>
+          <t>WC62 Toilet Portable - Fresh Water Flush</t>
         </is>
       </c>
       <c r="D85" s="6" t="inlineStr">
@@ -7270,7 +7272,7 @@
       </c>
       <c r="H85" s="6" t="inlineStr">
         <is>
-          <t>WC65 on site on the record</t>
+          <t>WC62 on site on the record</t>
         </is>
       </c>
     </row>
@@ -7281,11 +7283,11 @@
         </is>
       </c>
       <c r="B86" s="6" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C86" s="6" t="inlineStr">
         <is>
-          <t>WC68 Toilet Portable - Fresh Water Flush</t>
+          <t>WC65 Toilet Portable - Fresh Water Flush</t>
         </is>
       </c>
       <c r="D86" s="6" t="inlineStr">
@@ -7295,11 +7297,11 @@
       </c>
       <c r="E86" s="6" t="inlineStr">
         <is>
-          <t>Tue 13 Oct</t>
+          <t>Fri 16 Oct</t>
         </is>
       </c>
       <c r="F86" s="6" t="n">
-        <v>-29</v>
+        <v>-32</v>
       </c>
       <c r="G86" s="6" t="inlineStr">
         <is>
@@ -7308,7 +7310,7 @@
       </c>
       <c r="H86" s="6" t="inlineStr">
         <is>
-          <t>WC68 on site on the record</t>
+          <t>WC65 on site on the record</t>
         </is>
       </c>
     </row>
@@ -7319,11 +7321,11 @@
         </is>
       </c>
       <c r="B87" s="6" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>WC72 Toilet Portable - Fresh Water Flush</t>
+          <t>WC68 Toilet Portable - Fresh Water Flush</t>
         </is>
       </c>
       <c r="D87" s="6" t="inlineStr">
@@ -7346,7 +7348,7 @@
       </c>
       <c r="H87" s="6" t="inlineStr">
         <is>
-          <t>WC72 on site on the record</t>
+          <t>WC68 on site on the record</t>
         </is>
       </c>
     </row>
@@ -7357,11 +7359,11 @@
         </is>
       </c>
       <c r="B88" s="6" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>WC73 Toilet Portable - Fresh Water Flush</t>
+          <t>WC72 Toilet Portable - Fresh Water Flush</t>
         </is>
       </c>
       <c r="D88" s="6" t="inlineStr">
@@ -7384,7 +7386,7 @@
       </c>
       <c r="H88" s="6" t="inlineStr">
         <is>
-          <t>WC73 on site on the record</t>
+          <t>WC72 on site on the record</t>
         </is>
       </c>
     </row>
@@ -7395,11 +7397,11 @@
         </is>
       </c>
       <c r="B89" s="6" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>WC85 Toilet Portable - Fresh Water Flush</t>
+          <t>WC73 Toilet Portable - Fresh Water Flush</t>
         </is>
       </c>
       <c r="D89" s="6" t="inlineStr">
@@ -7409,11 +7411,11 @@
       </c>
       <c r="E89" s="6" t="inlineStr">
         <is>
-          <t>Fri 16 Oct</t>
+          <t>Tue 13 Oct</t>
         </is>
       </c>
       <c r="F89" s="6" t="n">
-        <v>-32</v>
+        <v>-29</v>
       </c>
       <c r="G89" s="6" t="inlineStr">
         <is>
@@ -7422,7 +7424,7 @@
       </c>
       <c r="H89" s="6" t="inlineStr">
         <is>
-          <t>WC85 on site on the record</t>
+          <t>WC73 on site on the record</t>
         </is>
       </c>
     </row>
@@ -7433,11 +7435,11 @@
         </is>
       </c>
       <c r="B90" s="6" t="n">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="C90" s="6" t="inlineStr">
         <is>
-          <t>WC67 Toilet Portable - Fresh Water Flush</t>
+          <t>WC85 Toilet Portable - Fresh Water Flush</t>
         </is>
       </c>
       <c r="D90" s="6" t="inlineStr">
@@ -7447,11 +7449,11 @@
       </c>
       <c r="E90" s="6" t="inlineStr">
         <is>
-          <t>Thu 01 Oct</t>
+          <t>Fri 16 Oct</t>
         </is>
       </c>
       <c r="F90" s="6" t="n">
-        <v>-17</v>
+        <v>-32</v>
       </c>
       <c r="G90" s="6" t="inlineStr">
         <is>
@@ -7460,7 +7462,7 @@
       </c>
       <c r="H90" s="6" t="inlineStr">
         <is>
-          <t>WC67 on site on the record</t>
+          <t>WC85 on site on the record</t>
         </is>
       </c>
     </row>
@@ -7471,25 +7473,25 @@
         </is>
       </c>
       <c r="B91" s="6" t="n">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>PG01 FWF Toilet</t>
+          <t>WC67 Toilet Portable - Fresh Water Flush</t>
         </is>
       </c>
       <c r="D91" s="6" t="inlineStr">
         <is>
-          <t>Thu 22 Oct</t>
+          <t>Mon 14 Sep</t>
         </is>
       </c>
       <c r="E91" s="6" t="inlineStr">
         <is>
-          <t>Fri 16 Oct</t>
+          <t>Thu 01 Oct</t>
         </is>
       </c>
       <c r="F91" s="6" t="n">
-        <v>6</v>
+        <v>-17</v>
       </c>
       <c r="G91" s="6" t="inlineStr">
         <is>
@@ -7498,7 +7500,7 @@
       </c>
       <c r="H91" s="6" t="inlineStr">
         <is>
-          <t>PG01 on site on the record</t>
+          <t>WC67 on site on the record</t>
         </is>
       </c>
     </row>
@@ -7509,11 +7511,11 @@
         </is>
       </c>
       <c r="B92" s="6" t="n">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C92" s="6" t="inlineStr">
         <is>
-          <t>PG03 FWF Toilet</t>
+          <t>PG01 FWF Toilet</t>
         </is>
       </c>
       <c r="D92" s="6" t="inlineStr">
@@ -7536,7 +7538,7 @@
       </c>
       <c r="H92" s="6" t="inlineStr">
         <is>
-          <t>PG03 on site on the record</t>
+          <t>PG01 on site on the record</t>
         </is>
       </c>
     </row>
@@ -7547,11 +7549,11 @@
         </is>
       </c>
       <c r="B93" s="6" t="n">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>PG05 FWF Toilet</t>
+          <t>PG03 FWF Toilet</t>
         </is>
       </c>
       <c r="D93" s="6" t="inlineStr">
@@ -7574,7 +7576,7 @@
       </c>
       <c r="H93" s="6" t="inlineStr">
         <is>
-          <t>PG05 on site on the record</t>
+          <t>PG03 on site on the record</t>
         </is>
       </c>
     </row>
@@ -7585,11 +7587,11 @@
         </is>
       </c>
       <c r="B94" s="6" t="n">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C94" s="6" t="inlineStr">
         <is>
-          <t>PG29 Toilet FWF</t>
+          <t>PG05 FWF Toilet</t>
         </is>
       </c>
       <c r="D94" s="6" t="inlineStr">
@@ -7612,7 +7614,7 @@
       </c>
       <c r="H94" s="6" t="inlineStr">
         <is>
-          <t>PG29 on site on the record</t>
+          <t>PG05 on site on the record</t>
         </is>
       </c>
     </row>
@@ -7623,11 +7625,11 @@
         </is>
       </c>
       <c r="B95" s="6" t="n">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>WC42 FWF Toilet</t>
+          <t>PG29 Toilet FWF</t>
         </is>
       </c>
       <c r="D95" s="6" t="inlineStr">
@@ -7637,11 +7639,11 @@
       </c>
       <c r="E95" s="6" t="inlineStr">
         <is>
-          <t>Mon 28 Sep</t>
+          <t>Fri 16 Oct</t>
         </is>
       </c>
       <c r="F95" s="6" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="G95" s="6" t="inlineStr">
         <is>
@@ -7650,7 +7652,7 @@
       </c>
       <c r="H95" s="6" t="inlineStr">
         <is>
-          <t>WC42 on site on the record</t>
+          <t>PG29 on site on the record</t>
         </is>
       </c>
     </row>
@@ -7661,11 +7663,11 @@
         </is>
       </c>
       <c r="B96" s="6" t="n">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C96" s="6" t="inlineStr">
         <is>
-          <t>WC53 FWF Toilet</t>
+          <t>WC42 FWF Toilet</t>
         </is>
       </c>
       <c r="D96" s="6" t="inlineStr">
@@ -7675,11 +7677,11 @@
       </c>
       <c r="E96" s="6" t="inlineStr">
         <is>
-          <t>Wed 14 Oct</t>
+          <t>Mon 28 Sep</t>
         </is>
       </c>
       <c r="F96" s="6" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="G96" s="6" t="inlineStr">
         <is>
@@ -7688,7 +7690,7 @@
       </c>
       <c r="H96" s="6" t="inlineStr">
         <is>
-          <t>WC53 on site on the record</t>
+          <t>WC42 on site on the record</t>
         </is>
       </c>
     </row>
@@ -7699,11 +7701,11 @@
         </is>
       </c>
       <c r="B97" s="6" t="n">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
-          <t>WC81 FWF Toilet</t>
+          <t>WC53 FWF Toilet</t>
         </is>
       </c>
       <c r="D97" s="6" t="inlineStr">
@@ -7713,11 +7715,11 @@
       </c>
       <c r="E97" s="6" t="inlineStr">
         <is>
-          <t>Mon 14 Sep</t>
+          <t>Wed 14 Oct</t>
         </is>
       </c>
       <c r="F97" s="6" t="n">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="G97" s="6" t="inlineStr">
         <is>
@@ -7726,7 +7728,7 @@
       </c>
       <c r="H97" s="6" t="inlineStr">
         <is>
-          <t>WC81 on site on the record</t>
+          <t>WC53 on site on the record</t>
         </is>
       </c>
     </row>
@@ -7737,11 +7739,11 @@
         </is>
       </c>
       <c r="B98" s="6" t="n">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C98" s="6" t="inlineStr">
         <is>
-          <t>WC12 Toilet Portable - Fresh Water Flush</t>
+          <t>WC81 FWF Toilet</t>
         </is>
       </c>
       <c r="D98" s="6" t="inlineStr">
@@ -7764,36 +7766,36 @@
       </c>
       <c r="H98" s="6" t="inlineStr">
         <is>
-          <t>WC12 on site on the record</t>
+          <t>WC81 on site on the record</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="6" t="inlineStr">
         <is>
-          <t>9968929</t>
+          <t>9968955</t>
         </is>
       </c>
       <c r="B99" s="6" t="n">
-        <v>1</v>
+        <v>158</v>
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>Portable Building Shell 4.8M x 3.0M</t>
+          <t>WC12 Toilet Portable - Fresh Water Flush</t>
         </is>
       </c>
       <c r="D99" s="6" t="inlineStr">
         <is>
+          <t>Thu 22 Oct</t>
+        </is>
+      </c>
+      <c r="E99" s="6" t="inlineStr">
+        <is>
           <t>Mon 14 Sep</t>
         </is>
       </c>
-      <c r="E99" s="6" t="inlineStr">
-        <is>
-          <t>Wed 16 Sep</t>
-        </is>
-      </c>
       <c r="F99" s="6" t="n">
-        <v>-2</v>
+        <v>38</v>
       </c>
       <c r="G99" s="6" t="inlineStr">
         <is>
@@ -7802,7 +7804,7 @@
       </c>
       <c r="H99" s="6" t="inlineStr">
         <is>
-          <t>T0021 on site on the record</t>
+          <t>WC12 on site on the record</t>
         </is>
       </c>
     </row>
@@ -7813,11 +7815,11 @@
         </is>
       </c>
       <c r="B100" s="6" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C100" s="6" t="inlineStr">
         <is>
-          <t>Toilet Portable - Fresh Water Flush</t>
+          <t>Portable Building Shell 4.8M x 3.0M</t>
         </is>
       </c>
       <c r="D100" s="6" t="inlineStr">
@@ -7827,11 +7829,11 @@
       </c>
       <c r="E100" s="6" t="inlineStr">
         <is>
-          <t>Sat 26 Sep</t>
+          <t>Wed 16 Sep</t>
         </is>
       </c>
       <c r="F100" s="6" t="n">
-        <v>-12</v>
+        <v>-2</v>
       </c>
       <c r="G100" s="6" t="inlineStr">
         <is>
@@ -7840,22 +7842,22 @@
       </c>
       <c r="H100" s="6" t="inlineStr">
         <is>
-          <t>T0024 on site on the record</t>
+          <t>T0021 on site on the record</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="6" t="inlineStr">
         <is>
-          <t>9968862</t>
+          <t>9968929</t>
         </is>
       </c>
       <c r="B101" s="6" t="n">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="C101" s="6" t="inlineStr">
         <is>
-          <t>P09 Portable Building Shell 6.0M x 3.0M - Cyclonic</t>
+          <t>Toilet Portable - Fresh Water Flush</t>
         </is>
       </c>
       <c r="D101" s="6" t="inlineStr">
@@ -7865,11 +7867,11 @@
       </c>
       <c r="E101" s="6" t="inlineStr">
         <is>
-          <t>Wed 16 Sep</t>
+          <t>Sat 26 Sep</t>
         </is>
       </c>
       <c r="F101" s="6" t="n">
-        <v>-2</v>
+        <v>-12</v>
       </c>
       <c r="G101" s="6" t="inlineStr">
         <is>
@@ -7878,7 +7880,7 @@
       </c>
       <c r="H101" s="6" t="inlineStr">
         <is>
-          <t>P09 on site on the record</t>
+          <t>T0024 on site on the record</t>
         </is>
       </c>
     </row>
@@ -7889,11 +7891,11 @@
         </is>
       </c>
       <c r="B102" s="6" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C102" s="6" t="inlineStr">
         <is>
-          <t>P17 Portable Building Shell Cyclone Rated 9.6m x 3</t>
+          <t>P09 Portable Building Shell 6.0M x 3.0M - Cyclonic</t>
         </is>
       </c>
       <c r="D102" s="6" t="inlineStr">
@@ -7916,7 +7918,7 @@
       </c>
       <c r="H102" s="6" t="inlineStr">
         <is>
-          <t>P17 on site on the record</t>
+          <t>P09 on site on the record</t>
         </is>
       </c>
     </row>
@@ -7927,11 +7929,11 @@
         </is>
       </c>
       <c r="B103" s="6" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C103" s="6" t="inlineStr">
         <is>
-          <t>P19 Portable Building Shell 6.0M x 3.0M</t>
+          <t>P17 Portable Building Shell Cyclone Rated 9.6m x 3</t>
         </is>
       </c>
       <c r="D103" s="6" t="inlineStr">
@@ -7954,7 +7956,7 @@
       </c>
       <c r="H103" s="6" t="inlineStr">
         <is>
-          <t>P19 on site on the record</t>
+          <t>P17 on site on the record</t>
         </is>
       </c>
     </row>
@@ -7965,11 +7967,11 @@
         </is>
       </c>
       <c r="B104" s="6" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C104" s="6" t="inlineStr">
         <is>
-          <t>P18 Portable Building Shell 4.8M x 2.4M</t>
+          <t>P19 Portable Building Shell 6.0M x 3.0M</t>
         </is>
       </c>
       <c r="D104" s="6" t="inlineStr">
@@ -7992,7 +7994,7 @@
       </c>
       <c r="H104" s="6" t="inlineStr">
         <is>
-          <t>P18 on site on the record</t>
+          <t>P19 on site on the record</t>
         </is>
       </c>
     </row>
@@ -8003,11 +8005,11 @@
         </is>
       </c>
       <c r="B105" s="6" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C105" s="6" t="inlineStr">
         <is>
-          <t>P20 Portable Building Shell 4.8M x 2.4M</t>
+          <t>P18 Portable Building Shell 4.8M x 2.4M</t>
         </is>
       </c>
       <c r="D105" s="6" t="inlineStr">
@@ -8030,7 +8032,7 @@
       </c>
       <c r="H105" s="6" t="inlineStr">
         <is>
-          <t>P20 on site on the record</t>
+          <t>P18 on site on the record</t>
         </is>
       </c>
     </row>
@@ -8041,11 +8043,11 @@
         </is>
       </c>
       <c r="B106" s="6" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="C106" s="6" t="inlineStr">
         <is>
-          <t>P10 Portable Building Shell 4.8M x 2.4M</t>
+          <t>P20 Portable Building Shell 4.8M x 2.4M</t>
         </is>
       </c>
       <c r="D106" s="6" t="inlineStr">
@@ -8055,11 +8057,11 @@
       </c>
       <c r="E106" s="6" t="inlineStr">
         <is>
-          <t>Thu 17 Sep</t>
+          <t>Wed 16 Sep</t>
         </is>
       </c>
       <c r="F106" s="6" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="G106" s="6" t="inlineStr">
         <is>
@@ -8068,7 +8070,7 @@
       </c>
       <c r="H106" s="6" t="inlineStr">
         <is>
-          <t>P10 on site on the record</t>
+          <t>P20 on site on the record</t>
         </is>
       </c>
     </row>
@@ -8079,11 +8081,11 @@
         </is>
       </c>
       <c r="B107" s="6" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C107" s="6" t="inlineStr">
         <is>
-          <t>P11 Portable Building Shell 4.8M x 2.4M</t>
+          <t>P10 Portable Building Shell 4.8M x 2.4M</t>
         </is>
       </c>
       <c r="D107" s="6" t="inlineStr">
@@ -8106,7 +8108,7 @@
       </c>
       <c r="H107" s="6" t="inlineStr">
         <is>
-          <t>P11 on site on the record</t>
+          <t>P10 on site on the record</t>
         </is>
       </c>
     </row>
@@ -8117,11 +8119,11 @@
         </is>
       </c>
       <c r="B108" s="6" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C108" s="6" t="inlineStr">
         <is>
-          <t>P12 Portable Building Shell 4.8M x 2.4M</t>
+          <t>P11 Portable Building Shell 4.8M x 2.4M</t>
         </is>
       </c>
       <c r="D108" s="6" t="inlineStr">
@@ -8144,7 +8146,7 @@
       </c>
       <c r="H108" s="6" t="inlineStr">
         <is>
-          <t>P12 on site on the record</t>
+          <t>P11 on site on the record</t>
         </is>
       </c>
     </row>
@@ -8155,11 +8157,11 @@
         </is>
       </c>
       <c r="B109" s="6" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C109" s="6" t="inlineStr">
         <is>
-          <t>P37 Portable Building Shell 6.0M x 3.0M</t>
+          <t>P12 Portable Building Shell 4.8M x 2.4M</t>
         </is>
       </c>
       <c r="D109" s="6" t="inlineStr">
@@ -8182,7 +8184,7 @@
       </c>
       <c r="H109" s="6" t="inlineStr">
         <is>
-          <t>P37 on site on the record</t>
+          <t>P12 on site on the record</t>
         </is>
       </c>
     </row>
@@ -8193,11 +8195,11 @@
         </is>
       </c>
       <c r="B110" s="6" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C110" s="6" t="inlineStr">
         <is>
-          <t>P13 Portable Building Shell 4.8M x 2.4M</t>
+          <t>P37 Portable Building Shell 6.0M x 3.0M</t>
         </is>
       </c>
       <c r="D110" s="6" t="inlineStr">
@@ -8207,11 +8209,11 @@
       </c>
       <c r="E110" s="6" t="inlineStr">
         <is>
-          <t>Mon 21 Sep</t>
+          <t>Thu 17 Sep</t>
         </is>
       </c>
       <c r="F110" s="6" t="n">
-        <v>-7</v>
+        <v>-3</v>
       </c>
       <c r="G110" s="6" t="inlineStr">
         <is>
@@ -8220,7 +8222,7 @@
       </c>
       <c r="H110" s="6" t="inlineStr">
         <is>
-          <t>P13 on site on the record</t>
+          <t>P37 on site on the record</t>
         </is>
       </c>
     </row>
@@ -8231,11 +8233,11 @@
         </is>
       </c>
       <c r="B111" s="6" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C111" s="6" t="inlineStr">
         <is>
-          <t>P14 Portable Building Shell 4.8M x 2.4M</t>
+          <t>P13 Portable Building Shell 4.8M x 2.4M</t>
         </is>
       </c>
       <c r="D111" s="6" t="inlineStr">
@@ -8258,7 +8260,7 @@
       </c>
       <c r="H111" s="6" t="inlineStr">
         <is>
-          <t>P14 on site on the record</t>
+          <t>P13 on site on the record</t>
         </is>
       </c>
     </row>
@@ -8269,11 +8271,11 @@
         </is>
       </c>
       <c r="B112" s="6" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C112" s="6" t="inlineStr">
         <is>
-          <t>P15 Portable Building Shell 4.8M x 2.4M</t>
+          <t>P14 Portable Building Shell 4.8M x 2.4M</t>
         </is>
       </c>
       <c r="D112" s="6" t="inlineStr">
@@ -8296,7 +8298,7 @@
       </c>
       <c r="H112" s="6" t="inlineStr">
         <is>
-          <t>P15 on site on the record</t>
+          <t>P14 on site on the record</t>
         </is>
       </c>
     </row>
@@ -8307,11 +8309,11 @@
         </is>
       </c>
       <c r="B113" s="6" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C113" s="6" t="inlineStr">
         <is>
-          <t>P16 Portable Building Shell 4.8M x 2.4M</t>
+          <t>P15 Portable Building Shell 4.8M x 2.4M</t>
         </is>
       </c>
       <c r="D113" s="6" t="inlineStr">
@@ -8334,7 +8336,7 @@
       </c>
       <c r="H113" s="6" t="inlineStr">
         <is>
-          <t>P16 on site on the record</t>
+          <t>P15 on site on the record</t>
         </is>
       </c>
     </row>
@@ -8345,11 +8347,11 @@
         </is>
       </c>
       <c r="B114" s="6" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C114" s="6" t="inlineStr">
         <is>
-          <t>P58 Portable Building Shell 6.0M x 3.0M - Cyclonic</t>
+          <t>P16 Portable Building Shell 4.8M x 2.4M</t>
         </is>
       </c>
       <c r="D114" s="6" t="inlineStr">
@@ -8359,11 +8361,11 @@
       </c>
       <c r="E114" s="6" t="inlineStr">
         <is>
-          <t>Wed 23 Sep</t>
+          <t>Mon 21 Sep</t>
         </is>
       </c>
       <c r="F114" s="6" t="n">
-        <v>-9</v>
+        <v>-7</v>
       </c>
       <c r="G114" s="6" t="inlineStr">
         <is>
@@ -8372,7 +8374,7 @@
       </c>
       <c r="H114" s="6" t="inlineStr">
         <is>
-          <t>P58 on site on the record</t>
+          <t>P16 on site on the record</t>
         </is>
       </c>
     </row>
@@ -8383,11 +8385,11 @@
         </is>
       </c>
       <c r="B115" s="6" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C115" s="6" t="inlineStr">
         <is>
-          <t>P44 Portable Building Shell 6.0M x 3.0M</t>
+          <t>P58 Portable Building Shell 6.0M x 3.0M - Cyclonic</t>
         </is>
       </c>
       <c r="D115" s="6" t="inlineStr">
@@ -8397,11 +8399,11 @@
       </c>
       <c r="E115" s="6" t="inlineStr">
         <is>
-          <t>Thu 24 Sep</t>
+          <t>Wed 23 Sep</t>
         </is>
       </c>
       <c r="F115" s="6" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="G115" s="6" t="inlineStr">
         <is>
@@ -8410,7 +8412,7 @@
       </c>
       <c r="H115" s="6" t="inlineStr">
         <is>
-          <t>P44 on site on the record</t>
+          <t>P58 on site on the record</t>
         </is>
       </c>
     </row>
@@ -8421,11 +8423,11 @@
         </is>
       </c>
       <c r="B116" s="6" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C116" s="6" t="inlineStr">
         <is>
-          <t>P41 Portable Building Shell 6.0M x 3.0M</t>
+          <t>P44 Portable Building Shell 6.0M x 3.0M</t>
         </is>
       </c>
       <c r="D116" s="6" t="inlineStr">
@@ -8435,11 +8437,11 @@
       </c>
       <c r="E116" s="6" t="inlineStr">
         <is>
-          <t>Tue 22 Sep</t>
+          <t>Thu 24 Sep</t>
         </is>
       </c>
       <c r="F116" s="6" t="n">
-        <v>-8</v>
+        <v>-10</v>
       </c>
       <c r="G116" s="6" t="inlineStr">
         <is>
@@ -8448,7 +8450,7 @@
       </c>
       <c r="H116" s="6" t="inlineStr">
         <is>
-          <t>P41 on site on the record</t>
+          <t>P44 on site on the record</t>
         </is>
       </c>
     </row>
@@ -8459,11 +8461,11 @@
         </is>
       </c>
       <c r="B117" s="6" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C117" s="6" t="inlineStr">
         <is>
-          <t>P06 Portable Building Shell 6.0M x 3.0M</t>
+          <t>P41 Portable Building Shell 6.0M x 3.0M</t>
         </is>
       </c>
       <c r="D117" s="6" t="inlineStr">
@@ -8473,11 +8475,11 @@
       </c>
       <c r="E117" s="6" t="inlineStr">
         <is>
-          <t>Mon 28 Sep</t>
+          <t>Tue 22 Sep</t>
         </is>
       </c>
       <c r="F117" s="6" t="n">
-        <v>-14</v>
+        <v>-8</v>
       </c>
       <c r="G117" s="6" t="inlineStr">
         <is>
@@ -8486,7 +8488,7 @@
       </c>
       <c r="H117" s="6" t="inlineStr">
         <is>
-          <t>P06 on site on the record</t>
+          <t>P41 on site on the record</t>
         </is>
       </c>
     </row>
@@ -8497,11 +8499,11 @@
         </is>
       </c>
       <c r="B118" s="6" t="n">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="C118" s="6" t="inlineStr">
         <is>
-          <t>P52 Portable Building Shell 12.0M x 3.0M - Cycloni</t>
+          <t>P06 Portable Building Shell 6.0M x 3.0M</t>
         </is>
       </c>
       <c r="D118" s="6" t="inlineStr">
@@ -8511,11 +8513,11 @@
       </c>
       <c r="E118" s="6" t="inlineStr">
         <is>
-          <t>Wed 07 Oct</t>
+          <t>Mon 28 Sep</t>
         </is>
       </c>
       <c r="F118" s="6" t="n">
-        <v>-23</v>
+        <v>-14</v>
       </c>
       <c r="G118" s="6" t="inlineStr">
         <is>
@@ -8524,7 +8526,7 @@
       </c>
       <c r="H118" s="6" t="inlineStr">
         <is>
-          <t>P52 on site on the record</t>
+          <t>P06 on site on the record</t>
         </is>
       </c>
     </row>
@@ -8535,11 +8537,11 @@
         </is>
       </c>
       <c r="B119" s="6" t="n">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="C119" s="6" t="inlineStr">
         <is>
-          <t>P54 Portable Building Shell 6.0M x 3.0M - Cyclonic</t>
+          <t>P52 Portable Building Shell 12.0M x 3.0M - Cycloni</t>
         </is>
       </c>
       <c r="D119" s="6" t="inlineStr">
@@ -8562,7 +8564,7 @@
       </c>
       <c r="H119" s="6" t="inlineStr">
         <is>
-          <t>P54 on site on the record</t>
+          <t>P52 on site on the record</t>
         </is>
       </c>
     </row>
@@ -8573,11 +8575,11 @@
         </is>
       </c>
       <c r="B120" s="6" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C120" s="6" t="inlineStr">
         <is>
-          <t>P55 Ticket Office 6.0Mx3.0M</t>
+          <t>P54 Portable Building Shell 6.0M x 3.0M - Cyclonic</t>
         </is>
       </c>
       <c r="D120" s="6" t="inlineStr">
@@ -8600,7 +8602,7 @@
       </c>
       <c r="H120" s="6" t="inlineStr">
         <is>
-          <t>P55 on site on the record</t>
+          <t>P54 on site on the record</t>
         </is>
       </c>
     </row>
@@ -8611,11 +8613,11 @@
         </is>
       </c>
       <c r="B121" s="6" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C121" s="6" t="inlineStr">
         <is>
-          <t>P56 Portable Building Shell Cyclone Rated 3.6m x 2</t>
+          <t>P55 Ticket Office 6.0Mx3.0M</t>
         </is>
       </c>
       <c r="D121" s="6" t="inlineStr">
@@ -8638,7 +8640,7 @@
       </c>
       <c r="H121" s="6" t="inlineStr">
         <is>
-          <t>P56 on site on the record</t>
+          <t>P55 on site on the record</t>
         </is>
       </c>
     </row>
@@ -8649,11 +8651,11 @@
         </is>
       </c>
       <c r="B122" s="6" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C122" s="6" t="inlineStr">
         <is>
-          <t>P57 Portable Building Shell Cyclone Rated 9.6m x 3</t>
+          <t>P56 Portable Building Shell Cyclone Rated 3.6m x 2</t>
         </is>
       </c>
       <c r="D122" s="6" t="inlineStr">
@@ -8676,7 +8678,7 @@
       </c>
       <c r="H122" s="6" t="inlineStr">
         <is>
-          <t>P57 on site on the record</t>
+          <t>P56 on site on the record</t>
         </is>
       </c>
     </row>
@@ -8687,11 +8689,11 @@
         </is>
       </c>
       <c r="B123" s="6" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C123" s="6" t="inlineStr">
         <is>
-          <t>P21 Portable Building Shell 6.0M x 3.0M - Cyclonic</t>
+          <t>P57 Portable Building Shell Cyclone Rated 9.6m x 3</t>
         </is>
       </c>
       <c r="D123" s="6" t="inlineStr">
@@ -8701,11 +8703,11 @@
       </c>
       <c r="E123" s="6" t="inlineStr">
         <is>
-          <t>Wed 16 Sep</t>
+          <t>Wed 07 Oct</t>
         </is>
       </c>
       <c r="F123" s="6" t="n">
-        <v>-2</v>
+        <v>-23</v>
       </c>
       <c r="G123" s="6" t="inlineStr">
         <is>
@@ -8714,7 +8716,7 @@
       </c>
       <c r="H123" s="6" t="inlineStr">
         <is>
-          <t>P21 on site on the record</t>
+          <t>P57 on site on the record</t>
         </is>
       </c>
     </row>
@@ -8725,11 +8727,11 @@
         </is>
       </c>
       <c r="B124" s="6" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C124" s="6" t="inlineStr">
         <is>
-          <t>P36 Portable Building Shell 6.0M x 3.0M</t>
+          <t>P21 Portable Building Shell 6.0M x 3.0M - Cyclonic</t>
         </is>
       </c>
       <c r="D124" s="6" t="inlineStr">
@@ -8739,11 +8741,11 @@
       </c>
       <c r="E124" s="6" t="inlineStr">
         <is>
-          <t>Thu 17 Sep</t>
+          <t>Wed 16 Sep</t>
         </is>
       </c>
       <c r="F124" s="6" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="G124" s="6" t="inlineStr">
         <is>
@@ -8752,7 +8754,7 @@
       </c>
       <c r="H124" s="6" t="inlineStr">
         <is>
-          <t>P36 on site on the record</t>
+          <t>P21 on site on the record</t>
         </is>
       </c>
     </row>
@@ -8763,11 +8765,11 @@
         </is>
       </c>
       <c r="B125" s="6" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C125" s="6" t="inlineStr">
         <is>
-          <t>P51 Portable Building Shell 12.0M x 3.0M - Cycloni</t>
+          <t>P36 Portable Building Shell 6.0M x 3.0M</t>
         </is>
       </c>
       <c r="D125" s="6" t="inlineStr">
@@ -8777,11 +8779,11 @@
       </c>
       <c r="E125" s="6" t="inlineStr">
         <is>
-          <t>Tue 06 Oct</t>
+          <t>Thu 17 Sep</t>
         </is>
       </c>
       <c r="F125" s="6" t="n">
-        <v>-22</v>
+        <v>-3</v>
       </c>
       <c r="G125" s="6" t="inlineStr">
         <is>
@@ -8790,7 +8792,7 @@
       </c>
       <c r="H125" s="6" t="inlineStr">
         <is>
-          <t>P51 on site on the record</t>
+          <t>P36 on site on the record</t>
         </is>
       </c>
     </row>
@@ -8801,11 +8803,11 @@
         </is>
       </c>
       <c r="B126" s="6" t="n">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="C126" s="6" t="inlineStr">
         <is>
-          <t>P46 Portable Building Shell 12.0M x 3.0M - Cycloni</t>
+          <t>P51 Portable Building Shell 12.0M x 3.0M - Cycloni</t>
         </is>
       </c>
       <c r="D126" s="6" t="inlineStr">
@@ -8828,7 +8830,7 @@
       </c>
       <c r="H126" s="6" t="inlineStr">
         <is>
-          <t>P46 on site on the record</t>
+          <t>P51 on site on the record</t>
         </is>
       </c>
     </row>
@@ -8839,11 +8841,11 @@
         </is>
       </c>
       <c r="B127" s="6" t="n">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C127" s="6" t="inlineStr">
         <is>
-          <t>P69 Portable Building Shell 6.0M x 3.0M</t>
+          <t>P46 Portable Building Shell 12.0M x 3.0M - Cycloni</t>
         </is>
       </c>
       <c r="D127" s="6" t="inlineStr">
@@ -8853,11 +8855,11 @@
       </c>
       <c r="E127" s="6" t="inlineStr">
         <is>
-          <t>Mon 12 Oct</t>
+          <t>Tue 06 Oct</t>
         </is>
       </c>
       <c r="F127" s="6" t="n">
-        <v>-28</v>
+        <v>-22</v>
       </c>
       <c r="G127" s="6" t="inlineStr">
         <is>
@@ -8866,7 +8868,7 @@
       </c>
       <c r="H127" s="6" t="inlineStr">
         <is>
-          <t>P69 on site on the record</t>
+          <t>P46 on site on the record</t>
         </is>
       </c>
     </row>
@@ -8877,11 +8879,11 @@
         </is>
       </c>
       <c r="B128" s="6" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C128" s="6" t="inlineStr">
         <is>
-          <t>P25 Portable Building Shell 6.0M x 3.0M - Cyclonic</t>
+          <t>P69 Portable Building Shell 6.0M x 3.0M</t>
         </is>
       </c>
       <c r="D128" s="6" t="inlineStr">
@@ -8891,11 +8893,11 @@
       </c>
       <c r="E128" s="6" t="inlineStr">
         <is>
-          <t>Wed 14 Oct</t>
+          <t>Mon 12 Oct</t>
         </is>
       </c>
       <c r="F128" s="6" t="n">
-        <v>-30</v>
+        <v>-28</v>
       </c>
       <c r="G128" s="6" t="inlineStr">
         <is>
@@ -8904,7 +8906,7 @@
       </c>
       <c r="H128" s="6" t="inlineStr">
         <is>
-          <t>P25 on site on the record</t>
+          <t>P69 on site on the record</t>
         </is>
       </c>
     </row>
@@ -8915,11 +8917,11 @@
         </is>
       </c>
       <c r="B129" s="6" t="n">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C129" s="6" t="inlineStr">
         <is>
-          <t>P67 Commentary Booth 6.0M x 3.0M</t>
+          <t>P25 Portable Building Shell 6.0M x 3.0M - Cyclonic</t>
         </is>
       </c>
       <c r="D129" s="6" t="inlineStr">
@@ -8942,7 +8944,7 @@
       </c>
       <c r="H129" s="6" t="inlineStr">
         <is>
-          <t>P67 on site on the record</t>
+          <t>P25 on site on the record</t>
         </is>
       </c>
     </row>
@@ -8953,11 +8955,11 @@
         </is>
       </c>
       <c r="B130" s="6" t="n">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C130" s="6" t="inlineStr">
         <is>
-          <t>P65 Portable Building Shell 6.0M x 3.0M - Cyclonic</t>
+          <t>P67 Commentary Booth 6.0M x 3.0M</t>
         </is>
       </c>
       <c r="D130" s="6" t="inlineStr">
@@ -8980,7 +8982,7 @@
       </c>
       <c r="H130" s="6" t="inlineStr">
         <is>
-          <t>P65 on site on the record</t>
+          <t>P67 on site on the record</t>
         </is>
       </c>
     </row>
@@ -8991,11 +8993,11 @@
         </is>
       </c>
       <c r="B131" s="6" t="n">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C131" s="6" t="inlineStr">
         <is>
-          <t>P66 Portable Building Shell 6.0M x 3.0M</t>
+          <t>P65 Portable Building Shell 6.0M x 3.0M - Cyclonic</t>
         </is>
       </c>
       <c r="D131" s="6" t="inlineStr">
@@ -9018,7 +9020,7 @@
       </c>
       <c r="H131" s="6" t="inlineStr">
         <is>
-          <t>P66 on site on the record</t>
+          <t>P65 on site on the record</t>
         </is>
       </c>
     </row>
@@ -9029,11 +9031,11 @@
         </is>
       </c>
       <c r="B132" s="6" t="n">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C132" s="6" t="inlineStr">
         <is>
-          <t>P60 Ticket Office 4.8Mx2.4M</t>
+          <t>P66 Portable Building Shell 6.0M x 3.0M</t>
         </is>
       </c>
       <c r="D132" s="6" t="inlineStr">
@@ -9043,11 +9045,11 @@
       </c>
       <c r="E132" s="6" t="inlineStr">
         <is>
-          <t>Thu 15 Oct</t>
+          <t>Wed 14 Oct</t>
         </is>
       </c>
       <c r="F132" s="6" t="n">
-        <v>-31</v>
+        <v>-30</v>
       </c>
       <c r="G132" s="6" t="inlineStr">
         <is>
@@ -9056,7 +9058,7 @@
       </c>
       <c r="H132" s="6" t="inlineStr">
         <is>
-          <t>P60 on site on the record</t>
+          <t>P66 on site on the record</t>
         </is>
       </c>
     </row>
@@ -9067,11 +9069,11 @@
         </is>
       </c>
       <c r="B133" s="6" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C133" s="6" t="inlineStr">
         <is>
-          <t>P62 Commentary Booth 6.0M x 3.0M</t>
+          <t>P60 Ticket Office 4.8Mx2.4M</t>
         </is>
       </c>
       <c r="D133" s="6" t="inlineStr">
@@ -9094,7 +9096,7 @@
       </c>
       <c r="H133" s="6" t="inlineStr">
         <is>
-          <t>P62 on site on the record</t>
+          <t>P60 on site on the record</t>
         </is>
       </c>
     </row>
@@ -9105,11 +9107,11 @@
         </is>
       </c>
       <c r="B134" s="6" t="n">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C134" s="6" t="inlineStr">
         <is>
-          <t>P63 Portable Building Shell 6.0M x 3.0M</t>
+          <t>P62 Commentary Booth 6.0M x 3.0M</t>
         </is>
       </c>
       <c r="D134" s="6" t="inlineStr">
@@ -9132,7 +9134,7 @@
       </c>
       <c r="H134" s="6" t="inlineStr">
         <is>
-          <t>P63 on site on the record</t>
+          <t>P62 on site on the record</t>
         </is>
       </c>
     </row>
@@ -9143,11 +9145,11 @@
         </is>
       </c>
       <c r="B135" s="6" t="n">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="C135" s="6" t="inlineStr">
         <is>
-          <t>P08 Portable Building Shell 6.0M x 3.0M</t>
+          <t>P63 Portable Building Shell 6.0M x 3.0M</t>
         </is>
       </c>
       <c r="D135" s="6" t="inlineStr">
@@ -9157,11 +9159,11 @@
       </c>
       <c r="E135" s="6" t="inlineStr">
         <is>
-          <t>Tue 06 Oct</t>
+          <t>Thu 15 Oct</t>
         </is>
       </c>
       <c r="F135" s="6" t="n">
-        <v>-22</v>
+        <v>-31</v>
       </c>
       <c r="G135" s="6" t="inlineStr">
         <is>
@@ -9170,7 +9172,7 @@
       </c>
       <c r="H135" s="6" t="inlineStr">
         <is>
-          <t>P08 on site on the record</t>
+          <t>P63 on site on the record</t>
         </is>
       </c>
     </row>
@@ -9181,11 +9183,11 @@
         </is>
       </c>
       <c r="B136" s="6" t="n">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C136" s="6" t="inlineStr">
         <is>
-          <t>P45 Portable Building Shell 6.0M x 3.0M</t>
+          <t>P08 Portable Building Shell 6.0M x 3.0M</t>
         </is>
       </c>
       <c r="D136" s="6" t="inlineStr">
@@ -9195,11 +9197,11 @@
       </c>
       <c r="E136" s="6" t="inlineStr">
         <is>
-          <t>Mon 12 Oct</t>
+          <t>Tue 06 Oct</t>
         </is>
       </c>
       <c r="F136" s="6" t="n">
-        <v>-28</v>
+        <v>-22</v>
       </c>
       <c r="G136" s="6" t="inlineStr">
         <is>
@@ -9208,36 +9210,36 @@
       </c>
       <c r="H136" s="6" t="inlineStr">
         <is>
-          <t>P45 on site on the record</t>
+          <t>P08 on site on the record</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="6" t="inlineStr">
         <is>
-          <t>9974042</t>
+          <t>9968862</t>
         </is>
       </c>
       <c r="B137" s="6" t="n">
-        <v>1</v>
+        <v>131</v>
       </c>
       <c r="C137" s="6" t="inlineStr">
         <is>
-          <t>Container  3.0M x 2.4M</t>
+          <t>P45 Portable Building Shell 6.0M x 3.0M</t>
         </is>
       </c>
       <c r="D137" s="6" t="inlineStr">
         <is>
-          <t>Mon 28 Sep</t>
+          <t>Mon 14 Sep</t>
         </is>
       </c>
       <c r="E137" s="6" t="inlineStr">
         <is>
-          <t>Wed 07 Oct</t>
+          <t>Mon 12 Oct</t>
         </is>
       </c>
       <c r="F137" s="6" t="n">
-        <v>-9</v>
+        <v>-28</v>
       </c>
       <c r="G137" s="6" t="inlineStr">
         <is>
@@ -9246,7 +9248,7 @@
       </c>
       <c r="H137" s="6" t="inlineStr">
         <is>
-          <t>T0258 on site on the record</t>
+          <t>P45 on site on the record</t>
         </is>
       </c>
     </row>
@@ -9257,11 +9259,11 @@
         </is>
       </c>
       <c r="B138" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C138" s="6" t="inlineStr">
         <is>
-          <t>Container - Refrigerated 6.0M x 2.4M</t>
+          <t>Container  3.0M x 2.4M</t>
         </is>
       </c>
       <c r="D138" s="6" t="inlineStr">
@@ -9271,11 +9273,11 @@
       </c>
       <c r="E138" s="6" t="inlineStr">
         <is>
-          <t>Tue 13 Oct</t>
+          <t>Wed 07 Oct</t>
         </is>
       </c>
       <c r="F138" s="6" t="n">
-        <v>-15</v>
+        <v>-9</v>
       </c>
       <c r="G138" s="6" t="inlineStr">
         <is>
@@ -9284,36 +9286,36 @@
       </c>
       <c r="H138" s="6" t="inlineStr">
         <is>
-          <t>T0266 on site on the record</t>
+          <t>T0258 on site on the record</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="6" t="inlineStr">
         <is>
-          <t>9961976</t>
+          <t>9974042</t>
         </is>
       </c>
       <c r="B139" s="6" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="C139" s="6" t="inlineStr">
         <is>
-          <t>COATES Forklift Rough Terrain 2.5t With Switchable</t>
+          <t>Container - Refrigerated 6.0M x 2.4M</t>
         </is>
       </c>
       <c r="D139" s="6" t="inlineStr">
         <is>
-          <t>Fri 11 Sep</t>
+          <t>Mon 28 Sep</t>
         </is>
       </c>
       <c r="E139" s="6" t="inlineStr">
         <is>
-          <t>Mon 14 Sep</t>
+          <t>Tue 13 Oct</t>
         </is>
       </c>
       <c r="F139" s="6" t="n">
-        <v>-3</v>
+        <v>-15</v>
       </c>
       <c r="G139" s="6" t="inlineStr">
         <is>
@@ -9322,7 +9324,7 @@
       </c>
       <c r="H139" s="6" t="inlineStr">
         <is>
-          <t>T0005 on site on the record</t>
+          <t>T0266 on site on the record</t>
         </is>
       </c>
     </row>
@@ -9333,11 +9335,11 @@
         </is>
       </c>
       <c r="B140" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C140" s="6" t="inlineStr">
         <is>
-          <t>COATES Forklift Rough Terrain 4WD With Rotator 2.5</t>
+          <t>COATES Forklift Rough Terrain 2.5t With Switchable</t>
         </is>
       </c>
       <c r="D140" s="6" t="inlineStr">
@@ -9371,11 +9373,11 @@
         </is>
       </c>
       <c r="B141" s="6" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C141" s="6" t="inlineStr">
         <is>
-          <t>COATES- 5T FORKLIFT 1.8TYNNES</t>
+          <t>COATES Forklift Rough Terrain 4WD With Rotator 2.5</t>
         </is>
       </c>
       <c r="D141" s="6" t="inlineStr">
@@ -9385,11 +9387,11 @@
       </c>
       <c r="E141" s="6" t="inlineStr">
         <is>
-          <t>Fri 25 Sep</t>
+          <t>Mon 14 Sep</t>
         </is>
       </c>
       <c r="F141" s="6" t="n">
-        <v>-14</v>
+        <v>-3</v>
       </c>
       <c r="G141" s="6" t="inlineStr">
         <is>
@@ -9398,7 +9400,7 @@
       </c>
       <c r="H141" s="6" t="inlineStr">
         <is>
-          <t>FL01 on site on the record</t>
+          <t>T0005 on site on the record</t>
         </is>
       </c>
     </row>
@@ -9409,101 +9411,101 @@
         </is>
       </c>
       <c r="B142" s="6" t="n">
+        <v>31</v>
+      </c>
+      <c r="C142" s="6" t="inlineStr">
+        <is>
+          <t>COATES- 5T FORKLIFT 1.8TYNNES</t>
+        </is>
+      </c>
+      <c r="D142" s="6" t="inlineStr">
+        <is>
+          <t>Fri 11 Sep</t>
+        </is>
+      </c>
+      <c r="E142" s="6" t="inlineStr">
+        <is>
+          <t>Fri 25 Sep</t>
+        </is>
+      </c>
+      <c r="F142" s="6" t="n">
+        <v>-14</v>
+      </c>
+      <c r="G142" s="6" t="inlineStr">
+        <is>
+          <t>no - over the event; record only</t>
+        </is>
+      </c>
+      <c r="H142" s="6" t="inlineStr">
+        <is>
+          <t>FL01 on site on the record</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="6" t="inlineStr">
+        <is>
+          <t>9961976</t>
+        </is>
+      </c>
+      <c r="B143" s="6" t="n">
         <v>35</v>
       </c>
-      <c r="C142" s="6" t="inlineStr">
+      <c r="C143" s="6" t="inlineStr">
         <is>
           <t>COATES-Forklift Rough Terrain 2.5t With Switchable</t>
         </is>
       </c>
-      <c r="D142" s="6" t="inlineStr">
+      <c r="D143" s="6" t="inlineStr">
         <is>
           <t>Mon 19 Oct</t>
         </is>
       </c>
-      <c r="E142" s="6" t="inlineStr">
+      <c r="E143" s="6" t="inlineStr">
         <is>
           <t>Mon 14 Sep</t>
         </is>
       </c>
-      <c r="F142" s="6" t="n">
+      <c r="F143" s="6" t="n">
         <v>35</v>
       </c>
-      <c r="G142" s="6" t="inlineStr">
+      <c r="G143" s="6" t="inlineStr">
         <is>
           <t>no - over the event; record only</t>
         </is>
       </c>
-      <c r="H142" s="6" t="inlineStr">
+      <c r="H143" s="6" t="inlineStr">
         <is>
           <t>T0005 on site on the record</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
-        <is>
-          <t>9961976</t>
-        </is>
-      </c>
-      <c r="B143" s="2" t="n">
-        <v>48</v>
-      </c>
-      <c r="C143" s="2" t="inlineStr">
-        <is>
-          <t>GN06 Generator - 60kVA (Diesel)</t>
-        </is>
-      </c>
-      <c r="D143" s="2" t="inlineStr">
-        <is>
-          <t>Mon 19 Oct</t>
-        </is>
-      </c>
-      <c r="E143" s="2" t="inlineStr">
-        <is>
-          <t>Thu 15 Oct</t>
-        </is>
-      </c>
-      <c r="F143" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="G143" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H143" s="2" t="inlineStr">
-        <is>
-          <t>GN06 on site on the record</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>9972648</t>
+          <t>9961976</t>
         </is>
       </c>
       <c r="B144" s="2" t="n">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>WB03 Barrier - Crash Rated Water filled - Armorzon</t>
+          <t>GN06 Generator - 60kVA (Diesel)</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>Fri 18 Sep</t>
+          <t>Mon 19 Oct</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>Wed 23 Sep</t>
+          <t>Thu 15 Oct</t>
         </is>
       </c>
       <c r="F144" s="2" t="n">
-        <v>-5</v>
+        <v>4</v>
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
@@ -9512,36 +9514,36 @@
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
-          <t>WB03 on site on the record</t>
+          <t>GN06 on site on the record</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>9961265</t>
+          <t>9972648</t>
         </is>
       </c>
       <c r="B145" s="2" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>VMS22 445T Variable Message Board Senior Premiair</t>
+          <t>WB03 Barrier - Crash Rated Water filled - Armorzon</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>Wed 21 Oct</t>
+          <t>Fri 18 Sep</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>Thu 22 Oct</t>
+          <t>Wed 23 Sep</t>
         </is>
       </c>
       <c r="F145" s="2" t="n">
-        <v>-1</v>
+        <v>-5</v>
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
@@ -9550,7 +9552,7 @@
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
-          <t>Andrew's word (22 Oct) / pin on site</t>
+          <t>WB03 on site on the record</t>
         </is>
       </c>
     </row>
@@ -9561,16 +9563,16 @@
         </is>
       </c>
       <c r="B146" s="2" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>VMS24 450T Variable Message Board Senior</t>
+          <t>VMS22 445T Variable Message Board Senior Premiair</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>Mon 19 Oct</t>
+          <t>Wed 21 Oct</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
@@ -9579,7 +9581,7 @@
         </is>
       </c>
       <c r="F146" s="2" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
@@ -9599,11 +9601,11 @@
         </is>
       </c>
       <c r="B147" s="2" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>VMS14 Variable Message Board Junior</t>
+          <t>VMS24 450T Variable Message Board Senior</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
@@ -9613,11 +9615,11 @@
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>Fri 16 Oct</t>
+          <t>Thu 22 Oct</t>
         </is>
       </c>
       <c r="F147" s="2" t="n">
-        <v>3</v>
+        <v>-3</v>
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
@@ -9626,7 +9628,7 @@
       </c>
       <c r="H147" s="2" t="inlineStr">
         <is>
-          <t>recorded on site (load T0158)</t>
+          <t>Andrew's word (22 Oct) / pin on site</t>
         </is>
       </c>
     </row>
@@ -9637,11 +9639,11 @@
         </is>
       </c>
       <c r="B148" s="2" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>VMS15 Variable Message Board Senior</t>
+          <t>VMS14 Variable Message Board Junior</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
@@ -9675,11 +9677,11 @@
         </is>
       </c>
       <c r="B149" s="2" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>VMS16 Variable Message Board Senior</t>
+          <t>VMS15 Variable Message Board Senior</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
@@ -9713,11 +9715,11 @@
         </is>
       </c>
       <c r="B150" s="2" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>VMS17 Variable Message Board Senior</t>
+          <t>VMS16 Variable Message Board Senior</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
@@ -9745,116 +9747,116 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="6" t="inlineStr">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>9961265</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>VMS17 Variable Message Board Senior</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>Mon 19 Oct</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>Fri 16 Oct</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H151" s="2" t="inlineStr">
+        <is>
+          <t>recorded on site (load T0158)</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="6" t="inlineStr">
         <is>
           <t>9992300</t>
         </is>
       </c>
-      <c r="B151" s="6" t="n">
+      <c r="B152" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="C151" s="6" t="inlineStr">
+      <c r="C152" s="6" t="inlineStr">
         <is>
           <t>Fork Extensions 2.4m</t>
         </is>
       </c>
-      <c r="D151" s="6" t="inlineStr">
+      <c r="D152" s="6" t="inlineStr">
         <is>
           <t>Sat 17 Oct</t>
         </is>
       </c>
-      <c r="E151" s="6" t="inlineStr">
+      <c r="E152" s="6" t="inlineStr">
         <is>
           <t>Fri 23 Oct</t>
         </is>
       </c>
-      <c r="F151" s="6" t="n">
+      <c r="F152" s="6" t="n">
         <v>-6</v>
       </c>
-      <c r="G151" s="6" t="inlineStr">
+      <c r="G152" s="6" t="inlineStr">
         <is>
           <t>no - over the event; record only</t>
         </is>
       </c>
-      <c r="H151" s="6" t="inlineStr">
+      <c r="H152" s="6" t="inlineStr">
         <is>
           <t>EQ0005 on site on the record</t>
         </is>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr">
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
         <is>
           <t>9992300</t>
         </is>
       </c>
-      <c r="B152" s="2" t="n">
+      <c r="B153" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="C152" s="2" t="inlineStr">
+      <c r="C153" s="2" t="inlineStr">
         <is>
           <t>Scissor Lift With Operator Protection 43ft (13.0M)</t>
         </is>
       </c>
-      <c r="D152" s="2" t="inlineStr">
+      <c r="D153" s="2" t="inlineStr">
         <is>
           <t>Mon 19 Oct</t>
         </is>
       </c>
-      <c r="E152" s="2" t="inlineStr">
+      <c r="E153" s="2" t="inlineStr">
         <is>
           <t>Thu 22 Oct</t>
         </is>
       </c>
-      <c r="F152" s="2" t="n">
+      <c r="F153" s="2" t="n">
         <v>-3</v>
       </c>
-      <c r="G152" s="2" t="inlineStr">
+      <c r="G153" s="2" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H152" s="2" t="inlineStr">
+      <c r="H153" s="2" t="inlineStr">
         <is>
           <t>EQ0001 on site on the record</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="6" t="inlineStr">
-        <is>
-          <t>9994954</t>
-        </is>
-      </c>
-      <c r="B153" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C153" s="6" t="inlineStr">
-        <is>
-          <t>P38 Portable Building Shell 6.0M x 3.0M - Cyclonic</t>
-        </is>
-      </c>
-      <c r="D153" s="6" t="inlineStr">
-        <is>
-          <t>Fri 23 Oct</t>
-        </is>
-      </c>
-      <c r="E153" s="6" t="inlineStr">
-        <is>
-          <t>Mon 28 Sep</t>
-        </is>
-      </c>
-      <c r="F153" s="6" t="n">
-        <v>25</v>
-      </c>
-      <c r="G153" s="6" t="inlineStr">
-        <is>
-          <t>no - over the event; record only</t>
-        </is>
-      </c>
-      <c r="H153" s="6" t="inlineStr">
-        <is>
-          <t>P38 on site on the record</t>
         </is>
       </c>
     </row>
@@ -9865,11 +9867,11 @@
         </is>
       </c>
       <c r="B154" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C154" s="6" t="inlineStr">
         <is>
-          <t>P39 Portable Building Shell 6.0M x 3.0M - Cyclonic</t>
+          <t>P38 Portable Building Shell 6.0M x 3.0M - Cyclonic</t>
         </is>
       </c>
       <c r="D154" s="6" t="inlineStr">
@@ -9892,7 +9894,7 @@
       </c>
       <c r="H154" s="6" t="inlineStr">
         <is>
-          <t>P39 on site on the record</t>
+          <t>P38 on site on the record</t>
         </is>
       </c>
     </row>
@@ -9903,11 +9905,11 @@
         </is>
       </c>
       <c r="B155" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C155" s="6" t="inlineStr">
         <is>
-          <t>P42 Portable Building Shell 6.0M x 3.0M - Cyclonic</t>
+          <t>P39 Portable Building Shell 6.0M x 3.0M - Cyclonic</t>
         </is>
       </c>
       <c r="D155" s="6" t="inlineStr">
@@ -9930,45 +9932,45 @@
       </c>
       <c r="H155" s="6" t="inlineStr">
         <is>
+          <t>P39 on site on the record</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="6" t="inlineStr">
+        <is>
+          <t>9994954</t>
+        </is>
+      </c>
+      <c r="B156" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C156" s="6" t="inlineStr">
+        <is>
+          <t>P42 Portable Building Shell 6.0M x 3.0M - Cyclonic</t>
+        </is>
+      </c>
+      <c r="D156" s="6" t="inlineStr">
+        <is>
+          <t>Fri 23 Oct</t>
+        </is>
+      </c>
+      <c r="E156" s="6" t="inlineStr">
+        <is>
+          <t>Mon 28 Sep</t>
+        </is>
+      </c>
+      <c r="F156" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="G156" s="6" t="inlineStr">
+        <is>
+          <t>no - over the event; record only</t>
+        </is>
+      </c>
+      <c r="H156" s="6" t="inlineStr">
+        <is>
           <t>P42 on site on the record</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="2" t="inlineStr">
-        <is>
-          <t>9994954</t>
-        </is>
-      </c>
-      <c r="B156" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="C156" s="2" t="inlineStr">
-        <is>
-          <t>GN26 Generator - 200kVA (Diesel)</t>
-        </is>
-      </c>
-      <c r="D156" s="2" t="inlineStr">
-        <is>
-          <t>Fri 23 Oct</t>
-        </is>
-      </c>
-      <c r="E156" s="2" t="inlineStr">
-        <is>
-          <t>Mon 12 Oct</t>
-        </is>
-      </c>
-      <c r="F156" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="G156" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H156" s="2" t="inlineStr">
-        <is>
-          <t>GN? on site on the record</t>
         </is>
       </c>
     </row>
@@ -9979,11 +9981,11 @@
         </is>
       </c>
       <c r="B157" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>GN27 Generator - 200kVA (Diesel)</t>
+          <t>GN26 Generator - 200kVA (Diesel)</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
@@ -10011,40 +10013,40 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="6" t="inlineStr">
+      <c r="A158" s="2" t="inlineStr">
         <is>
           <t>9994954</t>
         </is>
       </c>
-      <c r="B158" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="C158" s="6" t="inlineStr">
-        <is>
-          <t>WC09 Toilet Block 6.0M x 3.0M - CAT 2</t>
-        </is>
-      </c>
-      <c r="D158" s="6" t="inlineStr">
+      <c r="B158" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>GN27 Generator - 200kVA (Diesel)</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
         <is>
           <t>Fri 23 Oct</t>
         </is>
       </c>
-      <c r="E158" s="6" t="inlineStr">
-        <is>
-          <t>Thu 08 Oct</t>
-        </is>
-      </c>
-      <c r="F158" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="G158" s="6" t="inlineStr">
-        <is>
-          <t>no - over the event; record only</t>
-        </is>
-      </c>
-      <c r="H158" s="6" t="inlineStr">
-        <is>
-          <t>WC09 on site on the record</t>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>Mon 12 Oct</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>GN? on site on the record</t>
         </is>
       </c>
     </row>
@@ -10055,11 +10057,11 @@
         </is>
       </c>
       <c r="B159" s="6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C159" s="6" t="inlineStr">
         <is>
-          <t>WC09 Toilet Block Male Female Cyclone Rated 6m x 3</t>
+          <t>WC09 Toilet Block 6.0M x 3.0M - CAT 2</t>
         </is>
       </c>
       <c r="D159" s="6" t="inlineStr">
@@ -10093,11 +10095,11 @@
         </is>
       </c>
       <c r="B160" s="6" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C160" s="6" t="inlineStr">
         <is>
-          <t>Pee Panels</t>
+          <t>WC09 Toilet Block Male Female Cyclone Rated 6m x 3</t>
         </is>
       </c>
       <c r="D160" s="6" t="inlineStr">
@@ -10131,11 +10133,11 @@
         </is>
       </c>
       <c r="B161" s="6" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C161" s="6" t="inlineStr">
         <is>
-          <t>WC09 FWF Toilet</t>
+          <t>Pee Panels</t>
         </is>
       </c>
       <c r="D161" s="6" t="inlineStr">
@@ -10169,32 +10171,70 @@
         </is>
       </c>
       <c r="B162" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="C162" s="6" t="inlineStr">
+        <is>
+          <t>WC09 FWF Toilet</t>
+        </is>
+      </c>
+      <c r="D162" s="6" t="inlineStr">
+        <is>
+          <t>Fri 23 Oct</t>
+        </is>
+      </c>
+      <c r="E162" s="6" t="inlineStr">
+        <is>
+          <t>Thu 08 Oct</t>
+        </is>
+      </c>
+      <c r="F162" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="G162" s="6" t="inlineStr">
+        <is>
+          <t>no - over the event; record only</t>
+        </is>
+      </c>
+      <c r="H162" s="6" t="inlineStr">
+        <is>
+          <t>WC09 on site on the record</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="6" t="inlineStr">
+        <is>
+          <t>9994954</t>
+        </is>
+      </c>
+      <c r="B163" s="6" t="n">
         <v>22</v>
       </c>
-      <c r="C162" s="6" t="inlineStr">
+      <c r="C163" s="6" t="inlineStr">
         <is>
           <t>WC10 FWF Toilet</t>
         </is>
       </c>
-      <c r="D162" s="6" t="inlineStr">
+      <c r="D163" s="6" t="inlineStr">
         <is>
           <t>Fri 23 Oct</t>
         </is>
       </c>
-      <c r="E162" s="6" t="inlineStr">
+      <c r="E163" s="6" t="inlineStr">
         <is>
           <t>Tue 13 Oct</t>
         </is>
       </c>
-      <c r="F162" s="6" t="n">
+      <c r="F163" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="G162" s="6" t="inlineStr">
+      <c r="G163" s="6" t="inlineStr">
         <is>
           <t>no - over the event; record only</t>
         </is>
       </c>
-      <c r="H162" s="6" t="inlineStr">
+      <c r="H163" s="6" t="inlineStr">
         <is>
           <t>WC10 on site on the record</t>
         </is>
@@ -14018,11 +14058,19 @@
         </is>
       </c>
       <c r="L6" s="2" t="n"/>
-      <c r="M6" s="2" t="n"/>
-      <c r="N6" s="2" t="n"/>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>EQ0006</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>EQ0006 on our record since 25 Oct (Andrew: on site; record_25Oct2026_accessories_laserplane)</t>
+          <t>starts Fri 16 Oct, turned up Sun 25 Oct (-9 days)</t>
         </is>
       </c>
     </row>
@@ -28293,67 +28341,63 @@
       <c r="O240" s="6" t="inlineStr"/>
     </row>
     <row r="241">
-      <c r="A241" s="2" t="inlineStr">
+      <c r="A241" s="6" t="inlineStr">
         <is>
           <t>9961976</t>
         </is>
       </c>
-      <c r="B241" s="2" t="n">
+      <c r="B241" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="C241" s="2" t="inlineStr">
+      <c r="C241" s="6" t="inlineStr">
         <is>
           <t>Delivered</t>
         </is>
       </c>
-      <c r="D241" s="2" t="n">
+      <c r="D241" s="6" t="n">
         <v>1276701</v>
       </c>
-      <c r="E241" s="2" t="inlineStr">
+      <c r="E241" s="6" t="inlineStr">
         <is>
           <t>GN20-S01-Generator 365kVA Diesel</t>
         </is>
       </c>
-      <c r="F241" s="2" t="n">
+      <c r="F241" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="G241" s="2" t="n">
+      <c r="G241" s="6" t="n">
         <v>6260.4</v>
       </c>
-      <c r="H241" s="2" t="n">
+      <c r="H241" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="I241" s="2" t="inlineStr">
+      <c r="I241" s="6" t="inlineStr">
         <is>
           <t>NVAC-HIR</t>
         </is>
       </c>
-      <c r="J241" s="2" t="inlineStr">
+      <c r="J241" s="6" t="inlineStr">
         <is>
           <t>NVAC</t>
         </is>
       </c>
-      <c r="K241" s="2" t="inlineStr">
+      <c r="K241" s="6" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="L241" s="2" t="n"/>
-      <c r="M241" s="2" t="inlineStr">
-        <is>
-          <t>GN20</t>
-        </is>
-      </c>
-      <c r="N241" s="2" t="inlineStr">
+      <c r="L241" s="6" t="n"/>
+      <c r="M241" s="6" t="inlineStr">
+        <is>
+          <t>GN20-A</t>
+        </is>
+      </c>
+      <c r="N241" s="6" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="O241" s="2" t="inlineStr">
-        <is>
-          <t>GN20 on site from Wed 30 Sep (Andrew, 25 Oct: "the gn20 is here"); the line stands. Our record deleted the reference on 20 Oct and the P&amp;L dropped it on 22 Oct: both to be put back</t>
-        </is>
-      </c>
+      <c r="O241" s="6" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" s="6" t="inlineStr">
@@ -40836,7 +40880,7 @@
       </c>
       <c r="I26" s="5" t="inlineStr">
         <is>
-          <t>2 large sets on site: GN20, GN23</t>
+          <t>2 large sets on site: GN20-A, GN23</t>
         </is>
       </c>
       <c r="J26" s="5" t="inlineStr">
@@ -40992,7 +41036,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2 large sets (GN20, GN23) x 2 legs</t>
+          <t>2 large sets (GN20-A, GN23) x 2 legs</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -41504,13 +41548,13 @@
         </is>
       </c>
       <c r="B2" s="6" t="n">
-        <v>13270</v>
+        <v>9292.5</v>
       </c>
       <c r="C2" s="6" t="n">
         <v>16.1607</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>214452.49</v>
+        <v>150173.3</v>
       </c>
       <c r="E2" s="6" t="inlineStr">
         <is>
@@ -41768,7 +41812,7 @@
       <c r="B11" s="6" t="n"/>
       <c r="C11" s="6" t="n"/>
       <c r="D11" s="6" t="n">
-        <v>405150.96</v>
+        <v>340871.73</v>
       </c>
       <c r="E11" s="6" t="inlineStr"/>
       <c r="F11" s="6" t="n"/>
@@ -41882,7 +41926,7 @@
       </c>
       <c r="E2" s="6" t="inlineStr">
         <is>
-          <t>GN20</t>
+          <t>GN20-A</t>
         </is>
       </c>
       <c r="F2" s="6" t="inlineStr">
@@ -41898,10 +41942,12 @@
       <c r="H2" s="6" t="n">
         <v>6260.4</v>
       </c>
-      <c r="I2" s="6" t="n"/>
+      <c r="I2" s="6" t="n">
+        <v>6840.83</v>
+      </c>
       <c r="J2" s="6" t="inlineStr">
         <is>
-          <t>off the P&amp;L since 22 Oct: to be put back</t>
+          <t>Street Rate Card 2026 · Generator 315 kVA · next size down from 350 kVA · published Standby Rate before 23 Oct</t>
         </is>
       </c>
       <c r="K2" s="6" t="inlineStr">
